--- a/Liang_61_Report.xlsx
+++ b/Liang_61_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301517</t>
+          <t>301182</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,29 +518,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>陕西华达</t>
+          <t>凯旺科技</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60.05</v>
+        <v>63.76</v>
       </c>
       <c r="F2" t="n">
-        <v>59.75</v>
+        <v>63.44</v>
       </c>
       <c r="G2" t="n">
-        <v>12.7</v>
+        <v>7.9</v>
       </c>
       <c r="H2" t="n">
-        <v>57.96</v>
+        <v>61.54</v>
       </c>
       <c r="I2" t="n">
-        <v>7.21</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5.79</v>
+        <v>7.81</v>
       </c>
       <c r="K2" t="n">
-        <v>11.36</v>
+        <v>5.13</v>
       </c>
       <c r="L2" t="n">
         <v>98</v>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20.55</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>600769</t>
+          <t>688268</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,46 +572,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>祥龙电业</t>
+          <t>华特气体</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14.87</v>
+        <v>102.25</v>
       </c>
       <c r="F3" t="n">
-        <v>14.8</v>
+        <v>101.74</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="H3" t="n">
-        <v>14.36</v>
+        <v>98.69</v>
       </c>
       <c r="I3" t="n">
-        <v>7.21</v>
+        <v>7.25</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>10.72</v>
       </c>
       <c r="K3" t="n">
-        <v>6.3</v>
+        <v>2.29</v>
       </c>
       <c r="L3" t="n">
         <v>98</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.09</v>
+        <v>53.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300790</t>
+          <t>002655</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,46 +626,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>宇瞳光学</t>
+          <t>共达电声</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30.44</v>
+        <v>21.39</v>
       </c>
       <c r="F4" t="n">
-        <v>30.29</v>
+        <v>21.28</v>
       </c>
       <c r="G4" t="n">
-        <v>12.7</v>
+        <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>29.38</v>
+        <v>20.64</v>
       </c>
       <c r="I4" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>11.36</v>
+        <v>14.96</v>
       </c>
       <c r="K4" t="n">
-        <v>11.45</v>
+        <v>2.46</v>
       </c>
       <c r="L4" t="n">
         <v>98</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>69.14</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>000919</t>
+          <t>688312</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,46 +680,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金陵药业</t>
+          <t>燕麦科技</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9.52</v>
+        <v>60.18</v>
       </c>
       <c r="F5" t="n">
-        <v>9.470000000000001</v>
+        <v>59.88</v>
       </c>
       <c r="G5" t="n">
-        <v>21.4</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>9.19</v>
+        <v>58.08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.85</v>
+        <v>6.83</v>
       </c>
       <c r="J5" t="n">
-        <v>20.68</v>
+        <v>7.55</v>
       </c>
       <c r="K5" t="n">
-        <v>22.5</v>
+        <v>2.91</v>
       </c>
       <c r="L5" t="n">
         <v>98</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>75.65000000000001</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>603112</t>
+          <t>300790</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -734,29 +734,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>华翔股份</t>
+          <t>宇瞳光学</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18.99</v>
+        <v>30.31</v>
       </c>
       <c r="F6" t="n">
-        <v>18.9</v>
+        <v>30.16</v>
       </c>
       <c r="G6" t="n">
-        <v>19.1</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>18.33</v>
+        <v>29.26</v>
       </c>
       <c r="I6" t="n">
-        <v>6.93</v>
+        <v>6.65</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>16.47</v>
       </c>
       <c r="K6" t="n">
-        <v>19.6</v>
+        <v>5.39</v>
       </c>
       <c r="L6" t="n">
         <v>98</v>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22.94</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>603158</t>
+          <t>000823</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -788,46 +788,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>腾龙股份</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.14</v>
+        <v>14.58</v>
       </c>
       <c r="F7" t="n">
-        <v>13.07</v>
+        <v>14.51</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="H7" t="n">
-        <v>12.68</v>
+        <v>14.07</v>
       </c>
       <c r="I7" t="n">
-        <v>6.83</v>
+        <v>6.73</v>
       </c>
       <c r="J7" t="n">
-        <v>10.78</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>8.52</v>
+        <v>4.46</v>
       </c>
       <c r="L7" t="n">
         <v>98</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>42.02</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>920438</t>
+          <t>300632</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,46 +842,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>戈碧迦</t>
+          <t>光莆股份</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>40.7</v>
+        <v>16.89</v>
       </c>
       <c r="F8" t="n">
-        <v>40.5</v>
+        <v>16.81</v>
       </c>
       <c r="G8" t="n">
-        <v>10.8</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>39.28</v>
+        <v>16.31</v>
       </c>
       <c r="I8" t="n">
-        <v>6.82</v>
+        <v>6.43</v>
       </c>
       <c r="J8" t="n">
-        <v>2.46</v>
+        <v>16.15</v>
       </c>
       <c r="K8" t="n">
-        <v>9.18</v>
+        <v>1.79</v>
       </c>
       <c r="L8" t="n">
         <v>98</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>8.44</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300485</t>
+          <t>300681</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -896,46 +896,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>赛升药业</t>
+          <t>英搏尔</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12.12</v>
+        <v>25.16</v>
       </c>
       <c r="F9" t="n">
-        <v>12.06</v>
+        <v>25.03</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4</v>
+        <v>6.5</v>
       </c>
       <c r="H9" t="n">
-        <v>11.7</v>
+        <v>24.28</v>
       </c>
       <c r="I9" t="n">
-        <v>6.22</v>
+        <v>6.57</v>
       </c>
       <c r="J9" t="n">
-        <v>10.43</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>7.92</v>
+        <v>4.02</v>
       </c>
       <c r="L9" t="n">
         <v>98</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>21.47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>002039</t>
+          <t>605005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -950,29 +950,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>黔源电力</t>
+          <t>合兴股份</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.6</v>
+        <v>20.76</v>
       </c>
       <c r="F10" t="n">
-        <v>20.5</v>
+        <v>20.66</v>
       </c>
       <c r="G10" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>19.88</v>
+        <v>20.04</v>
       </c>
       <c r="I10" t="n">
-        <v>6.63</v>
+        <v>5.92</v>
       </c>
       <c r="J10" t="n">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="K10" t="n">
-        <v>6.08</v>
+        <v>7.51</v>
       </c>
       <c r="L10" t="n">
         <v>98</v>
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>19.12</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>002655</t>
+          <t>300938</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,29 +1004,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>共达电声</t>
+          <t>信测标准</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.29</v>
+        <v>40.62</v>
       </c>
       <c r="F11" t="n">
-        <v>21.18</v>
+        <v>40.42</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>20.54</v>
+        <v>39.21</v>
       </c>
       <c r="I11" t="n">
-        <v>6.5</v>
+        <v>5.92</v>
       </c>
       <c r="J11" t="n">
-        <v>7.17</v>
+        <v>4.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="L11" t="n">
         <v>98</v>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>32.68</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>301307</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1058,46 +1058,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>光韵达</t>
+          <t>美利信</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.07</v>
+        <v>43.2</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>42.98</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>12.61</v>
+        <v>41.69</v>
       </c>
       <c r="I12" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6</v>
+        <v>9.77</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>2.97</v>
       </c>
       <c r="L12" t="n">
         <v>98</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>15.63</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>603297</t>
+          <t>603186</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1112,40 +1112,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>永新光学</t>
+          <t>华正新材</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112.8</v>
+        <v>75.33</v>
       </c>
       <c r="F13" t="n">
-        <v>112.24</v>
+        <v>74.95</v>
       </c>
       <c r="G13" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>108.87</v>
+        <v>72.7</v>
       </c>
       <c r="I13" t="n">
-        <v>5.45</v>
+        <v>6.29</v>
       </c>
       <c r="J13" t="n">
-        <v>1.47</v>
+        <v>7.41</v>
       </c>
       <c r="K13" t="n">
-        <v>7.31</v>
+        <v>1.93</v>
       </c>
       <c r="L13" t="n">
         <v>98</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>11.29</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="14">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="F14" t="n">
-        <v>27.96</v>
+        <v>28.06</v>
       </c>
       <c r="G14" t="n">
-        <v>14.9</v>
+        <v>8.1</v>
       </c>
       <c r="H14" t="n">
-        <v>27.12</v>
+        <v>27.22</v>
       </c>
       <c r="I14" t="n">
-        <v>5.72</v>
+        <v>6.09</v>
       </c>
       <c r="J14" t="n">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>15.07</v>
+        <v>6.38</v>
       </c>
       <c r="L14" t="n">
         <v>98</v>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>16.85</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>300938</t>
+          <t>603158</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1220,46 +1220,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>信测标准</t>
+          <t>腾龙股份</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>40.6</v>
+        <v>13.06</v>
       </c>
       <c r="F15" t="n">
-        <v>40.4</v>
+        <v>12.99</v>
       </c>
       <c r="G15" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
-        <v>39.19</v>
+        <v>12.6</v>
       </c>
       <c r="I15" t="n">
-        <v>5.87</v>
+        <v>6.18</v>
       </c>
       <c r="J15" t="n">
-        <v>3.51</v>
+        <v>13.62</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>3.41</v>
       </c>
       <c r="L15" t="n">
         <v>98</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>18.1</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>002708</t>
+          <t>300233</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,29 +1274,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>金城医药</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.56</v>
+        <v>15.66</v>
       </c>
       <c r="F16" t="n">
-        <v>13.49</v>
+        <v>15.58</v>
       </c>
       <c r="G16" t="n">
-        <v>11.9</v>
+        <v>7.5</v>
       </c>
       <c r="H16" t="n">
-        <v>13.09</v>
+        <v>15.11</v>
       </c>
       <c r="I16" t="n">
-        <v>6.02</v>
+        <v>5.81</v>
       </c>
       <c r="J16" t="n">
-        <v>3.42</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>11.14</v>
+        <v>5.8</v>
       </c>
       <c r="L16" t="n">
         <v>98</v>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>14.36</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>301362</t>
+          <t>603112</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,29 +1328,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>民爆光电</t>
+          <t>华翔股份</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>130.13</v>
+        <v>18.84</v>
       </c>
       <c r="F17" t="n">
-        <v>129.48</v>
+        <v>18.75</v>
       </c>
       <c r="G17" t="n">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
       <c r="H17" t="n">
-        <v>125.6</v>
+        <v>18.19</v>
       </c>
       <c r="I17" t="n">
-        <v>3.28</v>
+        <v>6.08</v>
       </c>
       <c r="J17" t="n">
-        <v>14.98</v>
+        <v>4.78</v>
       </c>
       <c r="K17" t="n">
-        <v>7.62</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
         <v>98</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>36.13</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>300903</t>
+          <t>301099</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1382,29 +1382,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>科翔股份</t>
+          <t>雅创电子</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34.21</v>
+        <v>52.7</v>
       </c>
       <c r="F18" t="n">
-        <v>34.04</v>
+        <v>52.44</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H18" t="n">
-        <v>33.02</v>
+        <v>50.87</v>
       </c>
       <c r="I18" t="n">
-        <v>3.23</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.79</v>
+        <v>12.12</v>
       </c>
       <c r="K18" t="n">
-        <v>4.15</v>
+        <v>2.61</v>
       </c>
       <c r="L18" t="n">
         <v>98</v>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>26.05</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>301630</t>
+          <t>301306</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,46 +1436,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>同宇新材</t>
+          <t>西测测试</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>236.48</v>
+        <v>159.92</v>
       </c>
       <c r="F19" t="n">
-        <v>235.3</v>
+        <v>159.12</v>
       </c>
       <c r="G19" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>228.24</v>
+        <v>154.35</v>
       </c>
       <c r="I19" t="n">
-        <v>3.04</v>
+        <v>4.99</v>
       </c>
       <c r="J19" t="n">
-        <v>15.51</v>
+        <v>9.94</v>
       </c>
       <c r="K19" t="n">
-        <v>5.33</v>
+        <v>1.39</v>
       </c>
       <c r="L19" t="n">
         <v>98</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>22.43</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>301306</t>
+          <t>300706</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>西测测试</t>
+          <t>阿石创</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>156.99</v>
+        <v>37.31</v>
       </c>
       <c r="F20" t="n">
-        <v>156.21</v>
+        <v>37.12</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="H20" t="n">
-        <v>151.52</v>
+        <v>36.01</v>
       </c>
       <c r="I20" t="n">
-        <v>3.07</v>
+        <v>4.98</v>
       </c>
       <c r="J20" t="n">
-        <v>5.9</v>
+        <v>12.06</v>
       </c>
       <c r="K20" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="L20" t="n">
         <v>98</v>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>32.87</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>000990</t>
+          <t>002348</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,46 +1544,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>诚志股份</t>
+          <t>高乐股份</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>10.57</v>
+        <v>9.27</v>
       </c>
       <c r="F21" t="n">
-        <v>10.52</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H21" t="n">
-        <v>10.2</v>
+        <v>8.94</v>
       </c>
       <c r="I21" t="n">
-        <v>5.28</v>
+        <v>4.63</v>
       </c>
       <c r="J21" t="n">
-        <v>3.68</v>
+        <v>5.68</v>
       </c>
       <c r="K21" t="n">
-        <v>4.87</v>
+        <v>5.16</v>
       </c>
       <c r="L21" t="n">
         <v>98</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>28.49</v>
+        <v>19.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>603031</t>
+          <t>300227</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,29 +1598,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>安孚科技</t>
+          <t>光韵达</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53.32</v>
+        <v>12.95</v>
       </c>
       <c r="F22" t="n">
-        <v>53.05</v>
+        <v>12.89</v>
       </c>
       <c r="G22" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="H22" t="n">
-        <v>51.46</v>
+        <v>12.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.13</v>
+        <v>5.46</v>
       </c>
       <c r="J22" t="n">
-        <v>2.18</v>
+        <v>8.41</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>3.57</v>
       </c>
       <c r="L22" t="n">
         <v>98</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>15.2</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>003018</t>
+          <t>301517</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1652,46 +1652,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>金富科技</t>
+          <t>陕西华达</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>32.5</v>
+        <v>59.08</v>
       </c>
       <c r="F23" t="n">
-        <v>32.34</v>
+        <v>58.78</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="H23" t="n">
-        <v>31.37</v>
+        <v>57.02</v>
       </c>
       <c r="I23" t="n">
-        <v>5.14</v>
+        <v>5.48</v>
       </c>
       <c r="J23" t="n">
-        <v>4.08</v>
+        <v>10.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.25</v>
+        <v>6.41</v>
       </c>
       <c r="L23" t="n">
         <v>98</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>19.39</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>600173</t>
+          <t>002980</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1706,46 +1706,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>卧龙新能</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7.15</v>
+        <v>55.76</v>
       </c>
       <c r="F24" t="n">
-        <v>7.11</v>
+        <v>55.48</v>
       </c>
       <c r="G24" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="H24" t="n">
-        <v>6.9</v>
+        <v>53.82</v>
       </c>
       <c r="I24" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="J24" t="n">
-        <v>2.31</v>
+        <v>12.9</v>
       </c>
       <c r="K24" t="n">
-        <v>8.31</v>
+        <v>1.34</v>
       </c>
       <c r="L24" t="n">
         <v>98</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7.07</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>002838</t>
+          <t>301362</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,46 +1760,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>道恩股份</t>
+          <t>民爆光电</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>27.32</v>
+        <v>133</v>
       </c>
       <c r="F25" t="n">
-        <v>27.18</v>
+        <v>132.34</v>
       </c>
       <c r="G25" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="H25" t="n">
-        <v>26.36</v>
+        <v>128.37</v>
       </c>
       <c r="I25" t="n">
-        <v>5.08</v>
+        <v>5.56</v>
       </c>
       <c r="J25" t="n">
-        <v>0.93</v>
+        <v>19.8</v>
       </c>
       <c r="K25" t="n">
-        <v>8.6</v>
+        <v>3.19</v>
       </c>
       <c r="L25" t="n">
         <v>98</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6.43</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>300975</t>
+          <t>300042</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1814,29 +1814,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>商络电子</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>21.05</v>
+        <v>47.84</v>
       </c>
       <c r="F26" t="n">
-        <v>20.94</v>
+        <v>47.6</v>
       </c>
       <c r="G26" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="H26" t="n">
-        <v>20.31</v>
+        <v>46.17</v>
       </c>
       <c r="I26" t="n">
-        <v>4.99</v>
+        <v>3.06</v>
       </c>
       <c r="J26" t="n">
-        <v>6.91</v>
+        <v>12.6</v>
       </c>
       <c r="K26" t="n">
-        <v>4.14</v>
+        <v>2.14</v>
       </c>
       <c r="L26" t="n">
         <v>98</v>
@@ -1847,13 +1847,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>43.16</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>301172</t>
+          <t>301282</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,46 +1868,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>君逸数码</t>
+          <t>金禄电子</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>30.48</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>30.33</v>
+        <v>37.81</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="H27" t="n">
-        <v>29.42</v>
+        <v>36.68</v>
       </c>
       <c r="I27" t="n">
-        <v>4.96</v>
+        <v>3.32</v>
       </c>
       <c r="J27" t="n">
-        <v>8.56</v>
+        <v>12.38</v>
       </c>
       <c r="K27" t="n">
-        <v>5.31</v>
+        <v>1.97</v>
       </c>
       <c r="L27" t="n">
         <v>98</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>15.7</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>688106</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1922,29 +1922,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>金宏气体</t>
+          <t>力诺药包</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>28.46</v>
+        <v>24.43</v>
       </c>
       <c r="F28" t="n">
-        <v>28.32</v>
+        <v>24.31</v>
       </c>
       <c r="G28" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="H28" t="n">
-        <v>27.47</v>
+        <v>23.58</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>3.21</v>
       </c>
       <c r="J28" t="n">
-        <v>4.46</v>
+        <v>10.97</v>
       </c>
       <c r="K28" t="n">
-        <v>3.88</v>
+        <v>1.31</v>
       </c>
       <c r="L28" t="n">
         <v>98</v>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>38.9</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002650</t>
+          <t>002150</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ST加加</t>
+          <t>正泰电源</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7.67</v>
+        <v>30.75</v>
       </c>
       <c r="F29" t="n">
-        <v>7.63</v>
+        <v>30.6</v>
       </c>
       <c r="G29" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="H29" t="n">
-        <v>7.4</v>
+        <v>29.68</v>
       </c>
       <c r="I29" t="n">
-        <v>4.64</v>
+        <v>3.19</v>
       </c>
       <c r="J29" t="n">
-        <v>1.43</v>
+        <v>6.21</v>
       </c>
       <c r="K29" t="n">
-        <v>9.02</v>
+        <v>1.92</v>
       </c>
       <c r="L29" t="n">
         <v>98</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7.44</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>000823</t>
+          <t>002246</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,46 +2030,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>北化股份</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>14.29</v>
+        <v>24.1</v>
       </c>
       <c r="F30" t="n">
-        <v>14.22</v>
+        <v>23.98</v>
       </c>
       <c r="G30" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="H30" t="n">
-        <v>13.79</v>
+        <v>23.26</v>
       </c>
       <c r="I30" t="n">
-        <v>4.61</v>
+        <v>3.17</v>
       </c>
       <c r="J30" t="n">
-        <v>5.57</v>
+        <v>3.95</v>
       </c>
       <c r="K30" t="n">
-        <v>9.26</v>
+        <v>1.67</v>
       </c>
       <c r="L30" t="n">
         <v>98</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>26.28</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>301392</t>
+          <t>002897</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2084,29 +2084,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>汇成真空</t>
+          <t>意华股份</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>143.19</v>
+        <v>66.78</v>
       </c>
       <c r="F31" t="n">
-        <v>142.47</v>
+        <v>66.45</v>
       </c>
       <c r="G31" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="H31" t="n">
-        <v>138.2</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>4.73</v>
+        <v>3.36</v>
       </c>
       <c r="J31" t="n">
-        <v>9.130000000000001</v>
+        <v>6.37</v>
       </c>
       <c r="K31" t="n">
-        <v>3.17</v>
+        <v>1.97</v>
       </c>
       <c r="L31" t="n">
         <v>98</v>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>32.62</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>300121</t>
+          <t>300903</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2138,46 +2138,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>阳谷华泰</t>
+          <t>科翔股份</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12.71</v>
+        <v>34.4</v>
       </c>
       <c r="F32" t="n">
-        <v>12.65</v>
+        <v>34.23</v>
       </c>
       <c r="G32" t="n">
-        <v>11.7</v>
+        <v>3.9</v>
       </c>
       <c r="H32" t="n">
-        <v>12.27</v>
+        <v>33.2</v>
       </c>
       <c r="I32" t="n">
-        <v>4.78</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.47</v>
+        <v>7.12</v>
       </c>
       <c r="K32" t="n">
-        <v>11.58</v>
+        <v>2.53</v>
       </c>
       <c r="L32" t="n">
         <v>98</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>11.61</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>603186</t>
+          <t>603687</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,29 +2192,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>大胜达</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>73.83</v>
+        <v>18.05</v>
       </c>
       <c r="F33" t="n">
-        <v>73.45999999999999</v>
+        <v>17.96</v>
       </c>
       <c r="G33" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="H33" t="n">
-        <v>71.26000000000001</v>
+        <v>17.42</v>
       </c>
       <c r="I33" t="n">
-        <v>4.18</v>
+        <v>3.97</v>
       </c>
       <c r="J33" t="n">
-        <v>4.63</v>
+        <v>14.84</v>
       </c>
       <c r="K33" t="n">
-        <v>3.81</v>
+        <v>1.84</v>
       </c>
       <c r="L33" t="n">
         <v>98</v>
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>32.53</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>603328</t>
+          <t>000420</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2246,46 +2246,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>依顿电子</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12.8</v>
+        <v>5.06</v>
       </c>
       <c r="F34" t="n">
-        <v>12.74</v>
+        <v>5.03</v>
       </c>
       <c r="G34" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="H34" t="n">
-        <v>12.36</v>
+        <v>4.88</v>
       </c>
       <c r="I34" t="n">
-        <v>4.23</v>
+        <v>4.12</v>
       </c>
       <c r="J34" t="n">
-        <v>4.25</v>
+        <v>6.43</v>
       </c>
       <c r="K34" t="n">
-        <v>7.44</v>
+        <v>2.71</v>
       </c>
       <c r="L34" t="n">
         <v>98</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>32.81</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301421</t>
+          <t>300077</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2300,29 +2300,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>波长光电</t>
+          <t>国民技术</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102.31</v>
+        <v>21.58</v>
       </c>
       <c r="F35" t="n">
-        <v>101.8</v>
+        <v>21.47</v>
       </c>
       <c r="G35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H35" t="n">
-        <v>98.75</v>
+        <v>20.83</v>
       </c>
       <c r="I35" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="J35" t="n">
-        <v>7.24</v>
+        <v>10.43</v>
       </c>
       <c r="K35" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="L35" t="n">
         <v>98</v>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>20.6</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>603757</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2354,46 +2354,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>创维数字</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12.05</v>
+        <v>51.34</v>
       </c>
       <c r="F36" t="n">
-        <v>11.99</v>
+        <v>51.08</v>
       </c>
       <c r="G36" t="n">
-        <v>10.4</v>
+        <v>4.1</v>
       </c>
       <c r="H36" t="n">
-        <v>11.63</v>
+        <v>49.55</v>
       </c>
       <c r="I36" t="n">
-        <v>4.42</v>
+        <v>4.26</v>
       </c>
       <c r="J36" t="n">
-        <v>1.9</v>
+        <v>10.31</v>
       </c>
       <c r="K36" t="n">
-        <v>10.28</v>
+        <v>2.43</v>
       </c>
       <c r="L36" t="n">
         <v>98</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>15.54</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>300077</t>
+          <t>300485</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2408,46 +2408,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>国民技术</t>
+          <t>赛升药业</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>21.63</v>
+        <v>11.78</v>
       </c>
       <c r="F37" t="n">
-        <v>21.52</v>
+        <v>11.72</v>
       </c>
       <c r="G37" t="n">
-        <v>10.4</v>
+        <v>4.3</v>
       </c>
       <c r="H37" t="n">
-        <v>20.87</v>
+        <v>11.37</v>
       </c>
       <c r="I37" t="n">
-        <v>4.59</v>
+        <v>3.24</v>
       </c>
       <c r="J37" t="n">
-        <v>8.699999999999999</v>
+        <v>13.52</v>
       </c>
       <c r="K37" t="n">
-        <v>10.17</v>
+        <v>3.34</v>
       </c>
       <c r="L37" t="n">
         <v>98</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>65.98999999999999</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>688485</t>
+          <t>605289</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2462,46 +2462,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>九州一轨</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>41.9</v>
+        <v>112.9</v>
       </c>
       <c r="F38" t="n">
-        <v>41.69</v>
+        <v>112.34</v>
       </c>
       <c r="G38" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="H38" t="n">
-        <v>40.44</v>
+        <v>108.97</v>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>3.19</v>
       </c>
       <c r="J38" t="n">
-        <v>13.49</v>
+        <v>5.03</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6</v>
+        <v>1.68</v>
       </c>
       <c r="L38" t="n">
         <v>98</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>30.75</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>603196</t>
+          <t>300975</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,46 +2516,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>璞源材料</t>
+          <t>商络电子</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31.93</v>
+        <v>20.66</v>
       </c>
       <c r="F39" t="n">
-        <v>31.77</v>
+        <v>20.56</v>
       </c>
       <c r="G39" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="H39" t="n">
-        <v>30.82</v>
+        <v>19.94</v>
       </c>
       <c r="I39" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="J39" t="n">
-        <v>2.99</v>
+        <v>10.58</v>
       </c>
       <c r="K39" t="n">
-        <v>6.76</v>
+        <v>2.06</v>
       </c>
       <c r="L39" t="n">
         <v>98</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>13.86</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>600810</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2570,46 +2570,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>神马股份</t>
+          <t>创维数字</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8.83</v>
+        <v>11.89</v>
       </c>
       <c r="F40" t="n">
-        <v>8.789999999999999</v>
+        <v>11.83</v>
       </c>
       <c r="G40" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
-        <v>8.529999999999999</v>
+        <v>11.48</v>
       </c>
       <c r="I40" t="n">
         <v>3.03</v>
       </c>
       <c r="J40" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="K40" t="n">
-        <v>5.22</v>
+        <v>4.4</v>
       </c>
       <c r="L40" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>16.58</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>000420</t>
+          <t>000949</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2624,46 +2624,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>新乡化纤</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5.03</v>
+        <v>7.64</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="G41" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="H41" t="n">
-        <v>4.85</v>
+        <v>7.37</v>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="J41" t="n">
-        <v>4.58</v>
+        <v>3.78</v>
       </c>
       <c r="K41" t="n">
-        <v>5.79</v>
+        <v>1.85</v>
       </c>
       <c r="L41" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>34.51</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>301188</t>
+          <t>002039</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2678,32 +2678,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>力诺药包</t>
+          <t>黔源电力</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>24.46</v>
+        <v>20.17</v>
       </c>
       <c r="F42" t="n">
-        <v>24.34</v>
+        <v>20.07</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="H42" t="n">
-        <v>23.61</v>
+        <v>19.47</v>
       </c>
       <c r="I42" t="n">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
-        <v>6.79</v>
+        <v>4.82</v>
       </c>
       <c r="K42" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L42" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>26.76</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>301590</t>
+          <t>603507</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2732,46 +2732,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>优优绿能</t>
+          <t>振江股份</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>181.14</v>
+        <v>44.01</v>
       </c>
       <c r="F43" t="n">
-        <v>180.23</v>
+        <v>43.79</v>
       </c>
       <c r="G43" t="n">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="H43" t="n">
-        <v>174.82</v>
+        <v>42.48</v>
       </c>
       <c r="I43" t="n">
-        <v>3.53</v>
+        <v>4.76</v>
       </c>
       <c r="J43" t="n">
-        <v>6.34</v>
+        <v>6.04</v>
       </c>
       <c r="K43" t="n">
-        <v>8.5</v>
+        <v>1.64</v>
       </c>
       <c r="L43" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>6.16</v>
+        <v>19.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>301099</t>
+          <t>603203</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>雅创电子</t>
+          <t>快克智能</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>51.96</v>
+        <v>44.04</v>
       </c>
       <c r="F44" t="n">
-        <v>51.7</v>
+        <v>43.82</v>
       </c>
       <c r="G44" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="H44" t="n">
-        <v>50.15</v>
+        <v>42.51</v>
       </c>
       <c r="I44" t="n">
-        <v>3.53</v>
+        <v>4.61</v>
       </c>
       <c r="J44" t="n">
-        <v>6.78</v>
+        <v>3.34</v>
       </c>
       <c r="K44" t="n">
-        <v>4.61</v>
+        <v>3.21</v>
       </c>
       <c r="L44" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>19.36</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>002589</t>
+          <t>300121</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2840,46 +2840,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>瑞康医药</t>
+          <t>阳谷华泰</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.55</v>
+        <v>12.58</v>
       </c>
       <c r="F45" t="n">
-        <v>3.53</v>
+        <v>12.52</v>
       </c>
       <c r="G45" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="H45" t="n">
-        <v>3.42</v>
+        <v>12.14</v>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="J45" t="n">
-        <v>10.96</v>
+        <v>4.52</v>
       </c>
       <c r="K45" t="n">
-        <v>6.56</v>
+        <v>4.91</v>
       </c>
       <c r="L45" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>33.08</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>002338</t>
+          <t>688275</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2894,46 +2894,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>奥普光电</t>
+          <t>万润新能</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>51.93</v>
+        <v>113.4</v>
       </c>
       <c r="F46" t="n">
-        <v>51.67</v>
+        <v>112.83</v>
       </c>
       <c r="G46" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="H46" t="n">
-        <v>50.12</v>
+        <v>109.45</v>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>4.37</v>
       </c>
       <c r="J46" t="n">
-        <v>1.46</v>
+        <v>3.27</v>
       </c>
       <c r="K46" t="n">
-        <v>7.17</v>
+        <v>1.48</v>
       </c>
       <c r="L46" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>11.14</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>002348</t>
+          <t>688135</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2948,46 +2948,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>高乐股份</t>
+          <t>利扬芯片</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>9.220000000000001</v>
+        <v>28.63</v>
       </c>
       <c r="F47" t="n">
-        <v>9.17</v>
+        <v>28.49</v>
       </c>
       <c r="G47" t="n">
-        <v>11.2</v>
+        <v>4.7</v>
       </c>
       <c r="H47" t="n">
-        <v>8.890000000000001</v>
+        <v>27.64</v>
       </c>
       <c r="I47" t="n">
-        <v>4.06</v>
+        <v>3.81</v>
       </c>
       <c r="J47" t="n">
-        <v>4.12</v>
+        <v>4.92</v>
       </c>
       <c r="K47" t="n">
-        <v>11.5</v>
+        <v>3.49</v>
       </c>
       <c r="L47" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>21.25</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>002246</t>
+          <t>605366</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3002,32 +3002,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北化股份</t>
+          <t>宏柏新材</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>24.33</v>
+        <v>12.35</v>
       </c>
       <c r="F48" t="n">
-        <v>24.21</v>
+        <v>12.29</v>
       </c>
       <c r="G48" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="H48" t="n">
-        <v>23.48</v>
+        <v>11.92</v>
       </c>
       <c r="I48" t="n">
-        <v>4.15</v>
+        <v>6.1</v>
       </c>
       <c r="J48" t="n">
-        <v>2.96</v>
+        <v>4.14</v>
       </c>
       <c r="K48" t="n">
-        <v>3.85</v>
+        <v>2.09</v>
       </c>
       <c r="L48" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>24.29</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>000949</t>
+          <t>603163</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3056,32 +3056,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>新乡化纤</t>
+          <t>圣晖集成</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.59</v>
+        <v>108.01</v>
       </c>
       <c r="F49" t="n">
-        <v>7.55</v>
+        <v>107.47</v>
       </c>
       <c r="G49" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H49" t="n">
-        <v>7.32</v>
+        <v>104.25</v>
       </c>
       <c r="I49" t="n">
-        <v>3.27</v>
+        <v>5.41</v>
       </c>
       <c r="J49" t="n">
-        <v>2.16</v>
+        <v>3.39</v>
       </c>
       <c r="K49" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="L49" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3089,13 +3089,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>16.43</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>301629</t>
+          <t>301571</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3110,46 +3110,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>矽电股份</t>
+          <t>国科天成</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>266.5</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>265.17</v>
+        <v>69.41</v>
       </c>
       <c r="G50" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="H50" t="n">
-        <v>257.21</v>
+        <v>67.33</v>
       </c>
       <c r="I50" t="n">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
       <c r="J50" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="K50" t="n">
-        <v>5.35</v>
+        <v>2.4</v>
       </c>
       <c r="L50" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>10.57</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>688593</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>盛视科技</t>
+          <t>新相微</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>33.75</v>
+        <v>32.37</v>
       </c>
       <c r="F51" t="n">
-        <v>33.58</v>
+        <v>32.21</v>
       </c>
       <c r="G51" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H51" t="n">
-        <v>32.57</v>
+        <v>31.24</v>
       </c>
       <c r="I51" t="n">
-        <v>3.43</v>
+        <v>4.49</v>
       </c>
       <c r="J51" t="n">
-        <v>5.76</v>
+        <v>3.01</v>
       </c>
       <c r="K51" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="L51" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>15.72</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>688275</t>
+          <t>301323</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>万润新能</t>
+          <t>新莱福</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="F52" t="n">
-        <v>111.44</v>
+        <v>65.67</v>
       </c>
       <c r="G52" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="H52" t="n">
-        <v>108.1</v>
+        <v>63.7</v>
       </c>
       <c r="I52" t="n">
-        <v>3.08</v>
+        <v>5.13</v>
       </c>
       <c r="J52" t="n">
-        <v>1.95</v>
+        <v>6.73</v>
       </c>
       <c r="K52" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="L52" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3251,13 +3251,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>16.76</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>688376</t>
+          <t>300191</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3272,46 +3272,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>美埃科技</t>
+          <t>潜能恒信</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>70.2</v>
+        <v>38.01</v>
       </c>
       <c r="F53" t="n">
-        <v>69.84999999999999</v>
+        <v>37.82</v>
       </c>
       <c r="G53" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="H53" t="n">
-        <v>67.75</v>
+        <v>36.69</v>
       </c>
       <c r="I53" t="n">
-        <v>6.62</v>
+        <v>3.26</v>
       </c>
       <c r="J53" t="n">
-        <v>1.49</v>
+        <v>4.84</v>
       </c>
       <c r="K53" t="n">
-        <v>5.85</v>
+        <v>1.1</v>
       </c>
       <c r="L53" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>8.52</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>603162</t>
+          <t>603297</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3326,46 +3326,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>海通发展</t>
+          <t>永新光学</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14.83</v>
+        <v>111.75</v>
       </c>
       <c r="F54" t="n">
-        <v>14.76</v>
+        <v>111.19</v>
       </c>
       <c r="G54" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="H54" t="n">
-        <v>14.32</v>
+        <v>107.85</v>
       </c>
       <c r="I54" t="n">
-        <v>3.71</v>
+        <v>4.47</v>
       </c>
       <c r="J54" t="n">
-        <v>3.76</v>
+        <v>2.12</v>
       </c>
       <c r="K54" t="n">
-        <v>5.27</v>
+        <v>3.34</v>
       </c>
       <c r="L54" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>9.52</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>688135</t>
+          <t>002338</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3380,46 +3380,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>利扬芯片</t>
+          <t>奥普光电</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>28.81</v>
+        <v>51.93</v>
       </c>
       <c r="F55" t="n">
-        <v>28.67</v>
+        <v>51.67</v>
       </c>
       <c r="G55" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H55" t="n">
-        <v>27.81</v>
+        <v>50.12</v>
       </c>
       <c r="I55" t="n">
-        <v>4.46</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="K55" t="n">
-        <v>5.27</v>
+        <v>3.23</v>
       </c>
       <c r="L55" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>9.24</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>688330</t>
+          <t>688530</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3434,46 +3434,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>宏力达</t>
+          <t>欧莱新材</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>51.12</v>
+        <v>32.57</v>
       </c>
       <c r="F56" t="n">
-        <v>50.86</v>
+        <v>32.41</v>
       </c>
       <c r="G56" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
-        <v>49.33</v>
+        <v>31.44</v>
       </c>
       <c r="I56" t="n">
-        <v>3.69</v>
+        <v>3.96</v>
       </c>
       <c r="J56" t="n">
-        <v>1.5</v>
+        <v>13.44</v>
       </c>
       <c r="K56" t="n">
-        <v>6.23</v>
+        <v>2.53</v>
       </c>
       <c r="L56" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>6.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>688079</t>
+          <t>600769</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3488,46 +3488,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>美迪凯</t>
+          <t>祥龙电业</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>14.97</v>
+        <v>14.83</v>
       </c>
       <c r="F57" t="n">
-        <v>14.9</v>
+        <v>14.76</v>
       </c>
       <c r="G57" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H57" t="n">
-        <v>14.45</v>
+        <v>14.32</v>
       </c>
       <c r="I57" t="n">
-        <v>4.83</v>
+        <v>6.92</v>
       </c>
       <c r="J57" t="n">
-        <v>2.37</v>
+        <v>4.4</v>
       </c>
       <c r="K57" t="n">
-        <v>5.11</v>
+        <v>3.25</v>
       </c>
       <c r="L57" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>8.75</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>600791</t>
+          <t>002838</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>京能置业</t>
+          <t>道恩股份</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>13.26</v>
+        <v>27.1</v>
       </c>
       <c r="F58" t="n">
-        <v>13.19</v>
+        <v>26.96</v>
       </c>
       <c r="G58" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H58" t="n">
-        <v>12.79</v>
+        <v>26.15</v>
       </c>
       <c r="I58" t="n">
-        <v>5.66</v>
+        <v>4.23</v>
       </c>
       <c r="J58" t="n">
-        <v>3.56</v>
+        <v>1.49</v>
       </c>
       <c r="K58" t="n">
-        <v>3.38</v>
+        <v>4.49</v>
       </c>
       <c r="L58" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>12.8</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>603507</t>
+          <t>002993</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>振江股份</t>
+          <t>奥海科技</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>43.33</v>
+        <v>50.34</v>
       </c>
       <c r="F59" t="n">
-        <v>43.11</v>
+        <v>50.09</v>
       </c>
       <c r="G59" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H59" t="n">
-        <v>41.82</v>
+        <v>48.59</v>
       </c>
       <c r="I59" t="n">
-        <v>3.14</v>
+        <v>3.79</v>
       </c>
       <c r="J59" t="n">
-        <v>2.93</v>
+        <v>2.31</v>
       </c>
       <c r="K59" t="n">
-        <v>2.58</v>
+        <v>2.21</v>
       </c>
       <c r="L59" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>14.08</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>603226</t>
+          <t>920438</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3650,32 +3650,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>菲林格尔</t>
+          <t>戈碧迦</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>39.12</v>
+        <v>39.75</v>
       </c>
       <c r="F60" t="n">
-        <v>38.92</v>
+        <v>39.55</v>
       </c>
       <c r="G60" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="H60" t="n">
-        <v>37.75</v>
+        <v>38.36</v>
       </c>
       <c r="I60" t="n">
-        <v>6.22</v>
+        <v>4.33</v>
       </c>
       <c r="J60" t="n">
-        <v>0.91</v>
+        <v>3.28</v>
       </c>
       <c r="K60" t="n">
-        <v>4.86</v>
+        <v>3.68</v>
       </c>
       <c r="L60" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>7.6</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>301265</t>
+          <t>600791</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>华新环保</t>
+          <t>京能置业</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>21.2</v>
+        <v>13.2</v>
       </c>
       <c r="F61" t="n">
-        <v>21.09</v>
+        <v>13.13</v>
       </c>
       <c r="G61" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="H61" t="n">
-        <v>20.46</v>
+        <v>12.74</v>
       </c>
       <c r="I61" t="n">
-        <v>3.41</v>
+        <v>5.18</v>
       </c>
       <c r="J61" t="n">
-        <v>4.02</v>
+        <v>5.21</v>
       </c>
       <c r="K61" t="n">
-        <v>4.46</v>
+        <v>1.57</v>
       </c>
       <c r="L61" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3737,13 +3737,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>8.800000000000001</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>301252</t>
+          <t>301387</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3758,46 +3758,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>同星科技</t>
+          <t>光大同创</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>38.4</v>
+        <v>63.37</v>
       </c>
       <c r="F62" t="n">
-        <v>38.21</v>
+        <v>63.05</v>
       </c>
       <c r="G62" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="H62" t="n">
-        <v>37.06</v>
+        <v>61.16</v>
       </c>
       <c r="I62" t="n">
-        <v>4.38</v>
+        <v>6.04</v>
       </c>
       <c r="J62" t="n">
-        <v>4.76</v>
+        <v>7.49</v>
       </c>
       <c r="K62" t="n">
-        <v>5.89</v>
+        <v>3.32</v>
       </c>
       <c r="L62" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.26</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>688419</t>
+          <t>603226</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3812,32 +3812,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>耐科装备</t>
+          <t>菲林格尔</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>51.79</v>
+        <v>39.06</v>
       </c>
       <c r="F63" t="n">
-        <v>51.53</v>
+        <v>38.86</v>
       </c>
       <c r="G63" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H63" t="n">
-        <v>49.98</v>
+        <v>37.69</v>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>6.05</v>
       </c>
       <c r="J63" t="n">
-        <v>4.01</v>
+        <v>1.63</v>
       </c>
       <c r="K63" t="n">
-        <v>4.92</v>
+        <v>2.76</v>
       </c>
       <c r="L63" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>7.44</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>301326</t>
+          <t>603353</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>捷邦科技</t>
+          <t>和顺石油</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>153.01</v>
+        <v>42.92</v>
       </c>
       <c r="F64" t="n">
-        <v>152.24</v>
+        <v>42.71</v>
       </c>
       <c r="G64" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="H64" t="n">
-        <v>147.67</v>
+        <v>41.43</v>
       </c>
       <c r="I64" t="n">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="J64" t="n">
-        <v>1.38</v>
+        <v>4.44</v>
       </c>
       <c r="K64" t="n">
-        <v>4.08</v>
+        <v>1.29</v>
       </c>
       <c r="L64" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>9.210000000000001</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>301387</t>
+          <t>603115</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3920,46 +3920,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>光大同创</t>
+          <t>海星股份</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>61.62</v>
+        <v>46.02</v>
       </c>
       <c r="F65" t="n">
-        <v>61.31</v>
+        <v>45.79</v>
       </c>
       <c r="G65" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="H65" t="n">
-        <v>59.47</v>
+        <v>44.42</v>
       </c>
       <c r="I65" t="n">
-        <v>3.11</v>
+        <v>4.12</v>
       </c>
       <c r="J65" t="n">
-        <v>3.74</v>
+        <v>2.99</v>
       </c>
       <c r="K65" t="n">
-        <v>5.23</v>
+        <v>1.19</v>
       </c>
       <c r="L65" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>5.96</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>002993</t>
+          <t>301326</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3974,32 +3974,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>奥海科技</t>
+          <t>捷邦科技</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>50.27</v>
+        <v>151.51</v>
       </c>
       <c r="F66" t="n">
-        <v>50.02</v>
+        <v>150.75</v>
       </c>
       <c r="G66" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="H66" t="n">
-        <v>48.52</v>
+        <v>146.23</v>
       </c>
       <c r="I66" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="J66" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="K66" t="n">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="L66" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>9.32</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>603126</t>
+          <t>300389</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4028,46 +4028,46 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>中材节能</t>
+          <t>艾比森</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8.220000000000001</v>
+        <v>18.87</v>
       </c>
       <c r="F67" t="n">
-        <v>8.18</v>
+        <v>18.78</v>
       </c>
       <c r="G67" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="H67" t="n">
-        <v>7.93</v>
+        <v>18.22</v>
       </c>
       <c r="I67" t="n">
-        <v>3.92</v>
+        <v>4.95</v>
       </c>
       <c r="J67" t="n">
-        <v>1.7</v>
+        <v>6.46</v>
       </c>
       <c r="K67" t="n">
-        <v>5.51</v>
+        <v>1.9</v>
       </c>
       <c r="L67" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5.2</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>002824</t>
+          <t>300868</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>和胜股份</t>
+          <t>杰美特</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>22</v>
+        <v>58.02</v>
       </c>
       <c r="F68" t="n">
-        <v>21.89</v>
+        <v>57.73</v>
       </c>
       <c r="G68" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H68" t="n">
-        <v>21.23</v>
+        <v>56</v>
       </c>
       <c r="I68" t="n">
-        <v>5.36</v>
+        <v>7.21</v>
       </c>
       <c r="J68" t="n">
-        <v>3.36</v>
+        <v>5.53</v>
       </c>
       <c r="K68" t="n">
-        <v>3.57</v>
+        <v>1.91</v>
       </c>
       <c r="L68" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>9.800000000000001</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>605056</t>
+          <t>002650</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>咸亨国际</t>
+          <t>ST加加</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>27.69</v>
+        <v>7.68</v>
       </c>
       <c r="F69" t="n">
-        <v>27.55</v>
+        <v>7.64</v>
       </c>
       <c r="G69" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="H69" t="n">
-        <v>26.72</v>
+        <v>7.41</v>
       </c>
       <c r="I69" t="n">
-        <v>3.9</v>
+        <v>4.77</v>
       </c>
       <c r="J69" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="K69" t="n">
-        <v>3.02</v>
+        <v>3.53</v>
       </c>
       <c r="L69" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>10.33</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>300843</t>
+          <t>603162</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4190,32 +4190,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>胜蓝股份</t>
+          <t>海通发展</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>63</v>
+        <v>14.79</v>
       </c>
       <c r="F70" t="n">
-        <v>62.68</v>
+        <v>14.72</v>
       </c>
       <c r="G70" t="n">
         <v>3.6</v>
       </c>
       <c r="H70" t="n">
-        <v>60.8</v>
+        <v>14.28</v>
       </c>
       <c r="I70" t="n">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="J70" t="n">
-        <v>1.92</v>
+        <v>5.19</v>
       </c>
       <c r="K70" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="L70" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>11.74</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>688345</t>
+          <t>301093</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>博力威</t>
+          <t>华兰股份</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>50.99</v>
+        <v>88.02</v>
       </c>
       <c r="F71" t="n">
-        <v>50.74</v>
+        <v>87.58</v>
       </c>
       <c r="G71" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="H71" t="n">
-        <v>49.22</v>
+        <v>84.95</v>
       </c>
       <c r="I71" t="n">
-        <v>4.19</v>
+        <v>4.62</v>
       </c>
       <c r="J71" t="n">
-        <v>2.86</v>
+        <v>1.89</v>
       </c>
       <c r="K71" t="n">
-        <v>3.38</v>
+        <v>1.67</v>
       </c>
       <c r="L71" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>8.73</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>300559</t>
+          <t>688376</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4298,32 +4298,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>佳发教育</t>
+          <t>美埃科技</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>14.76</v>
+        <v>68.81</v>
       </c>
       <c r="F72" t="n">
-        <v>14.69</v>
+        <v>68.47</v>
       </c>
       <c r="G72" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H72" t="n">
-        <v>14.25</v>
+        <v>66.42</v>
       </c>
       <c r="I72" t="n">
-        <v>3.72</v>
+        <v>4.51</v>
       </c>
       <c r="J72" t="n">
-        <v>3.01</v>
+        <v>2.1</v>
       </c>
       <c r="K72" t="n">
-        <v>3.44</v>
+        <v>2.55</v>
       </c>
       <c r="L72" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -4331,13 +4331,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>8.539999999999999</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>603121</t>
+          <t>300756</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4352,32 +4352,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>华培动力</t>
+          <t>金马游乐</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>20.69</v>
+        <v>45.55</v>
       </c>
       <c r="F73" t="n">
-        <v>20.59</v>
+        <v>45.32</v>
       </c>
       <c r="G73" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H73" t="n">
-        <v>19.97</v>
+        <v>43.96</v>
       </c>
       <c r="I73" t="n">
-        <v>5.51</v>
+        <v>6.05</v>
       </c>
       <c r="J73" t="n">
-        <v>1.9</v>
+        <v>3.04</v>
       </c>
       <c r="K73" t="n">
-        <v>3.34</v>
+        <v>2.59</v>
       </c>
       <c r="L73" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7.99</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>688662</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4406,32 +4406,32 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>富信科技</t>
+          <t>华丰股份</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>63.09</v>
+        <v>45.55</v>
       </c>
       <c r="F74" t="n">
-        <v>62.77</v>
+        <v>45.32</v>
       </c>
       <c r="G74" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H74" t="n">
-        <v>60.89</v>
+        <v>43.96</v>
       </c>
       <c r="I74" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="K74" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="L74" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>8.289999999999999</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>002782</t>
+          <t>688079</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>可立克</t>
+          <t>美迪凯</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>22.05</v>
+        <v>14.94</v>
       </c>
       <c r="F75" t="n">
-        <v>21.94</v>
+        <v>14.87</v>
       </c>
       <c r="G75" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H75" t="n">
-        <v>21.28</v>
+        <v>14.42</v>
       </c>
       <c r="I75" t="n">
-        <v>3.13</v>
+        <v>4.62</v>
       </c>
       <c r="J75" t="n">
-        <v>1.15</v>
+        <v>3.34</v>
       </c>
       <c r="K75" t="n">
-        <v>3.36</v>
+        <v>2.22</v>
       </c>
       <c r="L75" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>7.44</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>301093</t>
+          <t>002782</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4514,32 +4514,32 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>华兰股份</t>
+          <t>可立克</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>87.18000000000001</v>
+        <v>22.08</v>
       </c>
       <c r="F76" t="n">
-        <v>86.73999999999999</v>
+        <v>21.97</v>
       </c>
       <c r="G76" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="H76" t="n">
-        <v>84.14</v>
+        <v>21.31</v>
       </c>
       <c r="I76" t="n">
-        <v>3.63</v>
+        <v>3.27</v>
       </c>
       <c r="J76" t="n">
-        <v>1.02</v>
+        <v>2.01</v>
       </c>
       <c r="K76" t="n">
-        <v>2.85</v>
+        <v>1.92</v>
       </c>
       <c r="L76" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>8.359999999999999</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>605319</t>
+          <t>688330</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4568,32 +4568,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>无锡振华</t>
+          <t>宏力达</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>28.46</v>
+        <v>50.83</v>
       </c>
       <c r="F77" t="n">
-        <v>28.32</v>
+        <v>50.58</v>
       </c>
       <c r="G77" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="H77" t="n">
-        <v>27.47</v>
+        <v>49.06</v>
       </c>
       <c r="I77" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
-        <v>1.08</v>
+        <v>2.16</v>
       </c>
       <c r="K77" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="L77" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>6.39</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>002937</t>
+          <t>300137</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4622,29 +4622,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>兴瑞科技</t>
+          <t>先河环保</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>29.08</v>
+        <v>13.21</v>
       </c>
       <c r="F78" t="n">
-        <v>28.93</v>
+        <v>13.14</v>
       </c>
       <c r="G78" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="n">
-        <v>28.06</v>
+        <v>12.75</v>
       </c>
       <c r="I78" t="n">
-        <v>3.19</v>
+        <v>3.69</v>
       </c>
       <c r="J78" t="n">
-        <v>1.09</v>
+        <v>3.22</v>
       </c>
       <c r="K78" t="n">
-        <v>3.01</v>
+        <v>1.68</v>
       </c>
       <c r="L78" t="n">
         <v>52</v>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>5.72</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>688383</t>
+          <t>301235</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4676,32 +4676,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>新益昌</t>
+          <t>华康洁净</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>94.56999999999999</v>
+        <v>50.35</v>
       </c>
       <c r="F79" t="n">
-        <v>94.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="G79" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="H79" t="n">
-        <v>91.28</v>
+        <v>48.6</v>
       </c>
       <c r="I79" t="n">
-        <v>6.29</v>
+        <v>4.07</v>
       </c>
       <c r="J79" t="n">
-        <v>1.09</v>
+        <v>5.78</v>
       </c>
       <c r="K79" t="n">
-        <v>2.56</v>
+        <v>1.79</v>
       </c>
       <c r="L79" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>6.26</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>002718</t>
+          <t>300559</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4730,29 +4730,29 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>友邦吊顶</t>
+          <t>佳发教育</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>74.28</v>
+        <v>14.98</v>
       </c>
       <c r="F80" t="n">
-        <v>73.91</v>
+        <v>14.91</v>
       </c>
       <c r="G80" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="H80" t="n">
-        <v>71.69</v>
+        <v>14.46</v>
       </c>
       <c r="I80" t="n">
-        <v>7.36</v>
+        <v>5.27</v>
       </c>
       <c r="J80" t="n">
-        <v>1.5</v>
+        <v>4.57</v>
       </c>
       <c r="K80" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="L80" t="n">
         <v>50</v>
@@ -4763,7 +4763,493 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>6.23</v>
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>688383</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>新益昌</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="F81" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L81" t="n">
+        <v>50</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>300696</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>爱乐达</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H82" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L82" t="n">
+        <v>50</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>002937</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>兴瑞科技</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="F83" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H83" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L83" t="n">
+        <v>48</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>301369</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>联动科技</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>143.23</v>
+      </c>
+      <c r="F84" t="n">
+        <v>142.51</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H84" t="n">
+        <v>138.23</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L84" t="n">
+        <v>48</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>688667</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>菱电电控</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>114</v>
+      </c>
+      <c r="F85" t="n">
+        <v>113.43</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H85" t="n">
+        <v>110.03</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L85" t="n">
+        <v>45</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>301133</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>金钟股份</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F86" t="n">
+        <v>43.58</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="I86" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L86" t="n">
+        <v>40</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>601515</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>衢州东峰</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L87" t="n">
+        <v>39</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>000908</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ST景峰</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="F88" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L88" t="n">
+        <v>35</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>300819</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>聚杰微纤</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="F89" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L89" t="n">
+        <v>34</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>5.73</v>
       </c>
     </row>
   </sheetData>

--- a/Liang_61_Report.xlsx
+++ b/Liang_61_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>19.35</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="3">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>53.21</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="4">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>45.68</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688312</t>
+          <t>000823</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,29 +680,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>燕麦科技</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60.18</v>
+        <v>14.58</v>
       </c>
       <c r="F5" t="n">
-        <v>59.88</v>
+        <v>14.51</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="H5" t="n">
-        <v>58.08</v>
+        <v>14.07</v>
       </c>
       <c r="I5" t="n">
-        <v>6.83</v>
+        <v>6.73</v>
       </c>
       <c r="J5" t="n">
-        <v>7.55</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.91</v>
+        <v>4.46</v>
       </c>
       <c r="L5" t="n">
         <v>98</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26.33</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300790</t>
+          <t>688312</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -734,46 +734,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宇瞳光学</t>
+          <t>燕麦科技</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30.31</v>
+        <v>60.18</v>
       </c>
       <c r="F6" t="n">
-        <v>30.16</v>
+        <v>59.88</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>29.26</v>
+        <v>58.08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.65</v>
+        <v>6.83</v>
       </c>
       <c r="J6" t="n">
-        <v>16.47</v>
+        <v>7.55</v>
       </c>
       <c r="K6" t="n">
-        <v>5.39</v>
+        <v>2.91</v>
       </c>
       <c r="L6" t="n">
         <v>98</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>64.8</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>000823</t>
+          <t>300681</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -788,29 +788,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>英搏尔</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.58</v>
+        <v>25.16</v>
       </c>
       <c r="F7" t="n">
-        <v>14.51</v>
+        <v>25.03</v>
       </c>
       <c r="G7" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="H7" t="n">
-        <v>14.07</v>
+        <v>24.28</v>
       </c>
       <c r="I7" t="n">
-        <v>6.73</v>
+        <v>6.57</v>
       </c>
       <c r="J7" t="n">
-        <v>8.039999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="L7" t="n">
         <v>98</v>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24.8</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300632</t>
+          <t>300790</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,46 +842,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>光莆股份</t>
+          <t>宇瞳光学</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.89</v>
+        <v>30.31</v>
       </c>
       <c r="F8" t="n">
-        <v>16.81</v>
+        <v>30.16</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>16.31</v>
+        <v>29.26</v>
       </c>
       <c r="I8" t="n">
-        <v>6.43</v>
+        <v>6.65</v>
       </c>
       <c r="J8" t="n">
-        <v>16.15</v>
+        <v>16.47</v>
       </c>
       <c r="K8" t="n">
-        <v>1.79</v>
+        <v>5.39</v>
       </c>
       <c r="L8" t="n">
         <v>98</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>23.32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300681</t>
+          <t>603158</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -896,29 +896,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>英搏尔</t>
+          <t>腾龙股份</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25.16</v>
+        <v>13.06</v>
       </c>
       <c r="F9" t="n">
-        <v>25.03</v>
+        <v>12.99</v>
       </c>
       <c r="G9" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="H9" t="n">
-        <v>24.28</v>
+        <v>12.6</v>
       </c>
       <c r="I9" t="n">
-        <v>6.57</v>
+        <v>6.18</v>
       </c>
       <c r="J9" t="n">
-        <v>9.390000000000001</v>
+        <v>13.62</v>
       </c>
       <c r="K9" t="n">
-        <v>4.02</v>
+        <v>3.41</v>
       </c>
       <c r="L9" t="n">
         <v>98</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>22</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>605005</t>
+          <t>603186</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -950,46 +950,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>合兴股份</t>
+          <t>华正新材</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.76</v>
+        <v>75.33</v>
       </c>
       <c r="F10" t="n">
-        <v>20.66</v>
+        <v>74.95</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>20.04</v>
+        <v>72.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.92</v>
+        <v>6.29</v>
       </c>
       <c r="J10" t="n">
-        <v>3.17</v>
+        <v>7.41</v>
       </c>
       <c r="K10" t="n">
-        <v>7.51</v>
+        <v>1.93</v>
       </c>
       <c r="L10" t="n">
         <v>98</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>10.58</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300938</t>
+          <t>301362</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,29 +1004,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>信测标准</t>
+          <t>民爆光电</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.62</v>
+        <v>133</v>
       </c>
       <c r="F11" t="n">
-        <v>40.42</v>
+        <v>132.34</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H11" t="n">
-        <v>39.21</v>
+        <v>128.37</v>
       </c>
       <c r="I11" t="n">
-        <v>5.92</v>
+        <v>5.56</v>
       </c>
       <c r="J11" t="n">
-        <v>4.96</v>
+        <v>19.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="L11" t="n">
         <v>98</v>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>16.71</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>301307</t>
+          <t>301517</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1058,46 +1058,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>美利信</t>
+          <t>陕西华达</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>43.2</v>
+        <v>59.08</v>
       </c>
       <c r="F12" t="n">
-        <v>42.98</v>
+        <v>58.78</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="H12" t="n">
-        <v>41.69</v>
+        <v>57.02</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>5.48</v>
       </c>
       <c r="J12" t="n">
-        <v>9.77</v>
+        <v>10.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.97</v>
+        <v>6.41</v>
       </c>
       <c r="L12" t="n">
         <v>98</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>17.86</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>603186</t>
+          <t>300233</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1112,46 +1112,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>金城医药</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>75.33</v>
+        <v>15.66</v>
       </c>
       <c r="F13" t="n">
-        <v>74.95</v>
+        <v>15.58</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
-        <v>72.7</v>
+        <v>15.11</v>
       </c>
       <c r="I13" t="n">
-        <v>6.29</v>
+        <v>5.81</v>
       </c>
       <c r="J13" t="n">
-        <v>7.41</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1.93</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
         <v>98</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>34.14</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>605016</t>
+          <t>605005</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1166,29 +1166,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>百龙创园</t>
+          <t>合兴股份</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28.2</v>
+        <v>20.76</v>
       </c>
       <c r="F14" t="n">
-        <v>28.06</v>
+        <v>20.66</v>
       </c>
       <c r="G14" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>27.22</v>
+        <v>20.04</v>
       </c>
       <c r="I14" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="K14" t="n">
-        <v>6.38</v>
+        <v>7.51</v>
       </c>
       <c r="L14" t="n">
         <v>98</v>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>15.15</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>603158</t>
+          <t>603112</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1220,46 +1220,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>腾龙股份</t>
+          <t>华翔股份</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.06</v>
+        <v>18.84</v>
       </c>
       <c r="F15" t="n">
-        <v>12.99</v>
+        <v>18.75</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8</v>
+        <v>9.1</v>
       </c>
       <c r="H15" t="n">
-        <v>12.6</v>
+        <v>18.19</v>
       </c>
       <c r="I15" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="J15" t="n">
-        <v>13.62</v>
+        <v>4.78</v>
       </c>
       <c r="K15" t="n">
-        <v>3.41</v>
+        <v>7.6</v>
       </c>
       <c r="L15" t="n">
         <v>98</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>34.59</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>300233</t>
+          <t>605016</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,29 +1274,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金城医药</t>
+          <t>百龙创园</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>15.66</v>
+        <v>28.2</v>
       </c>
       <c r="F16" t="n">
-        <v>15.58</v>
+        <v>28.06</v>
       </c>
       <c r="G16" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="H16" t="n">
-        <v>15.11</v>
+        <v>27.22</v>
       </c>
       <c r="I16" t="n">
-        <v>5.81</v>
+        <v>6.09</v>
       </c>
       <c r="J16" t="n">
-        <v>8.960000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8</v>
+        <v>6.38</v>
       </c>
       <c r="L16" t="n">
         <v>98</v>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>21.3</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>603112</t>
+          <t>002150</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,46 +1328,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>华翔股份</t>
+          <t>正泰电源</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>18.84</v>
+        <v>30.75</v>
       </c>
       <c r="F17" t="n">
-        <v>18.75</v>
+        <v>30.6</v>
       </c>
       <c r="G17" t="n">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="H17" t="n">
-        <v>18.19</v>
+        <v>29.68</v>
       </c>
       <c r="I17" t="n">
-        <v>6.08</v>
+        <v>3.19</v>
       </c>
       <c r="J17" t="n">
-        <v>4.78</v>
+        <v>6.21</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6</v>
+        <v>1.92</v>
       </c>
       <c r="L17" t="n">
         <v>98</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>18.27</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>301099</t>
+          <t>300975</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1382,29 +1382,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>雅创电子</t>
+          <t>商络电子</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>52.7</v>
+        <v>20.66</v>
       </c>
       <c r="F18" t="n">
-        <v>52.44</v>
+        <v>20.56</v>
       </c>
       <c r="G18" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="n">
-        <v>50.87</v>
+        <v>19.94</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>3.04</v>
       </c>
       <c r="J18" t="n">
-        <v>12.12</v>
+        <v>10.58</v>
       </c>
       <c r="K18" t="n">
-        <v>2.61</v>
+        <v>2.06</v>
       </c>
       <c r="L18" t="n">
         <v>98</v>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>22.81</v>
+        <v>32.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>301306</t>
+          <t>300042</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,29 +1436,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>西测测试</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>159.92</v>
+        <v>47.84</v>
       </c>
       <c r="F19" t="n">
-        <v>159.12</v>
+        <v>47.6</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="n">
-        <v>154.35</v>
+        <v>46.17</v>
       </c>
       <c r="I19" t="n">
-        <v>4.99</v>
+        <v>3.06</v>
       </c>
       <c r="J19" t="n">
-        <v>9.94</v>
+        <v>12.6</v>
       </c>
       <c r="K19" t="n">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="L19" t="n">
         <v>98</v>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>36.34</v>
+        <v>35.24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>300706</t>
+          <t>300903</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>阿石创</t>
+          <t>科翔股份</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.31</v>
+        <v>34.4</v>
       </c>
       <c r="F20" t="n">
-        <v>37.12</v>
+        <v>34.23</v>
       </c>
       <c r="G20" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="H20" t="n">
-        <v>36.01</v>
+        <v>33.2</v>
       </c>
       <c r="I20" t="n">
-        <v>4.98</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
-        <v>12.06</v>
+        <v>7.12</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="L20" t="n">
         <v>98</v>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>19.95</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>002348</t>
+          <t>000420</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,46 +1544,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>高乐股份</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.27</v>
+        <v>5.06</v>
       </c>
       <c r="F21" t="n">
-        <v>9.220000000000001</v>
+        <v>5.03</v>
       </c>
       <c r="G21" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="H21" t="n">
-        <v>8.94</v>
+        <v>4.88</v>
       </c>
       <c r="I21" t="n">
-        <v>4.63</v>
+        <v>4.12</v>
       </c>
       <c r="J21" t="n">
-        <v>5.68</v>
+        <v>6.43</v>
       </c>
       <c r="K21" t="n">
-        <v>5.16</v>
+        <v>2.71</v>
       </c>
       <c r="L21" t="n">
         <v>98</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>19.03</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>603687</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,29 +1598,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>光韵达</t>
+          <t>大胜达</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12.95</v>
+        <v>18.05</v>
       </c>
       <c r="F22" t="n">
-        <v>12.89</v>
+        <v>17.96</v>
       </c>
       <c r="G22" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="H22" t="n">
-        <v>12.5</v>
+        <v>17.42</v>
       </c>
       <c r="I22" t="n">
-        <v>5.46</v>
+        <v>3.97</v>
       </c>
       <c r="J22" t="n">
-        <v>8.41</v>
+        <v>14.84</v>
       </c>
       <c r="K22" t="n">
-        <v>3.57</v>
+        <v>1.84</v>
       </c>
       <c r="L22" t="n">
         <v>98</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>18.82</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>301517</t>
+          <t>002348</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1652,29 +1652,29 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>陕西华达</t>
+          <t>高乐股份</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>59.08</v>
+        <v>9.27</v>
       </c>
       <c r="F23" t="n">
-        <v>58.78</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
-        <v>57.02</v>
+        <v>8.94</v>
       </c>
       <c r="I23" t="n">
-        <v>5.48</v>
+        <v>4.63</v>
       </c>
       <c r="J23" t="n">
-        <v>10.3</v>
+        <v>5.68</v>
       </c>
       <c r="K23" t="n">
-        <v>6.41</v>
+        <v>5.16</v>
       </c>
       <c r="L23" t="n">
         <v>98</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>24.01</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>002980</t>
+          <t>301306</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1706,29 +1706,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>西测测试</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>55.76</v>
+        <v>159.92</v>
       </c>
       <c r="F24" t="n">
-        <v>55.48</v>
+        <v>159.12</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="n">
-        <v>53.82</v>
+        <v>154.35</v>
       </c>
       <c r="I24" t="n">
-        <v>5.49</v>
+        <v>4.99</v>
       </c>
       <c r="J24" t="n">
-        <v>12.9</v>
+        <v>9.94</v>
       </c>
       <c r="K24" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="L24" t="n">
         <v>98</v>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>28.15</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>301362</t>
+          <t>002897</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,29 +1760,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>民爆光电</t>
+          <t>意华股份</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>133</v>
+        <v>66.78</v>
       </c>
       <c r="F25" t="n">
-        <v>132.34</v>
+        <v>66.45</v>
       </c>
       <c r="G25" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="H25" t="n">
-        <v>128.37</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>5.56</v>
+        <v>3.36</v>
       </c>
       <c r="J25" t="n">
-        <v>19.8</v>
+        <v>6.37</v>
       </c>
       <c r="K25" t="n">
-        <v>3.19</v>
+        <v>1.97</v>
       </c>
       <c r="L25" t="n">
         <v>98</v>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>31.1</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>300042</t>
+          <t>300077</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1814,29 +1814,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>国民技术</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>47.84</v>
+        <v>21.58</v>
       </c>
       <c r="F26" t="n">
-        <v>47.6</v>
+        <v>21.47</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="H26" t="n">
-        <v>46.17</v>
+        <v>20.83</v>
       </c>
       <c r="I26" t="n">
-        <v>3.06</v>
+        <v>4.35</v>
       </c>
       <c r="J26" t="n">
-        <v>12.6</v>
+        <v>10.43</v>
       </c>
       <c r="K26" t="n">
-        <v>2.14</v>
+        <v>3.96</v>
       </c>
       <c r="L26" t="n">
         <v>98</v>
@@ -1847,13 +1847,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>47.58</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>301282</t>
+          <t>603757</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,29 +1868,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>金禄电子</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>38</v>
+        <v>51.34</v>
       </c>
       <c r="F27" t="n">
-        <v>37.81</v>
+        <v>51.08</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="H27" t="n">
-        <v>36.68</v>
+        <v>49.55</v>
       </c>
       <c r="I27" t="n">
-        <v>3.32</v>
+        <v>4.26</v>
       </c>
       <c r="J27" t="n">
-        <v>12.38</v>
+        <v>10.31</v>
       </c>
       <c r="K27" t="n">
-        <v>1.97</v>
+        <v>2.43</v>
       </c>
       <c r="L27" t="n">
         <v>98</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>21.7</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="28">
@@ -1947,7 +1947,7 @@
         <v>1.31</v>
       </c>
       <c r="L28" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>28.45</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002150</t>
+          <t>002980</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>正泰电源</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30.75</v>
+        <v>55.76</v>
       </c>
       <c r="F29" t="n">
-        <v>30.6</v>
+        <v>55.48</v>
       </c>
       <c r="G29" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H29" t="n">
-        <v>29.68</v>
+        <v>53.82</v>
       </c>
       <c r="I29" t="n">
-        <v>3.19</v>
+        <v>5.49</v>
       </c>
       <c r="J29" t="n">
-        <v>6.21</v>
+        <v>12.9</v>
       </c>
       <c r="K29" t="n">
-        <v>1.92</v>
+        <v>1.34</v>
       </c>
       <c r="L29" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>27.07</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>002246</t>
+          <t>301099</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,32 +2030,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>北化股份</t>
+          <t>雅创电子</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>24.1</v>
+        <v>52.7</v>
       </c>
       <c r="F30" t="n">
-        <v>23.98</v>
+        <v>52.44</v>
       </c>
       <c r="G30" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="H30" t="n">
-        <v>23.26</v>
+        <v>50.87</v>
       </c>
       <c r="I30" t="n">
-        <v>3.17</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.95</v>
+        <v>12.12</v>
       </c>
       <c r="K30" t="n">
-        <v>1.67</v>
+        <v>2.61</v>
       </c>
       <c r="L30" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>21.05</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>002897</t>
+          <t>300227</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>意华股份</t>
+          <t>光韵达</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>66.78</v>
+        <v>12.95</v>
       </c>
       <c r="F31" t="n">
-        <v>66.45</v>
+        <v>12.89</v>
       </c>
       <c r="G31" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="H31" t="n">
-        <v>64.45999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3.36</v>
+        <v>5.46</v>
       </c>
       <c r="J31" t="n">
-        <v>6.37</v>
+        <v>8.41</v>
       </c>
       <c r="K31" t="n">
-        <v>1.97</v>
+        <v>3.57</v>
       </c>
       <c r="L31" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>30.71</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>300903</t>
+          <t>605289</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2138,32 +2138,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>科翔股份</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>34.4</v>
+        <v>112.9</v>
       </c>
       <c r="F32" t="n">
-        <v>34.23</v>
+        <v>112.34</v>
       </c>
       <c r="G32" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="H32" t="n">
-        <v>33.2</v>
+        <v>108.97</v>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>3.19</v>
       </c>
       <c r="J32" t="n">
-        <v>7.12</v>
+        <v>5.03</v>
       </c>
       <c r="K32" t="n">
-        <v>2.53</v>
+        <v>1.68</v>
       </c>
       <c r="L32" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>32.11</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>603687</t>
+          <t>300632</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,32 +2192,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>大胜达</t>
+          <t>光莆股份</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>18.05</v>
+        <v>16.89</v>
       </c>
       <c r="F33" t="n">
-        <v>17.96</v>
+        <v>16.81</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="H33" t="n">
-        <v>17.42</v>
+        <v>16.31</v>
       </c>
       <c r="I33" t="n">
-        <v>3.97</v>
+        <v>6.43</v>
       </c>
       <c r="J33" t="n">
-        <v>14.84</v>
+        <v>16.15</v>
       </c>
       <c r="K33" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="L33" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>56.5</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>000420</t>
+          <t>300485</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>赛升药业</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.06</v>
+        <v>11.78</v>
       </c>
       <c r="F34" t="n">
-        <v>5.03</v>
+        <v>11.72</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="n">
-        <v>4.88</v>
+        <v>11.37</v>
       </c>
       <c r="I34" t="n">
-        <v>4.12</v>
+        <v>3.24</v>
       </c>
       <c r="J34" t="n">
-        <v>6.43</v>
+        <v>13.52</v>
       </c>
       <c r="K34" t="n">
-        <v>2.71</v>
+        <v>3.34</v>
       </c>
       <c r="L34" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2279,13 +2279,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>31.63</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>300077</t>
+          <t>300706</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2300,32 +2300,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>国民技术</t>
+          <t>阿石创</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>21.58</v>
+        <v>37.31</v>
       </c>
       <c r="F35" t="n">
-        <v>21.47</v>
+        <v>37.12</v>
       </c>
       <c r="G35" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="H35" t="n">
-        <v>20.83</v>
+        <v>36.01</v>
       </c>
       <c r="I35" t="n">
-        <v>4.35</v>
+        <v>4.98</v>
       </c>
       <c r="J35" t="n">
-        <v>10.43</v>
+        <v>12.06</v>
       </c>
       <c r="K35" t="n">
-        <v>3.96</v>
+        <v>2.7</v>
       </c>
       <c r="L35" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>51.35</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>603757</t>
+          <t>301282</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>大元泵业</t>
+          <t>金禄电子</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>51.34</v>
+        <v>38</v>
       </c>
       <c r="F36" t="n">
-        <v>51.08</v>
+        <v>37.81</v>
       </c>
       <c r="G36" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="H36" t="n">
-        <v>49.55</v>
+        <v>36.68</v>
       </c>
       <c r="I36" t="n">
-        <v>4.26</v>
+        <v>3.32</v>
       </c>
       <c r="J36" t="n">
-        <v>10.31</v>
+        <v>12.38</v>
       </c>
       <c r="K36" t="n">
-        <v>2.43</v>
+        <v>1.97</v>
       </c>
       <c r="L36" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>38.67</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>300485</t>
+          <t>301307</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2408,32 +2408,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>赛升药业</t>
+          <t>美利信</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11.78</v>
+        <v>43.2</v>
       </c>
       <c r="F37" t="n">
-        <v>11.72</v>
+        <v>42.98</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="H37" t="n">
-        <v>11.37</v>
+        <v>41.69</v>
       </c>
       <c r="I37" t="n">
-        <v>3.24</v>
+        <v>6.4</v>
       </c>
       <c r="J37" t="n">
-        <v>13.52</v>
+        <v>9.77</v>
       </c>
       <c r="K37" t="n">
-        <v>3.34</v>
+        <v>2.97</v>
       </c>
       <c r="L37" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>17.97</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>605289</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2462,32 +2462,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>罗曼股份</t>
+          <t>创维数字</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112.9</v>
+        <v>11.89</v>
       </c>
       <c r="F38" t="n">
-        <v>112.34</v>
+        <v>11.83</v>
       </c>
       <c r="G38" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
-        <v>108.97</v>
+        <v>11.48</v>
       </c>
       <c r="I38" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="J38" t="n">
-        <v>5.03</v>
+        <v>2.44</v>
       </c>
       <c r="K38" t="n">
-        <v>1.68</v>
+        <v>4.4</v>
       </c>
       <c r="L38" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>24.42</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>300975</t>
+          <t>300938</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,32 +2516,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>商络电子</t>
+          <t>信测标准</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>20.66</v>
+        <v>40.62</v>
       </c>
       <c r="F39" t="n">
-        <v>20.56</v>
+        <v>40.42</v>
       </c>
       <c r="G39" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="H39" t="n">
-        <v>19.94</v>
+        <v>39.21</v>
       </c>
       <c r="I39" t="n">
-        <v>3.04</v>
+        <v>5.92</v>
       </c>
       <c r="J39" t="n">
-        <v>10.58</v>
+        <v>4.96</v>
       </c>
       <c r="K39" t="n">
-        <v>2.06</v>
+        <v>3.22</v>
       </c>
       <c r="L39" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>43.28</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>002246</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>创维数字</t>
+          <t>北化股份</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11.89</v>
+        <v>24.1</v>
       </c>
       <c r="F40" t="n">
-        <v>11.83</v>
+        <v>23.98</v>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="H40" t="n">
-        <v>11.48</v>
+        <v>23.26</v>
       </c>
       <c r="I40" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="J40" t="n">
-        <v>2.44</v>
+        <v>3.95</v>
       </c>
       <c r="K40" t="n">
-        <v>4.4</v>
+        <v>1.67</v>
       </c>
       <c r="L40" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>12.97</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>000949</t>
+          <t>300121</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2624,32 +2624,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新乡化纤</t>
+          <t>阳谷华泰</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7.64</v>
+        <v>12.58</v>
       </c>
       <c r="F41" t="n">
-        <v>7.6</v>
+        <v>12.52</v>
       </c>
       <c r="G41" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="H41" t="n">
-        <v>7.37</v>
+        <v>12.14</v>
       </c>
       <c r="I41" t="n">
-        <v>3.95</v>
+        <v>3.71</v>
       </c>
       <c r="J41" t="n">
-        <v>3.78</v>
+        <v>4.52</v>
       </c>
       <c r="K41" t="n">
-        <v>1.85</v>
+        <v>4.91</v>
       </c>
       <c r="L41" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>18.91</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="42">
@@ -2703,7 +2703,7 @@
         <v>2.67</v>
       </c>
       <c r="L42" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>16.81</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>603507</t>
+          <t>603203</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>振江股份</t>
+          <t>快克智能</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>44.01</v>
+        <v>44.04</v>
       </c>
       <c r="F43" t="n">
-        <v>43.79</v>
+        <v>43.82</v>
       </c>
       <c r="G43" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="H43" t="n">
-        <v>42.48</v>
+        <v>42.51</v>
       </c>
       <c r="I43" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="J43" t="n">
-        <v>6.04</v>
+        <v>3.34</v>
       </c>
       <c r="K43" t="n">
-        <v>1.64</v>
+        <v>3.21</v>
       </c>
       <c r="L43" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>19.12</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>603203</t>
+          <t>000949</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>快克智能</t>
+          <t>新乡化纤</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>44.04</v>
+        <v>7.64</v>
       </c>
       <c r="F44" t="n">
-        <v>43.82</v>
+        <v>7.6</v>
       </c>
       <c r="G44" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="H44" t="n">
-        <v>42.51</v>
+        <v>7.37</v>
       </c>
       <c r="I44" t="n">
-        <v>4.61</v>
+        <v>3.95</v>
       </c>
       <c r="J44" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="K44" t="n">
-        <v>3.21</v>
+        <v>1.85</v>
       </c>
       <c r="L44" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>14.3</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>300121</t>
+          <t>603507</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2840,32 +2840,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>阳谷华泰</t>
+          <t>振江股份</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12.58</v>
+        <v>44.01</v>
       </c>
       <c r="F45" t="n">
-        <v>12.52</v>
+        <v>43.79</v>
       </c>
       <c r="G45" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="H45" t="n">
-        <v>12.14</v>
+        <v>42.48</v>
       </c>
       <c r="I45" t="n">
-        <v>3.71</v>
+        <v>4.76</v>
       </c>
       <c r="J45" t="n">
-        <v>4.52</v>
+        <v>6.04</v>
       </c>
       <c r="K45" t="n">
-        <v>4.91</v>
+        <v>1.64</v>
       </c>
       <c r="L45" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>9.84</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>688275</t>
+          <t>688135</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2894,32 +2894,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>万润新能</t>
+          <t>利扬芯片</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>113.4</v>
+        <v>28.63</v>
       </c>
       <c r="F46" t="n">
-        <v>112.83</v>
+        <v>28.49</v>
       </c>
       <c r="G46" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="H46" t="n">
-        <v>109.45</v>
+        <v>27.64</v>
       </c>
       <c r="I46" t="n">
-        <v>4.37</v>
+        <v>3.81</v>
       </c>
       <c r="J46" t="n">
-        <v>3.27</v>
+        <v>4.92</v>
       </c>
       <c r="K46" t="n">
-        <v>1.48</v>
+        <v>3.49</v>
       </c>
       <c r="L46" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>18.45</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>688135</t>
+          <t>688275</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2948,32 +2948,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>利扬芯片</t>
+          <t>万润新能</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>28.63</v>
+        <v>113.4</v>
       </c>
       <c r="F47" t="n">
-        <v>28.49</v>
+        <v>112.83</v>
       </c>
       <c r="G47" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="H47" t="n">
-        <v>27.64</v>
+        <v>109.45</v>
       </c>
       <c r="I47" t="n">
-        <v>3.81</v>
+        <v>4.37</v>
       </c>
       <c r="J47" t="n">
-        <v>4.92</v>
+        <v>3.27</v>
       </c>
       <c r="K47" t="n">
-        <v>3.49</v>
+        <v>1.48</v>
       </c>
       <c r="L47" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>13.14</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="48">
@@ -3027,7 +3027,7 @@
         <v>2.09</v>
       </c>
       <c r="L48" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>15.48</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="49">
@@ -3081,7 +3081,7 @@
         <v>2.27</v>
       </c>
       <c r="L49" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3089,13 +3089,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>14.39</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>301571</t>
+          <t>603297</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>国科天成</t>
+          <t>永新光学</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>69.76000000000001</v>
+        <v>111.75</v>
       </c>
       <c r="F50" t="n">
-        <v>69.41</v>
+        <v>111.19</v>
       </c>
       <c r="G50" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="H50" t="n">
-        <v>67.33</v>
+        <v>107.85</v>
       </c>
       <c r="I50" t="n">
-        <v>3.42</v>
+        <v>4.47</v>
       </c>
       <c r="J50" t="n">
-        <v>4.15</v>
+        <v>2.12</v>
       </c>
       <c r="K50" t="n">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="L50" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>13.7</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>688593</t>
+          <t>301571</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>新相微</t>
+          <t>国科天成</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>32.37</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>32.21</v>
+        <v>69.41</v>
       </c>
       <c r="G51" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="H51" t="n">
-        <v>31.24</v>
+        <v>67.33</v>
       </c>
       <c r="I51" t="n">
-        <v>4.49</v>
+        <v>3.42</v>
       </c>
       <c r="J51" t="n">
-        <v>3.01</v>
+        <v>4.15</v>
       </c>
       <c r="K51" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="L51" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>12.44</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>301323</t>
+          <t>688593</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>新莱福</t>
+          <t>新相微</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>66</v>
+        <v>32.37</v>
       </c>
       <c r="F52" t="n">
-        <v>65.67</v>
+        <v>32.21</v>
       </c>
       <c r="G52" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H52" t="n">
-        <v>63.7</v>
+        <v>31.24</v>
       </c>
       <c r="I52" t="n">
-        <v>5.13</v>
+        <v>4.49</v>
       </c>
       <c r="J52" t="n">
-        <v>6.73</v>
+        <v>3.01</v>
       </c>
       <c r="K52" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="L52" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3251,13 +3251,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>12.06</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>300191</t>
+          <t>002838</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3272,32 +3272,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>潜能恒信</t>
+          <t>道恩股份</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>38.01</v>
+        <v>27.1</v>
       </c>
       <c r="F53" t="n">
-        <v>37.82</v>
+        <v>26.96</v>
       </c>
       <c r="G53" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="H53" t="n">
-        <v>36.69</v>
+        <v>26.15</v>
       </c>
       <c r="I53" t="n">
-        <v>3.26</v>
+        <v>4.23</v>
       </c>
       <c r="J53" t="n">
-        <v>4.84</v>
+        <v>1.49</v>
       </c>
       <c r="K53" t="n">
-        <v>1.1</v>
+        <v>4.49</v>
       </c>
       <c r="L53" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>16.12</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>603297</t>
+          <t>301323</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3326,32 +3326,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>永新光学</t>
+          <t>新莱福</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>111.75</v>
+        <v>66</v>
       </c>
       <c r="F54" t="n">
-        <v>111.19</v>
+        <v>65.67</v>
       </c>
       <c r="G54" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H54" t="n">
-        <v>107.85</v>
+        <v>63.7</v>
       </c>
       <c r="I54" t="n">
-        <v>4.47</v>
+        <v>5.13</v>
       </c>
       <c r="J54" t="n">
-        <v>2.12</v>
+        <v>6.73</v>
       </c>
       <c r="K54" t="n">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="L54" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>10.56</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="55">
@@ -3405,7 +3405,7 @@
         <v>3.23</v>
       </c>
       <c r="L55" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>10.06</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>688530</t>
+          <t>600769</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>欧莱新材</t>
+          <t>祥龙电业</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>32.57</v>
+        <v>14.83</v>
       </c>
       <c r="F56" t="n">
-        <v>32.41</v>
+        <v>14.76</v>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="H56" t="n">
-        <v>31.44</v>
+        <v>14.32</v>
       </c>
       <c r="I56" t="n">
-        <v>3.96</v>
+        <v>6.92</v>
       </c>
       <c r="J56" t="n">
-        <v>13.44</v>
+        <v>4.4</v>
       </c>
       <c r="K56" t="n">
-        <v>2.53</v>
+        <v>3.25</v>
       </c>
       <c r="L56" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>11.7</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>600769</t>
+          <t>688530</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>祥龙电业</t>
+          <t>欧莱新材</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>14.83</v>
+        <v>32.57</v>
       </c>
       <c r="F57" t="n">
-        <v>14.76</v>
+        <v>32.41</v>
       </c>
       <c r="G57" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="H57" t="n">
-        <v>14.32</v>
+        <v>31.44</v>
       </c>
       <c r="I57" t="n">
-        <v>6.92</v>
+        <v>3.96</v>
       </c>
       <c r="J57" t="n">
-        <v>4.4</v>
+        <v>13.44</v>
       </c>
       <c r="K57" t="n">
-        <v>3.25</v>
+        <v>2.53</v>
       </c>
       <c r="L57" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3521,13 +3521,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>9.710000000000001</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>002838</t>
+          <t>920438</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>道恩股份</t>
+          <t>戈碧迦</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>27.1</v>
+        <v>39.75</v>
       </c>
       <c r="F58" t="n">
-        <v>26.96</v>
+        <v>39.55</v>
       </c>
       <c r="G58" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="H58" t="n">
-        <v>26.15</v>
+        <v>38.36</v>
       </c>
       <c r="I58" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="J58" t="n">
-        <v>1.49</v>
+        <v>3.28</v>
       </c>
       <c r="K58" t="n">
-        <v>4.49</v>
+        <v>3.68</v>
       </c>
       <c r="L58" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>6.77</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>002993</t>
+          <t>300191</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>奥海科技</t>
+          <t>潜能恒信</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50.34</v>
+        <v>38.01</v>
       </c>
       <c r="F59" t="n">
-        <v>50.09</v>
+        <v>37.82</v>
       </c>
       <c r="G59" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="H59" t="n">
-        <v>48.59</v>
+        <v>36.69</v>
       </c>
       <c r="I59" t="n">
-        <v>3.79</v>
+        <v>3.26</v>
       </c>
       <c r="J59" t="n">
-        <v>2.31</v>
+        <v>4.84</v>
       </c>
       <c r="K59" t="n">
-        <v>2.21</v>
+        <v>1.1</v>
       </c>
       <c r="L59" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>10.99</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>920438</t>
+          <t>301387</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3650,32 +3650,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>戈碧迦</t>
+          <t>光大同创</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>39.75</v>
+        <v>63.37</v>
       </c>
       <c r="F60" t="n">
-        <v>39.55</v>
+        <v>63.05</v>
       </c>
       <c r="G60" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="H60" t="n">
-        <v>38.36</v>
+        <v>61.16</v>
       </c>
       <c r="I60" t="n">
-        <v>4.33</v>
+        <v>6.04</v>
       </c>
       <c r="J60" t="n">
-        <v>3.28</v>
+        <v>7.49</v>
       </c>
       <c r="K60" t="n">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="L60" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>7.35</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>600791</t>
+          <t>002993</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>京能置业</t>
+          <t>奥海科技</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>13.2</v>
+        <v>50.34</v>
       </c>
       <c r="F61" t="n">
-        <v>13.13</v>
+        <v>50.09</v>
       </c>
       <c r="G61" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H61" t="n">
-        <v>12.74</v>
+        <v>48.59</v>
       </c>
       <c r="I61" t="n">
-        <v>5.18</v>
+        <v>3.79</v>
       </c>
       <c r="J61" t="n">
-        <v>5.21</v>
+        <v>2.31</v>
       </c>
       <c r="K61" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="L61" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3737,13 +3737,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>12.22</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>301387</t>
+          <t>603226</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3758,32 +3758,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>光大同创</t>
+          <t>菲林格尔</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>63.37</v>
+        <v>39.06</v>
       </c>
       <c r="F62" t="n">
-        <v>63.05</v>
+        <v>38.86</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H62" t="n">
-        <v>61.16</v>
+        <v>37.69</v>
       </c>
       <c r="I62" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="J62" t="n">
-        <v>7.49</v>
+        <v>1.63</v>
       </c>
       <c r="K62" t="n">
-        <v>3.32</v>
+        <v>2.76</v>
       </c>
       <c r="L62" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>7.88</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>603226</t>
+          <t>600791</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3812,32 +3812,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>菲林格尔</t>
+          <t>京能置业</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>39.06</v>
+        <v>13.2</v>
       </c>
       <c r="F63" t="n">
-        <v>38.86</v>
+        <v>13.13</v>
       </c>
       <c r="G63" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H63" t="n">
-        <v>37.69</v>
+        <v>12.74</v>
       </c>
       <c r="I63" t="n">
-        <v>6.05</v>
+        <v>5.18</v>
       </c>
       <c r="J63" t="n">
-        <v>1.63</v>
+        <v>5.21</v>
       </c>
       <c r="K63" t="n">
-        <v>2.76</v>
+        <v>1.57</v>
       </c>
       <c r="L63" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>8.99</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>603353</t>
+          <t>301326</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t>捷邦科技</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42.92</v>
+        <v>151.51</v>
       </c>
       <c r="F64" t="n">
-        <v>42.71</v>
+        <v>150.75</v>
       </c>
       <c r="G64" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H64" t="n">
-        <v>41.43</v>
+        <v>146.23</v>
       </c>
       <c r="I64" t="n">
-        <v>4.73</v>
+        <v>3.62</v>
       </c>
       <c r="J64" t="n">
-        <v>4.44</v>
+        <v>2.31</v>
       </c>
       <c r="K64" t="n">
-        <v>1.29</v>
+        <v>2.16</v>
       </c>
       <c r="L64" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>12.73</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>603115</t>
+          <t>300389</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3920,32 +3920,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>海星股份</t>
+          <t>艾比森</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>46.02</v>
+        <v>18.87</v>
       </c>
       <c r="F65" t="n">
-        <v>45.79</v>
+        <v>18.78</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H65" t="n">
-        <v>44.42</v>
+        <v>18.22</v>
       </c>
       <c r="I65" t="n">
-        <v>4.12</v>
+        <v>4.95</v>
       </c>
       <c r="J65" t="n">
-        <v>2.99</v>
+        <v>6.46</v>
       </c>
       <c r="K65" t="n">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="L65" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>12.91</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>301326</t>
+          <t>603353</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3974,32 +3974,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>捷邦科技</t>
+          <t>和顺石油</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>151.51</v>
+        <v>42.92</v>
       </c>
       <c r="F66" t="n">
-        <v>150.75</v>
+        <v>42.71</v>
       </c>
       <c r="G66" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H66" t="n">
-        <v>146.23</v>
+        <v>41.43</v>
       </c>
       <c r="I66" t="n">
-        <v>3.62</v>
+        <v>4.73</v>
       </c>
       <c r="J66" t="n">
-        <v>2.31</v>
+        <v>4.44</v>
       </c>
       <c r="K66" t="n">
-        <v>2.16</v>
+        <v>1.29</v>
       </c>
       <c r="L66" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>10.04</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>300389</t>
+          <t>603115</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4028,32 +4028,32 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>艾比森</t>
+          <t>海星股份</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>18.87</v>
+        <v>46.02</v>
       </c>
       <c r="F67" t="n">
-        <v>18.78</v>
+        <v>45.79</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
-        <v>18.22</v>
+        <v>44.42</v>
       </c>
       <c r="I67" t="n">
-        <v>4.95</v>
+        <v>4.12</v>
       </c>
       <c r="J67" t="n">
-        <v>6.46</v>
+        <v>2.99</v>
       </c>
       <c r="K67" t="n">
-        <v>1.9</v>
+        <v>1.19</v>
       </c>
       <c r="L67" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>10.58</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="68">
@@ -4107,7 +4107,7 @@
         <v>1.91</v>
       </c>
       <c r="L68" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>10.13</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>002650</t>
+          <t>603162</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ST加加</t>
+          <t>海通发展</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.68</v>
+        <v>14.79</v>
       </c>
       <c r="F69" t="n">
-        <v>7.64</v>
+        <v>14.72</v>
       </c>
       <c r="G69" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="H69" t="n">
-        <v>7.41</v>
+        <v>14.28</v>
       </c>
       <c r="I69" t="n">
-        <v>4.77</v>
+        <v>3.43</v>
       </c>
       <c r="J69" t="n">
-        <v>1.72</v>
+        <v>5.19</v>
       </c>
       <c r="K69" t="n">
-        <v>3.53</v>
+        <v>2.31</v>
       </c>
       <c r="L69" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>5.83</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>603162</t>
+          <t>688376</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4190,32 +4190,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>海通发展</t>
+          <t>美埃科技</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>14.79</v>
+        <v>68.81</v>
       </c>
       <c r="F70" t="n">
-        <v>14.72</v>
+        <v>68.47</v>
       </c>
       <c r="G70" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="H70" t="n">
-        <v>14.28</v>
+        <v>66.42</v>
       </c>
       <c r="I70" t="n">
-        <v>3.43</v>
+        <v>4.51</v>
       </c>
       <c r="J70" t="n">
-        <v>5.19</v>
+        <v>2.1</v>
       </c>
       <c r="K70" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="L70" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>8.57</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301093</t>
+          <t>300756</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>华兰股份</t>
+          <t>金马游乐</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>88.02</v>
+        <v>45.55</v>
       </c>
       <c r="F71" t="n">
-        <v>87.58</v>
+        <v>45.32</v>
       </c>
       <c r="G71" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="H71" t="n">
-        <v>84.95</v>
+        <v>43.96</v>
       </c>
       <c r="I71" t="n">
-        <v>4.62</v>
+        <v>6.05</v>
       </c>
       <c r="J71" t="n">
-        <v>1.89</v>
+        <v>3.04</v>
       </c>
       <c r="K71" t="n">
-        <v>1.67</v>
+        <v>2.59</v>
       </c>
       <c r="L71" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>10.22</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>688376</t>
+          <t>301093</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4298,32 +4298,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>美埃科技</t>
+          <t>华兰股份</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>68.81</v>
+        <v>88.02</v>
       </c>
       <c r="F72" t="n">
-        <v>68.47</v>
+        <v>87.58</v>
       </c>
       <c r="G72" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="H72" t="n">
-        <v>66.42</v>
+        <v>84.95</v>
       </c>
       <c r="I72" t="n">
-        <v>4.51</v>
+        <v>4.62</v>
       </c>
       <c r="J72" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="K72" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="L72" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -4331,13 +4331,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>7.86</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>300756</t>
+          <t>688079</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4352,32 +4352,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>金马游乐</t>
+          <t>美迪凯</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>45.55</v>
+        <v>14.94</v>
       </c>
       <c r="F73" t="n">
-        <v>45.32</v>
+        <v>14.87</v>
       </c>
       <c r="G73" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="H73" t="n">
-        <v>43.96</v>
+        <v>14.42</v>
       </c>
       <c r="I73" t="n">
-        <v>6.05</v>
+        <v>4.62</v>
       </c>
       <c r="J73" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="K73" t="n">
-        <v>2.59</v>
+        <v>2.22</v>
       </c>
       <c r="L73" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7.13</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>605100</t>
+          <t>002782</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4406,32 +4406,32 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>华丰股份</t>
+          <t>可立克</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>45.55</v>
+        <v>22.08</v>
       </c>
       <c r="F74" t="n">
-        <v>45.32</v>
+        <v>21.97</v>
       </c>
       <c r="G74" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="n">
-        <v>43.96</v>
+        <v>21.31</v>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="J74" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="K74" t="n">
-        <v>3.22</v>
+        <v>1.92</v>
       </c>
       <c r="L74" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>5.59</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>688079</t>
+          <t>300137</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>美迪凯</t>
+          <t>先河环保</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>14.94</v>
+        <v>13.21</v>
       </c>
       <c r="F75" t="n">
-        <v>14.87</v>
+        <v>13.14</v>
       </c>
       <c r="G75" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="n">
-        <v>14.42</v>
+        <v>12.75</v>
       </c>
       <c r="I75" t="n">
-        <v>4.62</v>
+        <v>3.69</v>
       </c>
       <c r="J75" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="K75" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="L75" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>8.06</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>002782</t>
+          <t>301235</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4514,32 +4514,32 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>可立克</t>
+          <t>华康洁净</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>22.08</v>
+        <v>50.35</v>
       </c>
       <c r="F76" t="n">
-        <v>21.97</v>
+        <v>50.1</v>
       </c>
       <c r="G76" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="H76" t="n">
-        <v>21.31</v>
+        <v>48.6</v>
       </c>
       <c r="I76" t="n">
-        <v>3.27</v>
+        <v>4.07</v>
       </c>
       <c r="J76" t="n">
-        <v>2.01</v>
+        <v>5.78</v>
       </c>
       <c r="K76" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="L76" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>8.58</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>688330</t>
+          <t>300559</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4568,32 +4568,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>宏力达</t>
+          <t>佳发教育</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>50.83</v>
+        <v>14.98</v>
       </c>
       <c r="F77" t="n">
-        <v>50.58</v>
+        <v>14.91</v>
       </c>
       <c r="G77" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H77" t="n">
-        <v>49.06</v>
+        <v>14.46</v>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>5.27</v>
       </c>
       <c r="J77" t="n">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="K77" t="n">
-        <v>2.77</v>
+        <v>1.7</v>
       </c>
       <c r="L77" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>6.11</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>300137</t>
+          <t>688383</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>先河环保</t>
+          <t>新益昌</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>13.21</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>13.14</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="H78" t="n">
-        <v>12.75</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>3.69</v>
+        <v>6.38</v>
       </c>
       <c r="J78" t="n">
-        <v>3.22</v>
+        <v>2.25</v>
       </c>
       <c r="K78" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="L78" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>9.01</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>301235</t>
+          <t>002937</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4676,32 +4676,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>华康洁净</t>
+          <t>兴瑞科技</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>50.35</v>
+        <v>29.77</v>
       </c>
       <c r="F79" t="n">
-        <v>50.1</v>
+        <v>29.62</v>
       </c>
       <c r="G79" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="H79" t="n">
-        <v>48.6</v>
+        <v>28.73</v>
       </c>
       <c r="I79" t="n">
-        <v>4.07</v>
+        <v>5.64</v>
       </c>
       <c r="J79" t="n">
-        <v>5.78</v>
+        <v>2.14</v>
       </c>
       <c r="K79" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="L79" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>8.4</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>300559</t>
+          <t>601515</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4730,32 +4730,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>佳发教育</t>
+          <t>衢州东峰</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>14.98</v>
+        <v>4.71</v>
       </c>
       <c r="F80" t="n">
-        <v>14.91</v>
+        <v>4.69</v>
       </c>
       <c r="G80" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="H80" t="n">
-        <v>14.46</v>
+        <v>4.55</v>
       </c>
       <c r="I80" t="n">
-        <v>5.27</v>
+        <v>3.29</v>
       </c>
       <c r="J80" t="n">
-        <v>4.57</v>
+        <v>2.25</v>
       </c>
       <c r="K80" t="n">
-        <v>1.7</v>
+        <v>0.77</v>
       </c>
       <c r="L80" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -4763,493 +4763,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>8.44</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>688383</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>新益昌</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>94.65000000000001</v>
-      </c>
-      <c r="F81" t="n">
-        <v>94.18000000000001</v>
-      </c>
-      <c r="G81" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H81" t="n">
-        <v>91.34999999999999</v>
-      </c>
-      <c r="I81" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="L81" t="n">
-        <v>50</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>8.58</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>300696</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>爱乐达</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="F82" t="n">
-        <v>29.05</v>
-      </c>
-      <c r="G82" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H82" t="n">
-        <v>28.18</v>
-      </c>
-      <c r="I82" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="K82" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="L82" t="n">
-        <v>50</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N82" t="n">
-        <v>5.92</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>002937</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>兴瑞科技</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="F83" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="G83" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H83" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="I83" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="J83" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="L83" t="n">
-        <v>48</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N83" t="n">
-        <v>7.38</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>301369</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>联动科技</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>143.23</v>
-      </c>
-      <c r="F84" t="n">
-        <v>142.51</v>
-      </c>
-      <c r="G84" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H84" t="n">
-        <v>138.23</v>
-      </c>
-      <c r="I84" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="J84" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="K84" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="L84" t="n">
-        <v>48</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N84" t="n">
-        <v>5.63</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>688667</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>菱电电控</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>114</v>
-      </c>
-      <c r="F85" t="n">
-        <v>113.43</v>
-      </c>
-      <c r="G85" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H85" t="n">
-        <v>110.03</v>
-      </c>
-      <c r="I85" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="J85" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="L85" t="n">
-        <v>45</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N85" t="n">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>301133</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>金钟股份</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="F86" t="n">
-        <v>43.58</v>
-      </c>
-      <c r="G86" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H86" t="n">
-        <v>42.27</v>
-      </c>
-      <c r="I86" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="J86" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L86" t="n">
-        <v>40</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N86" t="n">
-        <v>6.47</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>601515</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>衢州东峰</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="F87" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="G87" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H87" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="I87" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L87" t="n">
-        <v>39</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N87" t="n">
-        <v>8.06</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>000908</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>ST景峰</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="F88" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="G88" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H88" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="I88" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="J88" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="L88" t="n">
-        <v>35</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N88" t="n">
-        <v>5.78</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>300819</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>聚杰微纤</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>43.97</v>
-      </c>
-      <c r="F89" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="G89" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H89" t="n">
-        <v>42.44</v>
-      </c>
-      <c r="I89" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L89" t="n">
-        <v>34</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N89" t="n">
-        <v>5.73</v>
+        <v>5.97</v>
       </c>
     </row>
   </sheetData>

--- a/Liang_61_Report.xlsx
+++ b/Liang_61_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300790</t>
+          <t>605060</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,46 +518,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>宇瞳光学</t>
+          <t>联德股份</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30.13</v>
+        <v>57.62</v>
       </c>
       <c r="F2" t="n">
-        <v>29.98</v>
+        <v>57.33</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8</v>
+        <v>9.9</v>
       </c>
       <c r="H2" t="n">
-        <v>29.08</v>
+        <v>55.61</v>
       </c>
       <c r="I2" t="n">
-        <v>6.02</v>
+        <v>7.38</v>
       </c>
       <c r="J2" t="n">
-        <v>21.49</v>
+        <v>1.22</v>
       </c>
       <c r="K2" t="n">
-        <v>3.52</v>
+        <v>7.78</v>
       </c>
       <c r="L2" t="n">
         <v>98</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>21.11</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>603538</t>
+          <t>003019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,46 +572,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>宸展光电</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45.5</v>
+        <v>34.34</v>
       </c>
       <c r="F3" t="n">
-        <v>45.27</v>
+        <v>34.17</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>24.4</v>
       </c>
       <c r="H3" t="n">
-        <v>43.91</v>
+        <v>33.14</v>
       </c>
       <c r="I3" t="n">
-        <v>5.23</v>
+        <v>7.31</v>
       </c>
       <c r="J3" t="n">
-        <v>45.88</v>
+        <v>2.82</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4</v>
+        <v>25.98</v>
       </c>
       <c r="L3" t="n">
         <v>98</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>43.82</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300303</t>
+          <t>300889</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,46 +626,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>聚飞光电</t>
+          <t>爱克股份</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.23</v>
+        <v>26.84</v>
       </c>
       <c r="F4" t="n">
-        <v>10.18</v>
+        <v>26.71</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>13.2</v>
       </c>
       <c r="H4" t="n">
-        <v>9.869999999999999</v>
+        <v>25.91</v>
       </c>
       <c r="I4" t="n">
-        <v>5.46</v>
+        <v>7.23</v>
       </c>
       <c r="J4" t="n">
-        <v>18.79</v>
+        <v>2.46</v>
       </c>
       <c r="K4" t="n">
-        <v>1.86</v>
+        <v>11.98</v>
       </c>
       <c r="L4" t="n">
         <v>98</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>24.78</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>000795</t>
+          <t>300905</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,32 +680,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>英洛华</t>
+          <t>宝丽迪</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9.6</v>
+        <v>34.17</v>
       </c>
       <c r="F5" t="n">
-        <v>9.550000000000001</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>9.26</v>
+        <v>32.98</v>
       </c>
       <c r="I5" t="n">
-        <v>6.31</v>
+        <v>7.18</v>
       </c>
       <c r="J5" t="n">
-        <v>5.79</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>7.03</v>
+        <v>19.27</v>
       </c>
       <c r="L5" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.32</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>603687</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -734,46 +734,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>大胜达</t>
+          <t>奥浦迈</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18.16</v>
+        <v>51.7</v>
       </c>
       <c r="F6" t="n">
-        <v>18.07</v>
+        <v>51.44</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>11.1</v>
       </c>
       <c r="H6" t="n">
-        <v>17.53</v>
+        <v>49.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4.61</v>
+        <v>7.17</v>
       </c>
       <c r="J6" t="n">
-        <v>20.58</v>
+        <v>0.78</v>
       </c>
       <c r="K6" t="n">
-        <v>1.28</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>19.82</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300042</t>
+          <t>300881</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -788,46 +788,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>盛德鑫泰</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48.1</v>
+        <v>46.87</v>
       </c>
       <c r="F7" t="n">
-        <v>47.86</v>
+        <v>46.64</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>46.42</v>
+        <v>45.24</v>
       </c>
       <c r="I7" t="n">
-        <v>3.62</v>
+        <v>7.11</v>
       </c>
       <c r="J7" t="n">
-        <v>19.98</v>
+        <v>1.65</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7</v>
+        <v>10.54</v>
       </c>
       <c r="L7" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>18.96</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300265</t>
+          <t>600078</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,46 +842,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>通光线缆</t>
+          <t>澄星股份</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20.23</v>
+        <v>12.73</v>
       </c>
       <c r="F8" t="n">
-        <v>20.13</v>
+        <v>12.67</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>13.7</v>
       </c>
       <c r="H8" t="n">
-        <v>19.53</v>
+        <v>12.29</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>7.06</v>
       </c>
       <c r="J8" t="n">
-        <v>21.17</v>
+        <v>2.42</v>
       </c>
       <c r="K8" t="n">
-        <v>1.34</v>
+        <v>12.76</v>
       </c>
       <c r="L8" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>19.58</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688403</t>
+          <t>603088</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -896,46 +896,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>汇成股份</t>
+          <t>宁波精达</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.99</v>
+        <v>13.07</v>
       </c>
       <c r="F9" t="n">
-        <v>15.91</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>5.8</v>
+        <v>11.7</v>
       </c>
       <c r="H9" t="n">
-        <v>15.43</v>
+        <v>12.61</v>
       </c>
       <c r="I9" t="n">
-        <v>6.81</v>
+        <v>6.96</v>
       </c>
       <c r="J9" t="n">
-        <v>9.56</v>
+        <v>2.38</v>
       </c>
       <c r="K9" t="n">
-        <v>2.95</v>
+        <v>10.23</v>
       </c>
       <c r="L9" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>14.06</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300131</t>
+          <t>002283</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -950,46 +950,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>英唐智控</t>
+          <t>天润工业</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12.85</v>
+        <v>10.73</v>
       </c>
       <c r="F10" t="n">
-        <v>12.79</v>
+        <v>10.68</v>
       </c>
       <c r="G10" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>12.41</v>
+        <v>10.36</v>
       </c>
       <c r="I10" t="n">
-        <v>4.64</v>
+        <v>6.77</v>
       </c>
       <c r="J10" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="K10" t="n">
-        <v>1.99</v>
+        <v>5.83</v>
       </c>
       <c r="L10" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>15.53</v>
+        <v>27.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688268</t>
+          <t>603200</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,46 +1004,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>华特气体</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102.1</v>
+        <v>59.89</v>
       </c>
       <c r="F11" t="n">
-        <v>101.59</v>
+        <v>59.59</v>
       </c>
       <c r="G11" t="n">
-        <v>4.6</v>
+        <v>12.1</v>
       </c>
       <c r="H11" t="n">
-        <v>98.54000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="I11" t="n">
-        <v>7.09</v>
+        <v>6.76</v>
       </c>
       <c r="J11" t="n">
-        <v>12.92</v>
+        <v>1.79</v>
       </c>
       <c r="K11" t="n">
-        <v>1.38</v>
+        <v>10.85</v>
       </c>
       <c r="L11" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>16.01</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>603112</t>
+          <t>301500</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1058,32 +1058,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>华翔股份</t>
+          <t>飞南资源</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19.01</v>
+        <v>26.25</v>
       </c>
       <c r="F12" t="n">
-        <v>18.91</v>
+        <v>26.12</v>
       </c>
       <c r="G12" t="n">
-        <v>7.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>18.34</v>
+        <v>25.34</v>
       </c>
       <c r="I12" t="n">
-        <v>7.04</v>
+        <v>6.71</v>
       </c>
       <c r="J12" t="n">
-        <v>6.47</v>
+        <v>6.84</v>
       </c>
       <c r="K12" t="n">
-        <v>5.15</v>
+        <v>7.92</v>
       </c>
       <c r="L12" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>39.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>002655</t>
+          <t>300836</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1112,46 +1112,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>共达电声</t>
+          <t>佰奥智能</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21.16</v>
+        <v>60.25</v>
       </c>
       <c r="F13" t="n">
-        <v>21.05</v>
+        <v>59.95</v>
       </c>
       <c r="G13" t="n">
-        <v>4.2</v>
+        <v>12.3</v>
       </c>
       <c r="H13" t="n">
-        <v>20.42</v>
+        <v>58.15</v>
       </c>
       <c r="I13" t="n">
-        <v>5.85</v>
+        <v>6.64</v>
       </c>
       <c r="J13" t="n">
-        <v>19.52</v>
+        <v>1.46</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6</v>
+        <v>11.17</v>
       </c>
       <c r="L13" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>14.93</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>002708</t>
+          <t>301160</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1166,46 +1166,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>翔楼新材</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.49</v>
+        <v>58.9</v>
       </c>
       <c r="F14" t="n">
-        <v>13.42</v>
+        <v>58.61</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6</v>
+        <v>10.3</v>
       </c>
       <c r="H14" t="n">
-        <v>13.02</v>
+        <v>56.85</v>
       </c>
       <c r="I14" t="n">
-        <v>5.47</v>
+        <v>6.55</v>
       </c>
       <c r="J14" t="n">
-        <v>9.18</v>
+        <v>1.56</v>
       </c>
       <c r="K14" t="n">
-        <v>4.86</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6.37</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>301517</t>
+          <t>600713</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1220,46 +1220,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>陕西华达</t>
+          <t>南京医药</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>59.29</v>
+        <v>5.86</v>
       </c>
       <c r="F15" t="n">
-        <v>58.99</v>
+        <v>5.83</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>57.22</v>
+        <v>5.66</v>
       </c>
       <c r="I15" t="n">
-        <v>5.86</v>
+        <v>6.55</v>
       </c>
       <c r="J15" t="n">
-        <v>13.21</v>
+        <v>1.8</v>
       </c>
       <c r="K15" t="n">
-        <v>4.11</v>
+        <v>7.12</v>
       </c>
       <c r="L15" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.69</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>603158</t>
+          <t>688758</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,46 +1274,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>腾龙股份</t>
+          <t>赛分科技</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.16</v>
+        <v>20.54</v>
       </c>
       <c r="F16" t="n">
-        <v>13.09</v>
+        <v>20.44</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>14.9</v>
       </c>
       <c r="H16" t="n">
-        <v>12.7</v>
+        <v>19.83</v>
       </c>
       <c r="I16" t="n">
-        <v>6.99</v>
+        <v>6.48</v>
       </c>
       <c r="J16" t="n">
-        <v>17.82</v>
+        <v>0.92</v>
       </c>
       <c r="K16" t="n">
-        <v>2.23</v>
+        <v>14.52</v>
       </c>
       <c r="L16" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>11.35</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>603118</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,32 +1328,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>共进股份</t>
+          <t>力诺药包</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14.41</v>
+        <v>25.56</v>
       </c>
       <c r="F17" t="n">
-        <v>14.34</v>
+        <v>25.43</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>13.91</v>
+        <v>24.67</v>
       </c>
       <c r="I17" t="n">
-        <v>3.22</v>
+        <v>6.23</v>
       </c>
       <c r="J17" t="n">
-        <v>12.21</v>
+        <v>4.39</v>
       </c>
       <c r="K17" t="n">
-        <v>1.34</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>13.6</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>600184</t>
+          <t>603773</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1382,46 +1382,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>光电股份</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>19.62</v>
+        <v>41.65</v>
       </c>
       <c r="F18" t="n">
-        <v>19.52</v>
+        <v>41.44</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9</v>
+        <v>21.5</v>
       </c>
       <c r="H18" t="n">
-        <v>18.93</v>
+        <v>40.2</v>
       </c>
       <c r="I18" t="n">
-        <v>4.25</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>12.12</v>
+        <v>7.18</v>
       </c>
       <c r="K18" t="n">
-        <v>0.99</v>
+        <v>23.06</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>13.7</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>603328</t>
+          <t>301518</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,46 +1436,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>依顿电子</t>
+          <t>长华化学</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12.7</v>
+        <v>42.99</v>
       </c>
       <c r="F19" t="n">
-        <v>12.64</v>
+        <v>42.78</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>10.8</v>
       </c>
       <c r="H19" t="n">
-        <v>12.26</v>
+        <v>41.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3.42</v>
+        <v>6.17</v>
       </c>
       <c r="J19" t="n">
-        <v>8.210000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="K19" t="n">
-        <v>2.22</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10.35</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>603186</t>
+          <t>688767</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,46 +1490,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>博拓生物</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>74.01000000000001</v>
+        <v>35.12</v>
       </c>
       <c r="F20" t="n">
-        <v>73.64</v>
+        <v>34.94</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>17.1</v>
       </c>
       <c r="H20" t="n">
-        <v>71.43000000000001</v>
+        <v>33.89</v>
       </c>
       <c r="I20" t="n">
-        <v>4.43</v>
+        <v>6.04</v>
       </c>
       <c r="J20" t="n">
-        <v>10.78</v>
+        <v>0.9</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4</v>
+        <v>17.56</v>
       </c>
       <c r="L20" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>12.45</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>605016</t>
+          <t>000049</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,46 +1544,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>百龙创园</t>
+          <t>德赛电池</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>28.07</v>
+        <v>26.97</v>
       </c>
       <c r="F21" t="n">
-        <v>27.93</v>
+        <v>26.84</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>15.6</v>
       </c>
       <c r="H21" t="n">
-        <v>27.09</v>
+        <v>26.03</v>
       </c>
       <c r="I21" t="n">
-        <v>5.61</v>
+        <v>6.01</v>
       </c>
       <c r="J21" t="n">
-        <v>4.38</v>
+        <v>2.76</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>15.71</v>
       </c>
       <c r="L21" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5.13</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>301392</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,46 +1598,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>汇成真空</t>
+          <t>德方纳米</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>143.8</v>
+        <v>44.98</v>
       </c>
       <c r="F22" t="n">
-        <v>143.08</v>
+        <v>44.76</v>
       </c>
       <c r="G22" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="H22" t="n">
-        <v>138.79</v>
+        <v>43.42</v>
       </c>
       <c r="I22" t="n">
-        <v>5.18</v>
+        <v>5.96</v>
       </c>
       <c r="J22" t="n">
-        <v>21.69</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>1.19</v>
+        <v>10.07</v>
       </c>
       <c r="L22" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>12.58</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>002348</t>
+          <t>300121</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1652,46 +1652,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>高乐股份</t>
+          <t>阳谷华泰</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.210000000000001</v>
+        <v>13.38</v>
       </c>
       <c r="F23" t="n">
-        <v>9.16</v>
+        <v>13.31</v>
       </c>
       <c r="G23" t="n">
-        <v>4.8</v>
+        <v>14.6</v>
       </c>
       <c r="H23" t="n">
-        <v>8.890000000000001</v>
+        <v>12.91</v>
       </c>
       <c r="I23" t="n">
-        <v>3.95</v>
+        <v>5.94</v>
       </c>
       <c r="J23" t="n">
-        <v>7.78</v>
+        <v>2.61</v>
       </c>
       <c r="K23" t="n">
-        <v>3.53</v>
+        <v>14.53</v>
       </c>
       <c r="L23" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.51</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>000420</t>
+          <t>601311</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1706,46 +1706,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>骆驼股份</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.02</v>
+        <v>10.03</v>
       </c>
       <c r="F24" t="n">
-        <v>4.99</v>
+        <v>9.98</v>
       </c>
       <c r="G24" t="n">
-        <v>3.1</v>
+        <v>18.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.84</v>
+        <v>9.68</v>
       </c>
       <c r="I24" t="n">
-        <v>3.29</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
-        <v>8.720000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="K24" t="n">
-        <v>1.84</v>
+        <v>19.8</v>
       </c>
       <c r="L24" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>10.73</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>300903</t>
+          <t>002983</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,46 +1760,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>科翔股份</t>
+          <t>芯瑞达</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>34.32</v>
+        <v>24.59</v>
       </c>
       <c r="F25" t="n">
-        <v>34.15</v>
+        <v>24.47</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>11.9</v>
       </c>
       <c r="H25" t="n">
-        <v>33.13</v>
+        <v>23.74</v>
       </c>
       <c r="I25" t="n">
-        <v>3.56</v>
+        <v>5.54</v>
       </c>
       <c r="J25" t="n">
-        <v>9.83</v>
+        <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>1.75</v>
+        <v>11.44</v>
       </c>
       <c r="L25" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>11.09</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>300233</t>
+          <t>002047</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1814,46 +1814,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>金城医药</t>
+          <t>*ST宝鹰</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>15.51</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>15.43</v>
+        <v>4.97</v>
       </c>
       <c r="G26" t="n">
-        <v>5.1</v>
+        <v>8.1</v>
       </c>
       <c r="H26" t="n">
-        <v>14.97</v>
+        <v>4.82</v>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="J26" t="n">
-        <v>10.55</v>
+        <v>0.8</v>
       </c>
       <c r="K26" t="n">
-        <v>3.42</v>
+        <v>7.02</v>
       </c>
       <c r="L26" t="n">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>6.24</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>000823</t>
+          <t>301622</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,46 +1868,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>英思特</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14.43</v>
+        <v>67.36</v>
       </c>
       <c r="F27" t="n">
-        <v>14.36</v>
+        <v>67.02</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>13.93</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>5.64</v>
+        <v>5.48</v>
       </c>
       <c r="J27" t="n">
-        <v>9.949999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.76</v>
+        <v>19.08</v>
       </c>
       <c r="L27" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>7.69</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>603283</t>
+          <t>301373</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1922,46 +1922,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>赛腾股份</t>
+          <t>凌玮科技</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>46.36</v>
+        <v>85.78</v>
       </c>
       <c r="F28" t="n">
-        <v>46.13</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="H28" t="n">
-        <v>44.75</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>3.97</v>
+        <v>5.47</v>
       </c>
       <c r="J28" t="n">
-        <v>6.24</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>2.73</v>
+        <v>7.38</v>
       </c>
       <c r="L28" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7.75</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002897</t>
+          <t>688486</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>意华股份</t>
+          <t>龙迅股份</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>66.84999999999999</v>
+        <v>64.44</v>
       </c>
       <c r="F29" t="n">
-        <v>66.52</v>
+        <v>64.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8</v>
+        <v>12.1</v>
       </c>
       <c r="H29" t="n">
-        <v>64.52</v>
+        <v>62.2</v>
       </c>
       <c r="I29" t="n">
-        <v>3.47</v>
+        <v>5.45</v>
       </c>
       <c r="J29" t="n">
-        <v>8.960000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>1.38</v>
+        <v>11.75</v>
       </c>
       <c r="L29" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>10.84</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>002418</t>
+          <t>688499</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,46 +2030,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>康盛股份</t>
+          <t>利元亨</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.17</v>
+        <v>49.47</v>
       </c>
       <c r="F30" t="n">
-        <v>5.14</v>
+        <v>49.22</v>
       </c>
       <c r="G30" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>4.99</v>
+        <v>47.74</v>
       </c>
       <c r="I30" t="n">
-        <v>3.19</v>
+        <v>5.28</v>
       </c>
       <c r="J30" t="n">
-        <v>13.2</v>
+        <v>0.89</v>
       </c>
       <c r="K30" t="n">
-        <v>2.38</v>
+        <v>6.93</v>
       </c>
       <c r="L30" t="n">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.67</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>002980</t>
+          <t>301468</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2084,46 +2084,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>博盈特焊</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>55.68</v>
+        <v>52.3</v>
       </c>
       <c r="F31" t="n">
-        <v>55.4</v>
+        <v>52.04</v>
       </c>
       <c r="G31" t="n">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="H31" t="n">
-        <v>53.74</v>
+        <v>50.48</v>
       </c>
       <c r="I31" t="n">
-        <v>5.33</v>
+        <v>5.17</v>
       </c>
       <c r="J31" t="n">
-        <v>19.12</v>
+        <v>3.22</v>
       </c>
       <c r="K31" t="n">
-        <v>0.99</v>
+        <v>5.84</v>
       </c>
       <c r="L31" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>10.57</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>300681</t>
+          <t>300151</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2138,46 +2138,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>英搏尔</t>
+          <t>昌红科技</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>24.8</v>
+        <v>16.7</v>
       </c>
       <c r="F32" t="n">
-        <v>24.68</v>
+        <v>16.62</v>
       </c>
       <c r="G32" t="n">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
       <c r="H32" t="n">
-        <v>23.94</v>
+        <v>16.12</v>
       </c>
       <c r="I32" t="n">
-        <v>5.04</v>
+        <v>5.16</v>
       </c>
       <c r="J32" t="n">
-        <v>11.42</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>2.44</v>
+        <v>6.65</v>
       </c>
       <c r="L32" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.66</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>002580</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,46 +2192,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>光韵达</t>
+          <t>圣阳股份</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12.87</v>
+        <v>18.13</v>
       </c>
       <c r="F33" t="n">
-        <v>12.81</v>
+        <v>18.04</v>
       </c>
       <c r="G33" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="H33" t="n">
-        <v>12.43</v>
+        <v>17.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
-        <v>11.06</v>
+        <v>14.44</v>
       </c>
       <c r="K33" t="n">
-        <v>2.35</v>
+        <v>8.73</v>
       </c>
       <c r="L33" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6.18</v>
+        <v>175.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>688135</t>
+          <t>600184</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2246,46 +2246,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>利扬芯片</t>
+          <t>光电股份</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>29.03</v>
+        <v>20.6</v>
       </c>
       <c r="F34" t="n">
-        <v>28.88</v>
+        <v>20.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.8</v>
+        <v>7.9</v>
       </c>
       <c r="H34" t="n">
-        <v>28.01</v>
+        <v>19.88</v>
       </c>
       <c r="I34" t="n">
-        <v>5.26</v>
+        <v>4.99</v>
       </c>
       <c r="J34" t="n">
-        <v>7.64</v>
+        <v>4.49</v>
       </c>
       <c r="K34" t="n">
-        <v>2.71</v>
+        <v>6.7</v>
       </c>
       <c r="L34" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>5.12</v>
+        <v>80.45999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>300632</t>
+          <t>600841</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2300,46 +2300,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>光莆股份</t>
+          <t>动力新科</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16.74</v>
+        <v>9.48</v>
       </c>
       <c r="F35" t="n">
-        <v>16.66</v>
+        <v>9.43</v>
       </c>
       <c r="G35" t="n">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>16.16</v>
+        <v>9.15</v>
       </c>
       <c r="I35" t="n">
-        <v>5.48</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
-        <v>23.42</v>
+        <v>1.25</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>8.51</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>600810</t>
+          <t>300706</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2354,46 +2354,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>神马股份</t>
+          <t>阿石创</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9.050000000000001</v>
+        <v>39.07</v>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>38.87</v>
       </c>
       <c r="G36" t="n">
-        <v>4.4</v>
+        <v>10.6</v>
       </c>
       <c r="H36" t="n">
-        <v>8.73</v>
+        <v>37.7</v>
       </c>
       <c r="I36" t="n">
-        <v>5.6</v>
+        <v>5.08</v>
       </c>
       <c r="J36" t="n">
-        <v>6.96</v>
+        <v>7.78</v>
       </c>
       <c r="K36" t="n">
-        <v>2.04</v>
+        <v>10.13</v>
       </c>
       <c r="L36" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>6.74</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>300706</t>
+          <t>301487</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2408,46 +2408,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>阿石创</t>
+          <t>盟固利</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>37.18</v>
+        <v>21.54</v>
       </c>
       <c r="F37" t="n">
-        <v>36.99</v>
+        <v>21.43</v>
       </c>
       <c r="G37" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="H37" t="n">
-        <v>35.88</v>
+        <v>20.79</v>
       </c>
       <c r="I37" t="n">
-        <v>4.61</v>
+        <v>5.07</v>
       </c>
       <c r="J37" t="n">
-        <v>16.95</v>
+        <v>2.07</v>
       </c>
       <c r="K37" t="n">
-        <v>1.9</v>
+        <v>10.71</v>
       </c>
       <c r="L37" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>7.05</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>301099</t>
+          <t>688239</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2462,46 +2462,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>雅创电子</t>
+          <t>航宇科技</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>52.2</v>
+        <v>62.24</v>
       </c>
       <c r="F38" t="n">
-        <v>51.94</v>
+        <v>61.93</v>
       </c>
       <c r="G38" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="H38" t="n">
-        <v>50.38</v>
+        <v>60.07</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="J38" t="n">
-        <v>15.68</v>
+        <v>0.73</v>
       </c>
       <c r="K38" t="n">
-        <v>1.69</v>
+        <v>5.73</v>
       </c>
       <c r="L38" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>7.37</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>301282</t>
+          <t>002150</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,46 +2516,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>金禄电子</t>
+          <t>正泰电源</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>38.49</v>
+        <v>34.4</v>
       </c>
       <c r="F39" t="n">
-        <v>38.3</v>
+        <v>34.23</v>
       </c>
       <c r="G39" t="n">
-        <v>3.5</v>
+        <v>11.4</v>
       </c>
       <c r="H39" t="n">
-        <v>37.15</v>
+        <v>33.2</v>
       </c>
       <c r="I39" t="n">
-        <v>4.65</v>
+        <v>4.94</v>
       </c>
       <c r="J39" t="n">
-        <v>18.07</v>
+        <v>5.1</v>
       </c>
       <c r="K39" t="n">
-        <v>1.44</v>
+        <v>11.14</v>
       </c>
       <c r="L39" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>7.97</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>688593</t>
+          <t>000793</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2570,46 +2570,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>新相微</t>
+          <t>*ST华闻</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>32.03</v>
+        <v>2.96</v>
       </c>
       <c r="F40" t="n">
-        <v>31.87</v>
+        <v>2.95</v>
       </c>
       <c r="G40" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="H40" t="n">
-        <v>30.91</v>
+        <v>2.86</v>
       </c>
       <c r="I40" t="n">
-        <v>3.39</v>
+        <v>4.96</v>
       </c>
       <c r="J40" t="n">
-        <v>5.21</v>
+        <v>0.66</v>
       </c>
       <c r="K40" t="n">
-        <v>2.43</v>
+        <v>12.49</v>
       </c>
       <c r="L40" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5.39</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>300252</t>
+          <t>002528</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2624,46 +2624,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>金信诺</t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>14.51</v>
+        <v>4.85</v>
       </c>
       <c r="F41" t="n">
-        <v>14.44</v>
+        <v>4.83</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2</v>
+        <v>17.9</v>
       </c>
       <c r="H41" t="n">
-        <v>14.01</v>
+        <v>4.69</v>
       </c>
       <c r="I41" t="n">
-        <v>3.27</v>
+        <v>4.98</v>
       </c>
       <c r="J41" t="n">
-        <v>8.15</v>
+        <v>3.23</v>
       </c>
       <c r="K41" t="n">
-        <v>1.97</v>
+        <v>19.32</v>
       </c>
       <c r="L41" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>6.47</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>300938</t>
+          <t>688377</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2678,46 +2678,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>信测标准</t>
+          <t>迪威尔</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>40.57</v>
+        <v>38.13</v>
       </c>
       <c r="F42" t="n">
-        <v>40.37</v>
+        <v>37.94</v>
       </c>
       <c r="G42" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="H42" t="n">
-        <v>39.16</v>
+        <v>36.8</v>
       </c>
       <c r="I42" t="n">
-        <v>5.79</v>
+        <v>4.24</v>
       </c>
       <c r="J42" t="n">
-        <v>6.81</v>
+        <v>0.5</v>
       </c>
       <c r="K42" t="n">
-        <v>2.21</v>
+        <v>7.83</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>5.76</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>603203</t>
+          <t>301305</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2732,46 +2732,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>快克智能</t>
+          <t>朗坤科技</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>44.2</v>
+        <v>26.29</v>
       </c>
       <c r="F43" t="n">
-        <v>43.98</v>
+        <v>26.16</v>
       </c>
       <c r="G43" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="H43" t="n">
-        <v>42.66</v>
+        <v>25.38</v>
       </c>
       <c r="I43" t="n">
-        <v>4.99</v>
+        <v>4.2</v>
       </c>
       <c r="J43" t="n">
-        <v>4.8</v>
+        <v>1.79</v>
       </c>
       <c r="K43" t="n">
-        <v>2.31</v>
+        <v>6.61</v>
       </c>
       <c r="L43" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>5.19</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>301307</t>
+          <t>600864</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2786,46 +2786,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>美利信</t>
+          <t>哈投股份</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>42.53</v>
+        <v>6.77</v>
       </c>
       <c r="F44" t="n">
-        <v>42.32</v>
+        <v>6.74</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>10.3</v>
       </c>
       <c r="H44" t="n">
-        <v>41.05</v>
+        <v>6.54</v>
       </c>
       <c r="I44" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="J44" t="n">
-        <v>13.06</v>
+        <v>1.61</v>
       </c>
       <c r="K44" t="n">
-        <v>1.99</v>
+        <v>10.24</v>
       </c>
       <c r="L44" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>5.99</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>603090</t>
+          <t>600552</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2840,46 +2840,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>宏盛股份</t>
+          <t>凯盛科技</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>68.38</v>
+        <v>13.49</v>
       </c>
       <c r="F45" t="n">
-        <v>68.04000000000001</v>
+        <v>13.42</v>
       </c>
       <c r="G45" t="n">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>66</v>
+        <v>13.02</v>
       </c>
       <c r="I45" t="n">
-        <v>4.14</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
-        <v>8.17</v>
+        <v>2.29</v>
       </c>
       <c r="K45" t="n">
-        <v>2.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>5.46</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>300443</t>
+          <t>600382</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2894,46 +2894,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>金雷股份</t>
+          <t>广东明珠</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>29.51</v>
+        <v>9.43</v>
       </c>
       <c r="F46" t="n">
-        <v>29.36</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="H46" t="n">
-        <v>28.48</v>
+        <v>9.1</v>
       </c>
       <c r="I46" t="n">
-        <v>5.09</v>
+        <v>4.89</v>
       </c>
       <c r="J46" t="n">
-        <v>8.77</v>
+        <v>1.36</v>
       </c>
       <c r="K46" t="n">
-        <v>1.75</v>
+        <v>8.9</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>6.17</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>000949</t>
+          <t>688661</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2948,46 +2948,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>新乡化纤</t>
+          <t>和林微纳</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>7.58</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>7.54</v>
+        <v>86.42</v>
       </c>
       <c r="G47" t="n">
-        <v>2.7</v>
+        <v>8.1</v>
       </c>
       <c r="H47" t="n">
-        <v>7.31</v>
+        <v>83.83</v>
       </c>
       <c r="I47" t="n">
-        <v>3.13</v>
+        <v>4.89</v>
       </c>
       <c r="J47" t="n">
-        <v>5.69</v>
+        <v>1.03</v>
       </c>
       <c r="K47" t="n">
-        <v>1.39</v>
+        <v>7.03</v>
       </c>
       <c r="L47" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>7.13</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>002246</t>
+          <t>002158</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3002,46 +3002,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北化股份</t>
+          <t>汉钟精机</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>24.23</v>
+        <v>24.59</v>
       </c>
       <c r="F48" t="n">
-        <v>24.11</v>
+        <v>24.47</v>
       </c>
       <c r="G48" t="n">
-        <v>2.8</v>
+        <v>10.2</v>
       </c>
       <c r="H48" t="n">
-        <v>23.39</v>
+        <v>23.74</v>
       </c>
       <c r="I48" t="n">
-        <v>3.72</v>
+        <v>4.77</v>
       </c>
       <c r="J48" t="n">
-        <v>5.57</v>
+        <v>0.52</v>
       </c>
       <c r="K48" t="n">
-        <v>1.18</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>7.43</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>300191</t>
+          <t>688337</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3056,46 +3056,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>潜能恒信</t>
+          <t>普源精电</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>38.78</v>
+        <v>56.04</v>
       </c>
       <c r="F49" t="n">
-        <v>38.59</v>
+        <v>55.76</v>
       </c>
       <c r="G49" t="n">
-        <v>3.5</v>
+        <v>6.9</v>
       </c>
       <c r="H49" t="n">
-        <v>37.43</v>
+        <v>54.09</v>
       </c>
       <c r="I49" t="n">
-        <v>5.35</v>
+        <v>4.75</v>
       </c>
       <c r="J49" t="n">
-        <v>9.01</v>
+        <v>0.97</v>
       </c>
       <c r="K49" t="n">
-        <v>1.03</v>
+        <v>5.68</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>7.62</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>300485</t>
+          <t>601002</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3110,46 +3110,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>赛升药业</t>
+          <t>晋亿实业</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.87</v>
+        <v>6.12</v>
       </c>
       <c r="F50" t="n">
-        <v>11.81</v>
+        <v>6.09</v>
       </c>
       <c r="G50" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>11.46</v>
+        <v>5.91</v>
       </c>
       <c r="I50" t="n">
-        <v>4.03</v>
+        <v>4.62</v>
       </c>
       <c r="J50" t="n">
-        <v>15.96</v>
+        <v>2.75</v>
       </c>
       <c r="K50" t="n">
-        <v>1.97</v>
+        <v>7.99</v>
       </c>
       <c r="L50" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>5.28</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>002490</t>
+          <t>300671</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3164,46 +3164,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>山东墨龙</t>
+          <t>富满微</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>9.449999999999999</v>
+        <v>42.46</v>
       </c>
       <c r="F51" t="n">
-        <v>9.4</v>
+        <v>42.25</v>
       </c>
       <c r="G51" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="H51" t="n">
-        <v>9.119999999999999</v>
+        <v>40.98</v>
       </c>
       <c r="I51" t="n">
-        <v>3.05</v>
+        <v>4.61</v>
       </c>
       <c r="J51" t="n">
-        <v>14.49</v>
+        <v>1.79</v>
       </c>
       <c r="K51" t="n">
-        <v>1.03</v>
+        <v>7.13</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>7.36</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>688677</t>
+          <t>603138</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3218,46 +3218,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>海泰新光</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>73.16</v>
+        <v>20.44</v>
       </c>
       <c r="F52" t="n">
-        <v>72.79000000000001</v>
+        <v>20.34</v>
       </c>
       <c r="G52" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>70.61</v>
+        <v>19.73</v>
       </c>
       <c r="I52" t="n">
-        <v>3.57</v>
+        <v>4.55</v>
       </c>
       <c r="J52" t="n">
-        <v>8.94</v>
+        <v>3.02</v>
       </c>
       <c r="K52" t="n">
-        <v>0.89</v>
+        <v>7.36</v>
       </c>
       <c r="L52" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>7.65</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>603163</t>
+          <t>600987</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3272,46 +3272,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>圣晖集成</t>
+          <t>航民股份</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>107</v>
+        <v>7.82</v>
       </c>
       <c r="F53" t="n">
-        <v>106.46</v>
+        <v>7.78</v>
       </c>
       <c r="G53" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>103.27</v>
+        <v>7.55</v>
       </c>
       <c r="I53" t="n">
-        <v>4.42</v>
+        <v>4.55</v>
       </c>
       <c r="J53" t="n">
-        <v>4.86</v>
+        <v>0.43</v>
       </c>
       <c r="K53" t="n">
-        <v>1.62</v>
+        <v>9.27</v>
       </c>
       <c r="L53" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>605366</t>
+          <t>002552</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3326,46 +3326,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>宝鼎科技</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12.07</v>
+        <v>18.48</v>
       </c>
       <c r="F54" t="n">
-        <v>12.01</v>
+        <v>18.39</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>9.4</v>
       </c>
       <c r="H54" t="n">
-        <v>11.65</v>
+        <v>17.84</v>
       </c>
       <c r="I54" t="n">
-        <v>3.69</v>
+        <v>4.52</v>
       </c>
       <c r="J54" t="n">
-        <v>5.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>1.48</v>
+        <v>8.94</v>
       </c>
       <c r="L54" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>5.51</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>603031</t>
+          <t>002560</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3380,32 +3380,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>安孚科技</t>
+          <t>通达股份</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>52.28</v>
+        <v>13.85</v>
       </c>
       <c r="F55" t="n">
-        <v>52.02</v>
+        <v>13.78</v>
       </c>
       <c r="G55" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="H55" t="n">
-        <v>50.46</v>
+        <v>13.37</v>
       </c>
       <c r="I55" t="n">
-        <v>3.08</v>
+        <v>4.37</v>
       </c>
       <c r="J55" t="n">
-        <v>4.4</v>
+        <v>12.4</v>
       </c>
       <c r="K55" t="n">
-        <v>1.6</v>
+        <v>4.42</v>
       </c>
       <c r="L55" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>5.02</v>
+        <v>115.05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>688275</t>
+          <t>301327</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3434,46 +3434,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>万润新能</t>
+          <t>华宝新能</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>113.72</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>113.15</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="H56" t="n">
-        <v>109.76</v>
+        <v>64.36</v>
       </c>
       <c r="I56" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="J56" t="n">
-        <v>4.32</v>
+        <v>1.22</v>
       </c>
       <c r="K56" t="n">
-        <v>0.98</v>
+        <v>6.3</v>
       </c>
       <c r="L56" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>6.11</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>688813</t>
+          <t>002478</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3488,46 +3488,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>泰金新能</t>
+          <t>常宝股份</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>50.5</v>
+        <v>11.56</v>
       </c>
       <c r="F57" t="n">
-        <v>50.25</v>
+        <v>11.5</v>
       </c>
       <c r="G57" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="H57" t="n">
-        <v>48.74</v>
+        <v>11.16</v>
       </c>
       <c r="I57" t="n">
-        <v>3.85</v>
+        <v>4.24</v>
       </c>
       <c r="J57" t="n">
-        <v>37.55</v>
+        <v>2.25</v>
       </c>
       <c r="K57" t="n">
-        <v>0.99</v>
+        <v>7.05</v>
       </c>
       <c r="L57" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5.58</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>603393</t>
+          <t>688549</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3542,40 +3542,4306 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>新天然气</t>
+          <t>中巨芯-U</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>34.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>34.35</v>
+        <v>9.41</v>
       </c>
       <c r="G58" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="n">
-        <v>33.32</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="J58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="L58" t="n">
+        <v>98</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>14.57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>603660</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>苏州科达</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="G59" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K59" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L59" t="n">
+        <v>98</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>301317</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>鑫磊股份</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F60" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="L60" t="n">
+        <v>98</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>301488</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>豪恩汽电</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>133.53</v>
+      </c>
+      <c r="G61" t="n">
+        <v>12</v>
+      </c>
+      <c r="H61" t="n">
+        <v>129.52</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K61" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="L61" t="n">
+        <v>98</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>15.04</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>300302</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>同有科技</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="G62" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H62" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="L62" t="n">
+        <v>98</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>58.22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>002965</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>祥鑫科技</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="F63" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="G63" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H63" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="L63" t="n">
+        <v>98</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>8.710000000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>301662</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>宏工科技</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>137.87</v>
+      </c>
+      <c r="F64" t="n">
+        <v>137.18</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H64" t="n">
+        <v>133.06</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K64" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="L64" t="n">
+        <v>98</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>002023</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>海特高新</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="G65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K65" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="L65" t="n">
+        <v>98</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>12.08</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>605338</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>巴比食品</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="F66" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="G66" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K66" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="L66" t="n">
+        <v>98</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>300499</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>高澜股份</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="F67" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="G67" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="K67" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="L67" t="n">
+        <v>98</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>55.21</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>002213</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>大为股份</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="F68" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="G68" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H68" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="J68" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="K68" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="L68" t="n">
+        <v>98</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>108.73</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>002896</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>中大力德</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>74.73999999999999</v>
+      </c>
+      <c r="F69" t="n">
+        <v>74.37</v>
+      </c>
+      <c r="G69" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H69" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K69" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L69" t="n">
+        <v>98</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>22.26</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>300196</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>长海股份</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="F70" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K70" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="L70" t="n">
+        <v>98</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>13.39</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>600076</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>康欣新材</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="G71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="I71" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="L71" t="n">
+        <v>98</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>600567</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>山鹰国际</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G72" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K72" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L72" t="n">
+        <v>98</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>15.87</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>688275</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>万润新能</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>118.19</v>
+      </c>
+      <c r="F73" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="G73" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H73" t="n">
+        <v>114.07</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="L73" t="n">
+        <v>98</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>30.35</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>300975</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>商络电子</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="F74" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H74" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="I74" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K74" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L74" t="n">
+        <v>98</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>42.88</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>000722</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>湖南发展</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="L75" t="n">
+        <v>98</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>26.73</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>688049</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>炬芯科技</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="F76" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H76" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="L76" t="n">
+        <v>98</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>11.07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>600478</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>科力远</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L77" t="n">
+        <v>98</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>002246</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>北化股份</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F78" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="I78" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L78" t="n">
+        <v>98</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>300004</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>南风股份</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="F79" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K79" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="L79" t="n">
+        <v>98</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>13.21</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>603336</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>宏辉果蔬</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="F80" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="G80" t="n">
+        <v>9</v>
+      </c>
+      <c r="H80" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L80" t="n">
+        <v>98</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>300619</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>金银河</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="F81" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="G81" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H81" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L81" t="n">
+        <v>98</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>301238</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>瑞泰新材</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="F82" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="G82" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H82" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K82" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="L82" t="n">
+        <v>98</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>300267</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>尔康制药</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G83" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K83" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="L83" t="n">
+        <v>98</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>21.61</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>301391</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>卡莱特</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="F84" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="G84" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="I84" t="n">
         <v>3.6</v>
       </c>
-      <c r="K58" t="n">
+      <c r="J84" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K84" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="L84" t="n">
+        <v>98</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>8.18</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>300689</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>澄天伟业</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="F85" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K85" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="L85" t="n">
+        <v>98</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>000712</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>锦龙股份</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="F86" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="G86" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H86" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="I86" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K86" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="L86" t="n">
+        <v>98</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>德邦科技</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="F87" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H87" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="L87" t="n">
+        <v>98</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>13.95</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>92.01000000000001</v>
+      </c>
+      <c r="F88" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="G88" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H88" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="K88" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="L88" t="n">
+        <v>98</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>688530</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>欧莱新材</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="F89" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H89" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J89" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="K89" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L89" t="n">
+        <v>98</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>300377</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>赢时胜</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="F90" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="G90" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K90" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="L90" t="n">
+        <v>98</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>36.91</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>002083</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>孚日股份</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="F91" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>12</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K91" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="L91" t="n">
+        <v>98</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>39.47</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>600353</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>旭光电子</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="F92" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H92" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K92" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="L92" t="n">
+        <v>98</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>21.92</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>688591</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>泰凌微</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="F93" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="G93" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K93" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="L93" t="n">
+        <v>98</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>10.81</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>300147</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ST香雪</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="F94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H94" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K94" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L94" t="n">
+        <v>98</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>14.61</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>301099</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>雅创电子</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="F95" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H95" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="I95" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J95" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="L95" t="n">
+        <v>98</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>24.74</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>300470</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>中密控股</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="F96" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H96" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J96" t="n">
         <v>0.95</v>
       </c>
-      <c r="L58" t="n">
-        <v>30</v>
-      </c>
-      <c r="M58" t="inlineStr">
+      <c r="K96" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="L96" t="n">
+        <v>98</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>002034</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>旺能环境</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="F97" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="G97" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H97" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="I97" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K97" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="L97" t="n">
+        <v>98</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>002975</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>博杰股份</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F98" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="G98" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H98" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="I98" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="J98" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="K98" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="L98" t="n">
+        <v>98</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>95.52</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>603538</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>美诺华</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="F99" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="G99" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H99" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="I99" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J99" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="K99" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="L99" t="n">
+        <v>98</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>211.31</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>688268</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>华特气体</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>105.49</v>
+      </c>
+      <c r="F100" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>101.81</v>
+      </c>
+      <c r="I100" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="L100" t="n">
+        <v>98</v>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t>✅ 低</t>
         </is>
       </c>
-      <c r="N58" t="n">
-        <v>5.15</v>
+      <c r="N100" t="n">
+        <v>55.43</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>600590</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>泰豪科技</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="F101" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H101" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K101" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L101" t="n">
+        <v>98</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>27.67</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>002645</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>华宏科技</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>22</v>
+      </c>
+      <c r="F102" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="G102" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H102" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J102" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K102" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L102" t="n">
+        <v>98</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>107.32</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>300617</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>安靠智电</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="F103" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H103" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L103" t="n">
+        <v>98</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>603128</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>华贸物流</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G104" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="I104" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K104" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="L104" t="n">
+        <v>98</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>11.93</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>605268</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="F105" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="I105" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K105" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L105" t="n">
+        <v>98</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>14.07</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>603093</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>南华期货</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F106" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="G106" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H106" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="I106" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K106" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L106" t="n">
+        <v>96</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>002067</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>景兴纸业</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="F107" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L107" t="n">
+        <v>95</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>603333</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>尚纬股份</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="F108" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G108" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H108" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="I108" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K108" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="L108" t="n">
+        <v>93</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>002882</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>金龙羽</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F109" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="G109" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H109" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="I109" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K109" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="L109" t="n">
+        <v>92</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>688480</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>赛恩斯</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F110" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="I110" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K110" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L110" t="n">
+        <v>91</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>002706</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>良信股份</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="F111" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="G111" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H111" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="I111" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L111" t="n">
+        <v>90</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>300593</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>新雷能</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="F112" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H112" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="L112" t="n">
+        <v>90</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>13.33</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>002971</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>和远气体</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="F113" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="G113" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H113" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I113" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K113" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="L113" t="n">
+        <v>89</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>300731</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>科创新源</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="F114" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="I114" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K114" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L114" t="n">
+        <v>89</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>300926</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>博俊科技</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="F115" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="G115" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K115" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="L115" t="n">
+        <v>87</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>920522</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>纳科诺尔</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="G116" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K116" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="L116" t="n">
+        <v>87</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>300648</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>星云股份</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="F117" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="G117" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H117" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="I117" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K117" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="L117" t="n">
+        <v>86</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>688116</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>天奈科技</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="F118" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H118" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="I118" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L118" t="n">
+        <v>85</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>688155</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>先惠技术</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>81.28</v>
+      </c>
+      <c r="F119" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="G119" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H119" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K119" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="L119" t="n">
+        <v>84</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>⚠️ 高</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>600328</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>中盐化工</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="F120" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L120" t="n">
+        <v>83</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>003036</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>泰坦股份</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="F121" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H121" t="n">
+        <v>24</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K121" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="L121" t="n">
+        <v>82</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>10.46</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>688032</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>禾迈股份</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>117.72</v>
+      </c>
+      <c r="F122" t="n">
+        <v>117.13</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H122" t="n">
+        <v>113.62</v>
+      </c>
+      <c r="I122" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="L122" t="n">
+        <v>77</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>9.720000000000001</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>300990</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>同飞股份</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="F123" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H123" t="n">
+        <v>81.83</v>
+      </c>
+      <c r="I123" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L123" t="n">
+        <v>77</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>9.529999999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>688348</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>昱能科技</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="F124" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="I124" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K124" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L124" t="n">
+        <v>72</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>301248</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>杰创智能</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="F125" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H125" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="I125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="L125" t="n">
+        <v>72</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>301007</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>德迈仕</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="F126" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L126" t="n">
+        <v>68</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>688510</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>航亚科技</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="F127" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="I127" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L127" t="n">
+        <v>66</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>920799</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>艾融软件</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F128" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="G128" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H128" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K128" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L128" t="n">
+        <v>65</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>301133</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>金钟股份</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="F129" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H129" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="I129" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="L129" t="n">
+        <v>65</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>002121</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>科陆电子</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="F130" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="I130" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="L130" t="n">
+        <v>64</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>688408</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>中信博</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="F131" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="G131" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H131" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K131" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L131" t="n">
+        <v>64</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>300206</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>理邦仪器</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="F132" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="G132" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H132" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K132" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L132" t="n">
+        <v>63</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>002741</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>光华科技</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="F133" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G133" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="I133" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K133" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L133" t="n">
+        <v>59</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>688443</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>智翔金泰-U</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="F134" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H134" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="L134" t="n">
+        <v>59</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>002029</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>七 匹 狼</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="F135" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="I135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K135" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L135" t="n">
+        <v>57</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>000659</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>珠海中富</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F136" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="G136" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="I136" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L136" t="n">
+        <v>52</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>601515</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>衢州东峰</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F137" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H137" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I137" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L137" t="n">
+        <v>52</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>8.59</v>
       </c>
     </row>
   </sheetData>

--- a/Liang_61_Report.xlsx
+++ b/Liang_61_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>000049</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,29 +518,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>德赛电池</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>39.06</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>38.86</v>
+        <v>26.86</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>37.69</v>
+        <v>26.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>6.13</v>
       </c>
       <c r="J2" t="n">
-        <v>12.88</v>
+        <v>6.15</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6</v>
+        <v>4.96</v>
       </c>
       <c r="L2" t="n">
         <v>98</v>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>26.27</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>600545</t>
+          <t>300489</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,29 +572,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t>光智科技</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.13</v>
+        <v>64.83</v>
       </c>
       <c r="F3" t="n">
-        <v>4.11</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.99</v>
+        <v>62.57</v>
       </c>
       <c r="I3" t="n">
-        <v>4.56</v>
+        <v>5.52</v>
       </c>
       <c r="J3" t="n">
-        <v>12.02</v>
+        <v>15.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.51</v>
+        <v>4.06</v>
       </c>
       <c r="L3" t="n">
         <v>98</v>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>17.59</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>002213</t>
+          <t>002733</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,29 +626,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大为股份</t>
+          <t>雄韬股份</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34.14</v>
+        <v>29.3</v>
       </c>
       <c r="F4" t="n">
-        <v>33.97</v>
+        <v>29.15</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H4" t="n">
-        <v>32.95</v>
+        <v>28.28</v>
       </c>
       <c r="I4" t="n">
-        <v>5.01</v>
+        <v>6.55</v>
       </c>
       <c r="J4" t="n">
-        <v>23.79</v>
+        <v>7.81</v>
       </c>
       <c r="K4" t="n">
-        <v>3.29</v>
+        <v>2.38</v>
       </c>
       <c r="L4" t="n">
         <v>98</v>
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>31.76</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300489</t>
+          <t>600552</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,29 +680,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>光智科技</t>
+          <t>凯盛科技</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>64.83</v>
+        <v>13.6</v>
       </c>
       <c r="F5" t="n">
-        <v>64.51000000000001</v>
+        <v>13.53</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H5" t="n">
-        <v>62.57</v>
+        <v>13.12</v>
       </c>
       <c r="I5" t="n">
-        <v>5.52</v>
+        <v>5.75</v>
       </c>
       <c r="J5" t="n">
-        <v>15.75</v>
+        <v>6.23</v>
       </c>
       <c r="K5" t="n">
-        <v>4.06</v>
+        <v>3.09</v>
       </c>
       <c r="L5" t="n">
         <v>98</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>27.68</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300769</t>
+          <t>002083</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -734,29 +734,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>德方纳米</t>
+          <t>孚日股份</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.73</v>
+        <v>12.7</v>
       </c>
       <c r="F6" t="n">
-        <v>44.51</v>
+        <v>12.64</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>43.17</v>
+        <v>12.26</v>
       </c>
       <c r="I6" t="n">
-        <v>5.37</v>
+        <v>5.83</v>
       </c>
       <c r="J6" t="n">
-        <v>9.640000000000001</v>
+        <v>6.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>2.37</v>
       </c>
       <c r="L6" t="n">
         <v>98</v>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>21.02</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>000049</t>
+          <t>300302</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -788,29 +788,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>德赛电池</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>22.75</v>
       </c>
       <c r="F7" t="n">
-        <v>26.86</v>
+        <v>22.64</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>26.05</v>
+        <v>21.96</v>
       </c>
       <c r="I7" t="n">
-        <v>6.13</v>
+        <v>3.98</v>
       </c>
       <c r="J7" t="n">
-        <v>6.15</v>
+        <v>10.02</v>
       </c>
       <c r="K7" t="n">
-        <v>4.96</v>
+        <v>1.93</v>
       </c>
       <c r="L7" t="n">
         <v>98</v>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>12.28</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>603757</t>
+          <t>600545</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,29 +842,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>大元泵业</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55.9</v>
+        <v>4.13</v>
       </c>
       <c r="F8" t="n">
-        <v>55.62</v>
+        <v>4.11</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>53.95</v>
+        <v>3.99</v>
       </c>
       <c r="I8" t="n">
-        <v>3.21</v>
+        <v>4.56</v>
       </c>
       <c r="J8" t="n">
-        <v>13.66</v>
+        <v>12.02</v>
       </c>
       <c r="K8" t="n">
-        <v>2.62</v>
+        <v>3.51</v>
       </c>
       <c r="L8" t="n">
         <v>98</v>
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>27.12</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>600552</t>
+          <t>002213</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -896,32 +896,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>凯盛科技</t>
+          <t>大为股份</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13.6</v>
+        <v>34.14</v>
       </c>
       <c r="F9" t="n">
-        <v>13.53</v>
+        <v>33.97</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H9" t="n">
-        <v>13.12</v>
+        <v>32.95</v>
       </c>
       <c r="I9" t="n">
-        <v>5.75</v>
+        <v>5.01</v>
       </c>
       <c r="J9" t="n">
-        <v>6.23</v>
+        <v>23.79</v>
       </c>
       <c r="K9" t="n">
-        <v>3.09</v>
+        <v>3.29</v>
       </c>
       <c r="L9" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>15.21</v>
+        <v>39.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>002733</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -950,32 +950,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>德方纳米</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29.3</v>
+        <v>44.73</v>
       </c>
       <c r="F10" t="n">
-        <v>29.15</v>
+        <v>44.51</v>
       </c>
       <c r="G10" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="H10" t="n">
-        <v>28.28</v>
+        <v>43.17</v>
       </c>
       <c r="I10" t="n">
-        <v>6.55</v>
+        <v>5.37</v>
       </c>
       <c r="J10" t="n">
-        <v>7.81</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>2.38</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>15.83</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>002083</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,32 +1004,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>孚日股份</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.7</v>
+        <v>39.06</v>
       </c>
       <c r="F11" t="n">
-        <v>12.64</v>
+        <v>38.86</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>12.26</v>
+        <v>37.69</v>
       </c>
       <c r="I11" t="n">
-        <v>5.83</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>6.78</v>
+        <v>12.88</v>
       </c>
       <c r="K11" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="L11" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>15.54</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>601311</t>
+          <t>603757</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1058,32 +1058,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>骆驼股份</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.949999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="F12" t="n">
-        <v>9.9</v>
+        <v>55.62</v>
       </c>
       <c r="G12" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>9.6</v>
+        <v>53.95</v>
       </c>
       <c r="I12" t="n">
-        <v>4.96</v>
+        <v>3.21</v>
       </c>
       <c r="J12" t="n">
-        <v>4.01</v>
+        <v>13.66</v>
       </c>
       <c r="K12" t="n">
-        <v>4.83</v>
+        <v>2.62</v>
       </c>
       <c r="L12" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>9.02</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>300302</t>
+          <t>601311</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>骆驼股份</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22.75</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>22.64</v>
+        <v>9.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>21.96</v>
+        <v>9.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.98</v>
+        <v>4.96</v>
       </c>
       <c r="J13" t="n">
-        <v>10.02</v>
+        <v>4.01</v>
       </c>
       <c r="K13" t="n">
-        <v>1.93</v>
+        <v>4.83</v>
       </c>
       <c r="L13" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>16.14</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="14">
@@ -1191,7 +1191,7 @@
         <v>2.82</v>
       </c>
       <c r="L14" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>12.77</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>002528</t>
+          <t>300671</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1220,46 +1220,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ST英飞拓</t>
+          <t>富满微</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.8</v>
+        <v>42.2</v>
       </c>
       <c r="F15" t="n">
-        <v>4.78</v>
+        <v>41.99</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1</v>
+        <v>4.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.64</v>
+        <v>40.73</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="J15" t="n">
-        <v>6.58</v>
+        <v>6.18</v>
       </c>
       <c r="K15" t="n">
-        <v>5.24</v>
+        <v>3.28</v>
       </c>
       <c r="L15" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.36</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>300671</t>
+          <t>600590</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,32 +1274,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>富满微</t>
+          <t>泰豪科技</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42.2</v>
+        <v>14.91</v>
       </c>
       <c r="F16" t="n">
-        <v>41.99</v>
+        <v>14.84</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>40.73</v>
+        <v>14.39</v>
       </c>
       <c r="I16" t="n">
-        <v>3.97</v>
+        <v>5.67</v>
       </c>
       <c r="J16" t="n">
-        <v>6.18</v>
+        <v>5.67</v>
       </c>
       <c r="K16" t="n">
-        <v>3.28</v>
+        <v>1.76</v>
       </c>
       <c r="L16" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>11.09</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>600078</t>
+          <t>300975</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,32 +1328,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>澄星股份</t>
+          <t>商络电子</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.56</v>
+        <v>21.36</v>
       </c>
       <c r="F17" t="n">
-        <v>12.5</v>
+        <v>21.25</v>
       </c>
       <c r="G17" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>12.12</v>
+        <v>20.61</v>
       </c>
       <c r="I17" t="n">
-        <v>5.63</v>
+        <v>3.69</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8</v>
+        <v>7.19</v>
       </c>
       <c r="K17" t="n">
-        <v>3.82</v>
+        <v>1.35</v>
       </c>
       <c r="L17" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>9.220000000000001</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>300706</t>
+          <t>600078</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1382,32 +1382,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>阿石创</t>
+          <t>澄星股份</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38.75</v>
+        <v>12.56</v>
       </c>
       <c r="F18" t="n">
-        <v>38.56</v>
+        <v>12.5</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="H18" t="n">
-        <v>37.4</v>
+        <v>12.12</v>
       </c>
       <c r="I18" t="n">
-        <v>4.22</v>
+        <v>5.63</v>
       </c>
       <c r="J18" t="n">
-        <v>13.75</v>
+        <v>5.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.39</v>
+        <v>3.82</v>
       </c>
       <c r="L18" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>11.8</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>600590</t>
+          <t>002528</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,46 +1436,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>泰豪科技</t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14.91</v>
+        <v>4.8</v>
       </c>
       <c r="F19" t="n">
-        <v>14.84</v>
+        <v>4.78</v>
       </c>
       <c r="G19" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>14.39</v>
+        <v>4.64</v>
       </c>
       <c r="I19" t="n">
-        <v>5.67</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>5.67</v>
+        <v>6.58</v>
       </c>
       <c r="K19" t="n">
-        <v>1.76</v>
+        <v>5.24</v>
       </c>
       <c r="L19" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>13.46</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>300975</t>
+          <t>002038</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,32 +1490,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>商络电子</t>
+          <t>双鹭药业</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21.36</v>
+        <v>7.64</v>
       </c>
       <c r="F20" t="n">
-        <v>21.25</v>
+        <v>7.6</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
-        <v>20.61</v>
+        <v>7.37</v>
       </c>
       <c r="I20" t="n">
-        <v>3.69</v>
+        <v>3.52</v>
       </c>
       <c r="J20" t="n">
-        <v>7.19</v>
+        <v>12.2</v>
       </c>
       <c r="K20" t="n">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="L20" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>14.36</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>002038</t>
+          <t>300706</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>双鹭药业</t>
+          <t>阿石创</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.64</v>
+        <v>38.75</v>
       </c>
       <c r="F21" t="n">
-        <v>7.6</v>
+        <v>38.56</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>7.37</v>
+        <v>37.4</v>
       </c>
       <c r="I21" t="n">
-        <v>3.52</v>
+        <v>4.22</v>
       </c>
       <c r="J21" t="n">
-        <v>12.2</v>
+        <v>13.75</v>
       </c>
       <c r="K21" t="n">
-        <v>1.07</v>
+        <v>2.39</v>
       </c>
       <c r="L21" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>14.74</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>002164</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,32 +1598,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>力诺药包</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13.39</v>
+        <v>24.97</v>
       </c>
       <c r="F22" t="n">
-        <v>13.32</v>
+        <v>24.85</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="H22" t="n">
-        <v>12.92</v>
+        <v>24.1</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>3.78</v>
       </c>
       <c r="J22" t="n">
-        <v>5.1</v>
+        <v>10.35</v>
       </c>
       <c r="K22" t="n">
-        <v>4.45</v>
+        <v>1.21</v>
       </c>
       <c r="L22" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>6.28</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>301188</t>
+          <t>002164</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1652,32 +1652,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>力诺药包</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>24.97</v>
+        <v>13.39</v>
       </c>
       <c r="F23" t="n">
-        <v>24.85</v>
+        <v>13.32</v>
       </c>
       <c r="G23" t="n">
-        <v>2.9</v>
+        <v>6.1</v>
       </c>
       <c r="H23" t="n">
-        <v>24.1</v>
+        <v>12.92</v>
       </c>
       <c r="I23" t="n">
-        <v>3.78</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
-        <v>10.35</v>
+        <v>5.1</v>
       </c>
       <c r="K23" t="n">
-        <v>1.21</v>
+        <v>4.45</v>
       </c>
       <c r="L23" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>13.43</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>600382</t>
+          <t>603387</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1706,32 +1706,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>广东明珠</t>
+          <t>基蛋生物</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.529999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="F24" t="n">
-        <v>9.48</v>
+        <v>10.25</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="H24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="I24" t="n">
-        <v>6.01</v>
+        <v>5.64</v>
       </c>
       <c r="J24" t="n">
-        <v>4.84</v>
+        <v>10.26</v>
       </c>
       <c r="K24" t="n">
-        <v>3.97</v>
+        <v>2.31</v>
       </c>
       <c r="L24" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.1</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>603387</t>
+          <t>301196</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,32 +1760,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>基蛋生物</t>
+          <t>唯科科技</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10.3</v>
+        <v>111.25</v>
       </c>
       <c r="F25" t="n">
-        <v>10.25</v>
+        <v>110.69</v>
       </c>
       <c r="G25" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="H25" t="n">
-        <v>9.94</v>
+        <v>107.37</v>
       </c>
       <c r="I25" t="n">
-        <v>5.64</v>
+        <v>3.68</v>
       </c>
       <c r="J25" t="n">
-        <v>10.26</v>
+        <v>6.41</v>
       </c>
       <c r="K25" t="n">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="L25" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>10.35</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>301196</t>
+          <t>002023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1814,46 +1814,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>唯科科技</t>
+          <t>海特高新</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>111.25</v>
+        <v>10.8</v>
       </c>
       <c r="F26" t="n">
-        <v>110.69</v>
+        <v>10.75</v>
       </c>
       <c r="G26" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="H26" t="n">
-        <v>107.37</v>
+        <v>10.43</v>
       </c>
       <c r="I26" t="n">
-        <v>3.68</v>
+        <v>4.75</v>
       </c>
       <c r="J26" t="n">
-        <v>6.41</v>
+        <v>2.84</v>
       </c>
       <c r="K26" t="n">
-        <v>1.91</v>
+        <v>5.05</v>
       </c>
       <c r="L26" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>11.01</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>002196</t>
+          <t>002617</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,32 +1868,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>方正电机</t>
+          <t>露笑科技</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14.37</v>
+        <v>7.81</v>
       </c>
       <c r="F27" t="n">
-        <v>14.3</v>
+        <v>7.77</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="H27" t="n">
-        <v>13.87</v>
+        <v>7.54</v>
       </c>
       <c r="I27" t="n">
-        <v>3.53</v>
+        <v>6.84</v>
       </c>
       <c r="J27" t="n">
-        <v>5.69</v>
+        <v>3.46</v>
       </c>
       <c r="K27" t="n">
-        <v>3.09</v>
+        <v>2.35</v>
       </c>
       <c r="L27" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>7.68</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>002380</t>
+          <t>600382</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1922,32 +1922,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>科远智慧</t>
+          <t>广东明珠</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>34.7</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>34.53</v>
+        <v>9.48</v>
       </c>
       <c r="G28" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="H28" t="n">
-        <v>33.49</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>3.64</v>
+        <v>6.01</v>
       </c>
       <c r="J28" t="n">
-        <v>6.6</v>
+        <v>4.84</v>
       </c>
       <c r="K28" t="n">
-        <v>3.63</v>
+        <v>3.97</v>
       </c>
       <c r="L28" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>6.23</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002617</t>
+          <t>002196</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>方正电机</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7.81</v>
+        <v>14.37</v>
       </c>
       <c r="F29" t="n">
-        <v>7.77</v>
+        <v>14.3</v>
       </c>
       <c r="G29" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="H29" t="n">
-        <v>7.54</v>
+        <v>13.87</v>
       </c>
       <c r="I29" t="n">
-        <v>6.84</v>
+        <v>3.53</v>
       </c>
       <c r="J29" t="n">
-        <v>3.46</v>
+        <v>5.69</v>
       </c>
       <c r="K29" t="n">
-        <v>2.35</v>
+        <v>3.09</v>
       </c>
       <c r="L29" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>000525</t>
+          <t>002380</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,32 +2030,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>红太阳</t>
+          <t>科远智慧</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6.27</v>
+        <v>34.7</v>
       </c>
       <c r="F30" t="n">
-        <v>6.24</v>
+        <v>34.53</v>
       </c>
       <c r="G30" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="H30" t="n">
-        <v>6.05</v>
+        <v>33.49</v>
       </c>
       <c r="I30" t="n">
-        <v>4.15</v>
+        <v>3.64</v>
       </c>
       <c r="J30" t="n">
-        <v>4.01</v>
+        <v>6.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="L30" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>5.33</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>002896</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>中大力德</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>63.51</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>63.19</v>
+        <v>74.06</v>
       </c>
       <c r="G31" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>61.29</v>
+        <v>71.84</v>
       </c>
       <c r="I31" t="n">
-        <v>6.74</v>
+        <v>3.38</v>
       </c>
       <c r="J31" t="n">
-        <v>4.14</v>
+        <v>2.97</v>
       </c>
       <c r="K31" t="n">
-        <v>3.06</v>
+        <v>2.64</v>
       </c>
       <c r="L31" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>7.1</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>002896</t>
+          <t>000525</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2138,32 +2138,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>中大力德</t>
+          <t>红太阳</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>74.43000000000001</v>
+        <v>6.27</v>
       </c>
       <c r="F32" t="n">
-        <v>74.06</v>
+        <v>6.24</v>
       </c>
       <c r="G32" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="H32" t="n">
-        <v>71.84</v>
+        <v>6.05</v>
       </c>
       <c r="I32" t="n">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="J32" t="n">
-        <v>2.97</v>
+        <v>4.01</v>
       </c>
       <c r="K32" t="n">
-        <v>2.64</v>
+        <v>3.89</v>
       </c>
       <c r="L32" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>8.369999999999999</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301487</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,32 +2192,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>盟固利</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>21.17</v>
+        <v>63.51</v>
       </c>
       <c r="F33" t="n">
-        <v>21.06</v>
+        <v>63.19</v>
       </c>
       <c r="G33" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="H33" t="n">
-        <v>20.43</v>
+        <v>61.29</v>
       </c>
       <c r="I33" t="n">
-        <v>3.27</v>
+        <v>6.74</v>
       </c>
       <c r="J33" t="n">
-        <v>5.18</v>
+        <v>4.14</v>
       </c>
       <c r="K33" t="n">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="L33" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>5.79</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -2271,7 +2271,7 @@
         <v>2.49</v>
       </c>
       <c r="L34" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="35">
@@ -2325,7 +2325,7 @@
         <v>1.99</v>
       </c>
       <c r="L35" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>8.94</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>002534</t>
+          <t>301487</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>西子洁能</t>
+          <t>盟固利</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>17.87</v>
+        <v>21.17</v>
       </c>
       <c r="F36" t="n">
-        <v>17.78</v>
+        <v>21.06</v>
       </c>
       <c r="G36" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H36" t="n">
-        <v>17.25</v>
+        <v>20.43</v>
       </c>
       <c r="I36" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="J36" t="n">
         <v>5.18</v>
       </c>
-      <c r="J36" t="n">
-        <v>2.08</v>
-      </c>
       <c r="K36" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="L36" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>5.9</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>688679</t>
+          <t>605289</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2408,32 +2408,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>通源环境</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>58.23</v>
+        <v>115.05</v>
       </c>
       <c r="F37" t="n">
-        <v>57.94</v>
+        <v>114.47</v>
       </c>
       <c r="G37" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="n">
-        <v>56.2</v>
+        <v>111.04</v>
       </c>
       <c r="I37" t="n">
-        <v>4.92</v>
+        <v>3.59</v>
       </c>
       <c r="J37" t="n">
-        <v>3.91</v>
+        <v>4.11</v>
       </c>
       <c r="K37" t="n">
-        <v>2.96</v>
+        <v>1.24</v>
       </c>
       <c r="L37" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5.7</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>300196</t>
+          <t>002534</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2462,32 +2462,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>长海股份</t>
+          <t>西子洁能</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>18.32</v>
+        <v>17.87</v>
       </c>
       <c r="F38" t="n">
-        <v>18.23</v>
+        <v>17.78</v>
       </c>
       <c r="G38" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H38" t="n">
-        <v>17.68</v>
+        <v>17.25</v>
       </c>
       <c r="I38" t="n">
-        <v>4.45</v>
+        <v>5.18</v>
       </c>
       <c r="J38" t="n">
-        <v>6.41</v>
+        <v>2.08</v>
       </c>
       <c r="K38" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="L38" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.56</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>605289</t>
+          <t>300196</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,32 +2516,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>罗曼股份</t>
+          <t>长海股份</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>115.05</v>
+        <v>18.32</v>
       </c>
       <c r="F39" t="n">
-        <v>114.47</v>
+        <v>18.23</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="H39" t="n">
-        <v>111.04</v>
+        <v>17.68</v>
       </c>
       <c r="I39" t="n">
-        <v>3.59</v>
+        <v>4.45</v>
       </c>
       <c r="J39" t="n">
-        <v>4.11</v>
+        <v>6.41</v>
       </c>
       <c r="K39" t="n">
-        <v>1.24</v>
+        <v>3.03</v>
       </c>
       <c r="L39" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>9.800000000000001</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>300990</t>
+          <t>688679</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>同飞股份</t>
+          <t>通源环境</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>86.69</v>
+        <v>58.23</v>
       </c>
       <c r="F40" t="n">
-        <v>86.26000000000001</v>
+        <v>57.94</v>
       </c>
       <c r="G40" t="n">
         <v>4.8</v>
       </c>
       <c r="H40" t="n">
-        <v>83.67</v>
+        <v>56.2</v>
       </c>
       <c r="I40" t="n">
-        <v>5.36</v>
+        <v>4.92</v>
       </c>
       <c r="J40" t="n">
-        <v>5</v>
+        <v>3.91</v>
       </c>
       <c r="K40" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="L40" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>6.37</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>002201</t>
+          <t>300990</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2624,32 +2624,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
+          <t>同飞股份</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>11.63</v>
+        <v>86.69</v>
       </c>
       <c r="F41" t="n">
-        <v>11.57</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="H41" t="n">
-        <v>11.22</v>
+        <v>83.67</v>
       </c>
       <c r="I41" t="n">
-        <v>3.84</v>
+        <v>5.36</v>
       </c>
       <c r="J41" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="L41" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>6.7</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>688202</t>
+          <t>300121</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2678,32 +2678,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>美迪西</t>
+          <t>阳谷华泰</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>68.55</v>
+        <v>13.04</v>
       </c>
       <c r="F42" t="n">
-        <v>68.20999999999999</v>
+        <v>12.97</v>
       </c>
       <c r="G42" t="n">
         <v>4.2</v>
       </c>
       <c r="H42" t="n">
-        <v>66.16</v>
+        <v>12.58</v>
       </c>
       <c r="I42" t="n">
-        <v>4.18</v>
+        <v>3.25</v>
       </c>
       <c r="J42" t="n">
-        <v>3.5</v>
+        <v>4.42</v>
       </c>
       <c r="K42" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="L42" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>6.15</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>301468</t>
+          <t>002201</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>博盈特焊</t>
+          <t>九鼎新材</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>51.53</v>
+        <v>11.63</v>
       </c>
       <c r="F43" t="n">
-        <v>51.27</v>
+        <v>11.57</v>
       </c>
       <c r="G43" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
-        <v>49.73</v>
+        <v>11.22</v>
       </c>
       <c r="I43" t="n">
-        <v>3.62</v>
+        <v>3.84</v>
       </c>
       <c r="J43" t="n">
-        <v>9.5</v>
+        <v>4.95</v>
       </c>
       <c r="K43" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="L43" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>7.16</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>600841</t>
+          <t>688202</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>动力新科</t>
+          <t>美迪西</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9.449999999999999</v>
+        <v>68.55</v>
       </c>
       <c r="F44" t="n">
-        <v>9.4</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H44" t="n">
-        <v>9.119999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="I44" t="n">
-        <v>4.77</v>
+        <v>4.18</v>
       </c>
       <c r="J44" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="L44" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>5.65</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>301667</t>
+          <t>301468</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2840,32 +2840,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>纳百川</t>
+          <t>博盈特焊</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>85.84999999999999</v>
+        <v>51.53</v>
       </c>
       <c r="F45" t="n">
-        <v>85.42</v>
+        <v>51.27</v>
       </c>
       <c r="G45" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="H45" t="n">
-        <v>82.86</v>
+        <v>49.73</v>
       </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>3.62</v>
       </c>
       <c r="J45" t="n">
-        <v>19.11</v>
+        <v>9.5</v>
       </c>
       <c r="K45" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="L45" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>7.06</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>000796</t>
+          <t>301667</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2894,32 +2894,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>凯撒旅业</t>
+          <t>纳百川</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.43</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>5.4</v>
+        <v>85.42</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H46" t="n">
-        <v>5.24</v>
+        <v>82.86</v>
       </c>
       <c r="I46" t="n">
-        <v>3.63</v>
+        <v>4.8</v>
       </c>
       <c r="J46" t="n">
-        <v>3.83</v>
+        <v>19.11</v>
       </c>
       <c r="K46" t="n">
-        <v>2.71</v>
+        <v>2.08</v>
       </c>
       <c r="L46" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>5.31</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>688239</t>
+          <t>300731</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2948,32 +2948,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>航宇科技</t>
+          <t>科创新源</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>61.7</v>
+        <v>69.09</v>
       </c>
       <c r="F47" t="n">
-        <v>61.39</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="H47" t="n">
-        <v>59.55</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="J47" t="n">
-        <v>2.67</v>
+        <v>5.18</v>
       </c>
       <c r="K47" t="n">
-        <v>2.43</v>
+        <v>1.42</v>
       </c>
       <c r="L47" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>6.08</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="48">
@@ -3027,7 +3027,7 @@
         <v>2.37</v>
       </c>
       <c r="L48" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>6.26</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>300731</t>
+          <t>688239</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3056,32 +3056,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>科创新源</t>
+          <t>航宇科技</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>69.09</v>
+        <v>61.7</v>
       </c>
       <c r="F49" t="n">
-        <v>68.73999999999999</v>
+        <v>61.39</v>
       </c>
       <c r="G49" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>66.68000000000001</v>
+        <v>59.55</v>
       </c>
       <c r="I49" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="J49" t="n">
-        <v>5.18</v>
+        <v>2.67</v>
       </c>
       <c r="K49" t="n">
-        <v>1.42</v>
+        <v>2.43</v>
       </c>
       <c r="L49" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3089,13 +3089,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>8.25</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>688543</t>
+          <t>600841</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>国科军工</t>
+          <t>动力新科</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>71.22</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>70.86</v>
+        <v>9.4</v>
       </c>
       <c r="G50" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="H50" t="n">
-        <v>68.73</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>4.06</v>
+        <v>4.77</v>
       </c>
       <c r="J50" t="n">
-        <v>4.09</v>
+        <v>3.02</v>
       </c>
       <c r="K50" t="n">
-        <v>2.14</v>
+        <v>2.67</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>6.43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>301509</t>
+          <t>000796</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>金凯生科</t>
+          <t>凯撒旅业</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>44.08</v>
+        <v>5.43</v>
       </c>
       <c r="F51" t="n">
-        <v>43.86</v>
+        <v>5.4</v>
       </c>
       <c r="G51" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>42.54</v>
+        <v>5.24</v>
       </c>
       <c r="I51" t="n">
-        <v>6.65</v>
+        <v>3.63</v>
       </c>
       <c r="J51" t="n">
-        <v>15.17</v>
+        <v>3.83</v>
       </c>
       <c r="K51" t="n">
-        <v>1.81</v>
+        <v>2.71</v>
       </c>
       <c r="L51" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>7.1</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>603196</t>
+          <t>688543</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>璞源材料</t>
+          <t>国科军工</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>32.52</v>
+        <v>71.22</v>
       </c>
       <c r="F52" t="n">
-        <v>32.36</v>
+        <v>70.86</v>
       </c>
       <c r="G52" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H52" t="n">
-        <v>31.39</v>
+        <v>68.73</v>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>4.06</v>
       </c>
       <c r="J52" t="n">
-        <v>3.81</v>
+        <v>4.09</v>
       </c>
       <c r="K52" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3251,13 +3251,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>5.66</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>002427</t>
+          <t>301509</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3272,32 +3272,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>尤夫股份</t>
+          <t>金凯生科</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6.77</v>
+        <v>44.08</v>
       </c>
       <c r="F53" t="n">
-        <v>6.74</v>
+        <v>43.86</v>
       </c>
       <c r="G53" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H53" t="n">
-        <v>6.54</v>
+        <v>42.54</v>
       </c>
       <c r="I53" t="n">
-        <v>5.12</v>
+        <v>6.65</v>
       </c>
       <c r="J53" t="n">
-        <v>4.03</v>
+        <v>15.17</v>
       </c>
       <c r="K53" t="n">
-        <v>2.59</v>
+        <v>1.81</v>
       </c>
       <c r="L53" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5.01</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>002437</t>
+          <t>301319</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3326,32 +3326,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>誉衡药业</t>
+          <t>唯特偶</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.75</v>
+        <v>50.83</v>
       </c>
       <c r="F54" t="n">
-        <v>3.73</v>
+        <v>50.58</v>
       </c>
       <c r="G54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="K54" t="n">
         <v>2.8</v>
       </c>
-      <c r="H54" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="J54" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.87</v>
-      </c>
       <c r="L54" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3359,13 +3359,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>8.74</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>300267</t>
+          <t>603196</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3380,32 +3380,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>尔康制药</t>
+          <t>璞源材料</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.04</v>
+        <v>32.52</v>
       </c>
       <c r="F55" t="n">
-        <v>4.02</v>
+        <v>32.36</v>
       </c>
       <c r="G55" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="H55" t="n">
-        <v>3.9</v>
+        <v>31.39</v>
       </c>
       <c r="I55" t="n">
-        <v>3.59</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
-        <v>5.29</v>
+        <v>3.81</v>
       </c>
       <c r="K55" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="L55" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>5.83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>000593</t>
+          <t>002437</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>德龙汇能</t>
+          <t>誉衡药业</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>17.39</v>
+        <v>3.75</v>
       </c>
       <c r="F56" t="n">
-        <v>17.3</v>
+        <v>3.73</v>
       </c>
       <c r="G56" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H56" t="n">
-        <v>16.78</v>
+        <v>3.62</v>
       </c>
       <c r="I56" t="n">
-        <v>3.02</v>
+        <v>4.17</v>
       </c>
       <c r="J56" t="n">
-        <v>6.61</v>
+        <v>6.04</v>
       </c>
       <c r="K56" t="n">
-        <v>1.25</v>
+        <v>0.87</v>
       </c>
       <c r="L56" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>7.77</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>300842</t>
+          <t>002427</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>帝科股份</t>
+          <t>尤夫股份</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>85</v>
+        <v>6.77</v>
       </c>
       <c r="F57" t="n">
-        <v>84.58</v>
+        <v>6.74</v>
       </c>
       <c r="G57" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="H57" t="n">
-        <v>82.04000000000001</v>
+        <v>6.54</v>
       </c>
       <c r="I57" t="n">
-        <v>3.43</v>
+        <v>5.12</v>
       </c>
       <c r="J57" t="n">
-        <v>2.9</v>
+        <v>4.03</v>
       </c>
       <c r="K57" t="n">
-        <v>1.86</v>
+        <v>2.59</v>
       </c>
       <c r="L57" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3521,13 +3521,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>6.04</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>300617</t>
+          <t>000593</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安靠智电</t>
+          <t>德龙汇能</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>59.36</v>
+        <v>17.39</v>
       </c>
       <c r="F58" t="n">
-        <v>59.06</v>
+        <v>17.3</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H58" t="n">
-        <v>57.29</v>
+        <v>16.78</v>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="J58" t="n">
-        <v>4.36</v>
+        <v>6.61</v>
       </c>
       <c r="K58" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L58" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>6.87</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -3621,7 +3621,7 @@
         <v>1.13</v>
       </c>
       <c r="L59" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>7.88</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>002550</t>
+          <t>300267</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3650,32 +3650,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>千红制药</t>
+          <t>尔康制药</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7.95</v>
+        <v>4.04</v>
       </c>
       <c r="F60" t="n">
-        <v>7.91</v>
+        <v>4.02</v>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H60" t="n">
-        <v>7.67</v>
+        <v>3.9</v>
       </c>
       <c r="I60" t="n">
-        <v>4.88</v>
+        <v>3.59</v>
       </c>
       <c r="J60" t="n">
-        <v>4.1</v>
+        <v>5.29</v>
       </c>
       <c r="K60" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="L60" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>5.81</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="61">
@@ -3729,7 +3729,7 @@
         <v>1.58</v>
       </c>
       <c r="L61" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3737,13 +3737,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>6.73</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>603367</t>
+          <t>300617</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3758,32 +3758,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>辰欣药业</t>
+          <t>安靠智电</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>16.72</v>
+        <v>59.36</v>
       </c>
       <c r="F62" t="n">
-        <v>16.64</v>
+        <v>59.06</v>
       </c>
       <c r="G62" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="H62" t="n">
-        <v>16.14</v>
+        <v>57.29</v>
       </c>
       <c r="I62" t="n">
-        <v>5.76</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
-        <v>3.59</v>
+        <v>4.36</v>
       </c>
       <c r="K62" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="L62" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.13</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>002705</t>
+          <t>300842</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3812,32 +3812,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>新宝股份</t>
+          <t>帝科股份</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>15.47</v>
+        <v>85</v>
       </c>
       <c r="F63" t="n">
-        <v>15.39</v>
+        <v>84.58</v>
       </c>
       <c r="G63" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H63" t="n">
-        <v>14.93</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="J63" t="n">
-        <v>2.13</v>
+        <v>2.9</v>
       </c>
       <c r="K63" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="L63" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>5.07</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>002970</t>
+          <t>002550</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>锐明技术</t>
+          <t>千红制药</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>68.11</v>
+        <v>7.95</v>
       </c>
       <c r="F64" t="n">
-        <v>67.77</v>
+        <v>7.91</v>
       </c>
       <c r="G64" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="H64" t="n">
-        <v>65.73999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="I64" t="n">
-        <v>3.65</v>
+        <v>4.88</v>
       </c>
       <c r="J64" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="K64" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="L64" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>5.18</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>301080</t>
+          <t>603367</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3920,32 +3920,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>百普赛斯</t>
+          <t>辰欣药业</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>49.9</v>
+        <v>16.72</v>
       </c>
       <c r="F65" t="n">
-        <v>49.65</v>
+        <v>16.64</v>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H65" t="n">
-        <v>48.16</v>
+        <v>16.14</v>
       </c>
       <c r="I65" t="n">
-        <v>7.08</v>
+        <v>5.76</v>
       </c>
       <c r="J65" t="n">
-        <v>4.3</v>
+        <v>3.59</v>
       </c>
       <c r="K65" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="L65" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>5.09</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>688068</t>
+          <t>002970</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3974,32 +3974,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>热景生物</t>
+          <t>锐明技术</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>124.4</v>
+        <v>68.11</v>
       </c>
       <c r="F66" t="n">
-        <v>123.78</v>
+        <v>67.77</v>
       </c>
       <c r="G66" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="H66" t="n">
-        <v>120.07</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>3.51</v>
+        <v>3.65</v>
       </c>
       <c r="J66" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="K66" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="L66" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5.92</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>603227</t>
+          <t>002705</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4028,32 +4028,32 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>雪峰科技</t>
+          <t>新宝股份</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10.53</v>
+        <v>15.47</v>
       </c>
       <c r="F67" t="n">
-        <v>10.48</v>
+        <v>15.39</v>
       </c>
       <c r="G67" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H67" t="n">
-        <v>10.17</v>
+        <v>14.93</v>
       </c>
       <c r="I67" t="n">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="J67" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="K67" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="L67" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5.94</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301251</t>
+          <t>603227</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>威尔高</t>
+          <t>雪峰科技</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>66.90000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="F68" t="n">
-        <v>66.56999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="G68" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="H68" t="n">
-        <v>64.56999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="I68" t="n">
-        <v>3.26</v>
+        <v>3.74</v>
       </c>
       <c r="J68" t="n">
-        <v>8.32</v>
+        <v>2.75</v>
       </c>
       <c r="K68" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="L68" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>5.73</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>688480</t>
+          <t>688068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>赛恩斯</t>
+          <t>热景生物</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>88.40000000000001</v>
+        <v>124.4</v>
       </c>
       <c r="F69" t="n">
-        <v>87.95999999999999</v>
+        <v>123.78</v>
       </c>
       <c r="G69" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="H69" t="n">
-        <v>85.31999999999999</v>
+        <v>120.07</v>
       </c>
       <c r="I69" t="n">
-        <v>4.37</v>
+        <v>3.51</v>
       </c>
       <c r="J69" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="K69" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="L69" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>5.18</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>002035</t>
+          <t>301080</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4190,32 +4190,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>华帝股份</t>
+          <t>百普赛斯</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6.5</v>
+        <v>49.9</v>
       </c>
       <c r="F70" t="n">
-        <v>6.47</v>
+        <v>49.65</v>
       </c>
       <c r="G70" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H70" t="n">
-        <v>6.28</v>
+        <v>48.16</v>
       </c>
       <c r="I70" t="n">
-        <v>6.91</v>
+        <v>7.08</v>
       </c>
       <c r="J70" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="K70" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="L70" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -4223,61 +4223,655 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>5.07</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>688499</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>利元亨</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="F71" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H71" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="I71" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L71" t="n">
+        <v>43</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>300685</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>艾德生物</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="F72" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H72" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L72" t="n">
+        <v>43</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>301251</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>威尔高</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>66.56999999999999</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H73" t="n">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J73" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L73" t="n">
+        <v>42</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>688480</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>赛恩斯</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F74" t="n">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>85.31999999999999</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L74" t="n">
+        <v>40</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>002035</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>华帝股份</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H75" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="I75" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L75" t="n">
+        <v>39</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>688108</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>赛诺医疗</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="F76" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L76" t="n">
+        <v>38</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>688559</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>海目星</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="F77" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H77" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L77" t="n">
+        <v>38</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>002755</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>奥赛康</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E78" t="n">
         <v>15.99</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F78" t="n">
         <v>15.91</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G78" t="n">
         <v>2.7</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H78" t="n">
         <v>15.43</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I78" t="n">
         <v>3.29</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J78" t="n">
         <v>1.89</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K78" t="n">
         <v>1.26</v>
       </c>
-      <c r="L71" t="n">
-        <v>33</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>5.29</v>
+      <c r="L78" t="n">
+        <v>38</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>300580</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>贝斯特</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="F79" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L79" t="n">
+        <v>36</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>300668</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>杰恩设计</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="F80" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H80" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L80" t="n">
+        <v>32</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>002713</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>*ST东易</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="F81" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3</v>
+      </c>
+      <c r="H81" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="I81" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L81" t="n">
+        <v>31</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>003018</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>🔥 猎妖启动</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>量价共振/多头排列</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>金富科技</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="F82" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L82" t="n">
+        <v>31</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>✅ 低</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5.31</v>
       </c>
     </row>
   </sheetData>

--- a/Liang_61_Report.xlsx
+++ b/Liang_61_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>000049</t>
+          <t>300489</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,29 +518,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>德赛电池</t>
+          <t>光智科技</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>65.08</v>
       </c>
       <c r="F2" t="n">
-        <v>26.86</v>
+        <v>64.75</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>26.05</v>
+        <v>62.81</v>
       </c>
       <c r="I2" t="n">
-        <v>6.13</v>
+        <v>5.92</v>
       </c>
       <c r="J2" t="n">
-        <v>6.15</v>
+        <v>16.17</v>
       </c>
       <c r="K2" t="n">
-        <v>4.96</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>98</v>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15.2</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300489</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,29 +572,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>光智科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>64.83</v>
+        <v>39.13</v>
       </c>
       <c r="F3" t="n">
-        <v>64.51000000000001</v>
+        <v>38.93</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>62.57</v>
+        <v>37.76</v>
       </c>
       <c r="I3" t="n">
-        <v>5.52</v>
+        <v>3.99</v>
       </c>
       <c r="J3" t="n">
-        <v>15.75</v>
+        <v>13.32</v>
       </c>
       <c r="K3" t="n">
-        <v>4.06</v>
+        <v>2.48</v>
       </c>
       <c r="L3" t="n">
         <v>98</v>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34.25</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>002733</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,29 +626,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>德方纳米</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29.3</v>
+        <v>44.87</v>
       </c>
       <c r="F4" t="n">
-        <v>29.15</v>
+        <v>44.65</v>
       </c>
       <c r="G4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>28.28</v>
+        <v>43.31</v>
       </c>
       <c r="I4" t="n">
-        <v>6.55</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>7.81</v>
+        <v>9.77</v>
       </c>
       <c r="K4" t="n">
-        <v>2.38</v>
+        <v>3.41</v>
       </c>
       <c r="L4" t="n">
         <v>98</v>
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>19.59</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600552</t>
+          <t>002213</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,29 +680,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>凯盛科技</t>
+          <t>大为股份</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13.6</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>13.53</v>
+        <v>33.83</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>13.12</v>
+        <v>32.82</v>
       </c>
       <c r="I5" t="n">
-        <v>5.75</v>
+        <v>4.58</v>
       </c>
       <c r="J5" t="n">
-        <v>6.23</v>
+        <v>24.61</v>
       </c>
       <c r="K5" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="L5" t="n">
         <v>98</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>18.83</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>002083</t>
+          <t>600545</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -734,29 +734,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>孚日股份</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12.7</v>
+        <v>4.15</v>
       </c>
       <c r="F6" t="n">
-        <v>12.64</v>
+        <v>4.13</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="n">
-        <v>12.26</v>
+        <v>4.01</v>
       </c>
       <c r="I6" t="n">
-        <v>5.83</v>
+        <v>5.06</v>
       </c>
       <c r="J6" t="n">
-        <v>6.78</v>
+        <v>12.22</v>
       </c>
       <c r="K6" t="n">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>98</v>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>19.23</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300302</t>
+          <t>300300</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>海峡创新</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22.75</v>
+        <v>13.92</v>
       </c>
       <c r="F7" t="n">
-        <v>22.64</v>
+        <v>13.85</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>21.96</v>
+        <v>13.43</v>
       </c>
       <c r="I7" t="n">
-        <v>3.98</v>
+        <v>3.11</v>
       </c>
       <c r="J7" t="n">
-        <v>10.02</v>
+        <v>12.63</v>
       </c>
       <c r="K7" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="L7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>19.97</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>600545</t>
+          <t>000049</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,32 +842,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t>德赛电池</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.13</v>
+        <v>26.97</v>
       </c>
       <c r="F8" t="n">
-        <v>4.11</v>
+        <v>26.84</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.99</v>
+        <v>26.03</v>
       </c>
       <c r="I8" t="n">
-        <v>4.56</v>
+        <v>6.01</v>
       </c>
       <c r="J8" t="n">
-        <v>12.02</v>
+        <v>6.24</v>
       </c>
       <c r="K8" t="n">
-        <v>3.51</v>
+        <v>4.61</v>
       </c>
       <c r="L8" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>21.77</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>002213</t>
+          <t>600552</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -896,32 +896,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>大为股份</t>
+          <t>凯盛科技</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34.14</v>
+        <v>13.49</v>
       </c>
       <c r="F9" t="n">
-        <v>33.97</v>
+        <v>13.42</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="n">
-        <v>32.95</v>
+        <v>13.02</v>
       </c>
       <c r="I9" t="n">
-        <v>5.01</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>23.79</v>
+        <v>6.43</v>
       </c>
       <c r="K9" t="n">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="L9" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>39.31</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300769</t>
+          <t>002733</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -950,32 +950,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>德方纳米</t>
+          <t>雄韬股份</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>44.73</v>
+        <v>29.23</v>
       </c>
       <c r="F10" t="n">
-        <v>44.51</v>
+        <v>29.08</v>
       </c>
       <c r="G10" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>43.17</v>
+        <v>28.21</v>
       </c>
       <c r="I10" t="n">
-        <v>5.37</v>
+        <v>6.29</v>
       </c>
       <c r="J10" t="n">
-        <v>9.640000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>2.29</v>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>26.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002083</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,32 +1004,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>孚日股份</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>39.06</v>
+        <v>12.86</v>
       </c>
       <c r="F11" t="n">
-        <v>38.86</v>
+        <v>12.8</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="n">
-        <v>37.69</v>
+        <v>12.42</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>7.17</v>
       </c>
       <c r="J11" t="n">
-        <v>12.88</v>
+        <v>7.07</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="L11" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>32.52</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>603757</t>
+          <t>300302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1058,32 +1058,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>大元泵业</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>55.9</v>
+        <v>22.66</v>
       </c>
       <c r="F12" t="n">
-        <v>55.62</v>
+        <v>22.55</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>53.95</v>
+        <v>21.87</v>
       </c>
       <c r="I12" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="J12" t="n">
-        <v>13.66</v>
+        <v>10.38</v>
       </c>
       <c r="K12" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="L12" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>33.56</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="13">
@@ -1116,28 +1116,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="F13" t="n">
-        <v>9.9</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="I13" t="n">
-        <v>4.96</v>
+        <v>4.75</v>
       </c>
       <c r="J13" t="n">
-        <v>4.01</v>
+        <v>4.11</v>
       </c>
       <c r="K13" t="n">
-        <v>4.83</v>
+        <v>4.59</v>
       </c>
       <c r="L13" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>11.16</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1170,28 +1170,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18.4</v>
+        <v>18.44</v>
       </c>
       <c r="F14" t="n">
-        <v>18.31</v>
+        <v>18.35</v>
       </c>
       <c r="G14" t="n">
         <v>3.9</v>
       </c>
       <c r="H14" t="n">
-        <v>17.76</v>
+        <v>17.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3.31</v>
+        <v>3.54</v>
       </c>
       <c r="J14" t="n">
-        <v>5.18</v>
+        <v>5.29</v>
       </c>
       <c r="K14" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="L14" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>15.81</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="15">
@@ -1224,28 +1224,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>42.2</v>
+        <v>41.94</v>
       </c>
       <c r="F15" t="n">
-        <v>41.99</v>
+        <v>41.73</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>40.73</v>
+        <v>40.48</v>
       </c>
       <c r="I15" t="n">
-        <v>3.97</v>
+        <v>3.33</v>
       </c>
       <c r="J15" t="n">
-        <v>6.18</v>
+        <v>6.39</v>
       </c>
       <c r="K15" t="n">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="L15" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>13.73</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="16">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14.91</v>
+        <v>14.87</v>
       </c>
       <c r="F16" t="n">
-        <v>14.84</v>
+        <v>14.8</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H16" t="n">
-        <v>14.39</v>
+        <v>14.36</v>
       </c>
       <c r="I16" t="n">
-        <v>5.67</v>
+        <v>5.39</v>
       </c>
       <c r="J16" t="n">
-        <v>5.67</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="L16" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>16.66</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>300975</t>
+          <t>002528</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,32 +1328,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>商络电子</t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21.36</v>
+        <v>4.83</v>
       </c>
       <c r="F17" t="n">
-        <v>21.25</v>
+        <v>4.81</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>20.61</v>
+        <v>4.67</v>
       </c>
       <c r="I17" t="n">
-        <v>3.69</v>
+        <v>4.55</v>
       </c>
       <c r="J17" t="n">
-        <v>7.19</v>
+        <v>6.77</v>
       </c>
       <c r="K17" t="n">
-        <v>1.35</v>
+        <v>4.94</v>
       </c>
       <c r="L17" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>17.77</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="18">
@@ -1386,28 +1386,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.56</v>
+        <v>12.52</v>
       </c>
       <c r="F18" t="n">
-        <v>12.5</v>
+        <v>12.46</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="H18" t="n">
-        <v>12.12</v>
+        <v>12.09</v>
       </c>
       <c r="I18" t="n">
-        <v>5.63</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>5.8</v>
+        <v>6.12</v>
       </c>
       <c r="K18" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="L18" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>11.41</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>002528</t>
+          <t>002617</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,46 +1436,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ST英飞拓</t>
+          <t>露笑科技</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.8</v>
+        <v>7.68</v>
       </c>
       <c r="F19" t="n">
-        <v>4.78</v>
+        <v>7.64</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.64</v>
+        <v>7.41</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>5.06</v>
       </c>
       <c r="J19" t="n">
-        <v>6.58</v>
+        <v>4.41</v>
       </c>
       <c r="K19" t="n">
-        <v>5.24</v>
+        <v>2.74</v>
       </c>
       <c r="L19" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7.87</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>002038</t>
+          <t>300706</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,32 +1490,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>双鹭药业</t>
+          <t>阿石创</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.64</v>
+        <v>38.58</v>
       </c>
       <c r="F20" t="n">
-        <v>7.6</v>
+        <v>38.39</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="H20" t="n">
-        <v>7.37</v>
+        <v>37.24</v>
       </c>
       <c r="I20" t="n">
-        <v>3.52</v>
+        <v>3.77</v>
       </c>
       <c r="J20" t="n">
-        <v>12.2</v>
+        <v>14.16</v>
       </c>
       <c r="K20" t="n">
-        <v>1.07</v>
+        <v>2.27</v>
       </c>
       <c r="L20" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>18.24</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>300706</t>
+          <t>002164</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>阿石创</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38.75</v>
+        <v>13.31</v>
       </c>
       <c r="F21" t="n">
-        <v>38.56</v>
+        <v>13.24</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="H21" t="n">
-        <v>37.4</v>
+        <v>12.84</v>
       </c>
       <c r="I21" t="n">
-        <v>4.22</v>
+        <v>4.47</v>
       </c>
       <c r="J21" t="n">
-        <v>13.75</v>
+        <v>5.32</v>
       </c>
       <c r="K21" t="n">
-        <v>2.39</v>
+        <v>4.25</v>
       </c>
       <c r="L21" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>14.61</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>301188</t>
+          <t>603387</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,32 +1598,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>力诺药包</t>
+          <t>基蛋生物</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>24.97</v>
+        <v>10.24</v>
       </c>
       <c r="F22" t="n">
-        <v>24.85</v>
+        <v>10.19</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>24.1</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>3.78</v>
+        <v>5.03</v>
       </c>
       <c r="J22" t="n">
-        <v>10.35</v>
+        <v>10.49</v>
       </c>
       <c r="K22" t="n">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="L22" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>16.62</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>002164</t>
+          <t>600382</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1652,32 +1652,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>广东明珠</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>13.39</v>
+        <v>9.5</v>
       </c>
       <c r="F23" t="n">
-        <v>13.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="H23" t="n">
-        <v>12.92</v>
+        <v>9.17</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.67</v>
       </c>
       <c r="J23" t="n">
-        <v>5.1</v>
+        <v>4.98</v>
       </c>
       <c r="K23" t="n">
-        <v>4.45</v>
+        <v>3.77</v>
       </c>
       <c r="L23" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>7.77</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>603387</t>
+          <t>301196</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1706,32 +1706,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>基蛋生物</t>
+          <t>唯科科技</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10.3</v>
+        <v>111.1</v>
       </c>
       <c r="F24" t="n">
-        <v>10.25</v>
+        <v>110.54</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="H24" t="n">
-        <v>9.94</v>
+        <v>107.22</v>
       </c>
       <c r="I24" t="n">
-        <v>5.64</v>
+        <v>3.54</v>
       </c>
       <c r="J24" t="n">
-        <v>10.26</v>
+        <v>6.61</v>
       </c>
       <c r="K24" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="L24" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>12.81</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>301196</t>
+          <t>002196</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,32 +1760,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>唯科科技</t>
+          <t>方正电机</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>111.25</v>
+        <v>14.4</v>
       </c>
       <c r="F25" t="n">
-        <v>110.69</v>
+        <v>14.33</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="H25" t="n">
-        <v>107.37</v>
+        <v>13.9</v>
       </c>
       <c r="I25" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>6.41</v>
+        <v>5.92</v>
       </c>
       <c r="K25" t="n">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="L25" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>13.63</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>002023</t>
+          <t>002380</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1814,46 +1814,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>海特高新</t>
+          <t>科远智慧</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10.8</v>
+        <v>34.84</v>
       </c>
       <c r="F26" t="n">
-        <v>10.75</v>
+        <v>34.67</v>
       </c>
       <c r="G26" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="H26" t="n">
-        <v>10.43</v>
+        <v>33.63</v>
       </c>
       <c r="I26" t="n">
-        <v>4.75</v>
+        <v>4.06</v>
       </c>
       <c r="J26" t="n">
-        <v>2.84</v>
+        <v>6.83</v>
       </c>
       <c r="K26" t="n">
-        <v>5.05</v>
+        <v>3.44</v>
       </c>
       <c r="L26" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>⚠️ 高</t>
+          <t>✅ 低</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>002617</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,32 +1868,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7.81</v>
+        <v>63.66</v>
       </c>
       <c r="F27" t="n">
-        <v>7.77</v>
+        <v>63.34</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="H27" t="n">
-        <v>7.54</v>
+        <v>61.44</v>
       </c>
       <c r="I27" t="n">
-        <v>6.84</v>
+        <v>6.99</v>
       </c>
       <c r="J27" t="n">
-        <v>3.46</v>
+        <v>4.38</v>
       </c>
       <c r="K27" t="n">
-        <v>2.35</v>
+        <v>3.02</v>
       </c>
       <c r="L27" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>11.64</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>600382</t>
+          <t>000525</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1922,32 +1922,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>广东明珠</t>
+          <t>红太阳</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9.529999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="F28" t="n">
-        <v>9.48</v>
+        <v>6.19</v>
       </c>
       <c r="G28" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="H28" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>6.01</v>
+        <v>3.32</v>
       </c>
       <c r="J28" t="n">
-        <v>4.84</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.97</v>
+        <v>3.74</v>
       </c>
       <c r="L28" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7.55</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002196</t>
+          <t>002896</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>方正电机</t>
+          <t>中大力德</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14.37</v>
+        <v>74.58</v>
       </c>
       <c r="F29" t="n">
-        <v>14.3</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H29" t="n">
-        <v>13.87</v>
+        <v>71.98</v>
       </c>
       <c r="I29" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="J29" t="n">
-        <v>5.69</v>
+        <v>3.01</v>
       </c>
       <c r="K29" t="n">
-        <v>3.09</v>
+        <v>2.47</v>
       </c>
       <c r="L29" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>9.5</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>002380</t>
+          <t>688661</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,32 +2030,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>科远智慧</t>
+          <t>和林微纳</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34.7</v>
+        <v>88.09</v>
       </c>
       <c r="F30" t="n">
-        <v>34.53</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="H30" t="n">
-        <v>33.49</v>
+        <v>85.02</v>
       </c>
       <c r="I30" t="n">
-        <v>3.64</v>
+        <v>6.39</v>
       </c>
       <c r="J30" t="n">
-        <v>6.6</v>
+        <v>3.27</v>
       </c>
       <c r="K30" t="n">
-        <v>3.63</v>
+        <v>2.43</v>
       </c>
       <c r="L30" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.71</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>002896</t>
+          <t>301487</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>中大力德</t>
+          <t>盟固利</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>74.43000000000001</v>
+        <v>21.15</v>
       </c>
       <c r="F31" t="n">
-        <v>74.06</v>
+        <v>21.04</v>
       </c>
       <c r="G31" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H31" t="n">
-        <v>71.84</v>
+        <v>20.41</v>
       </c>
       <c r="I31" t="n">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="J31" t="n">
-        <v>2.97</v>
+        <v>5.35</v>
       </c>
       <c r="K31" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="L31" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>10.35</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>000525</t>
+          <t>002283</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2138,32 +2138,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>红太阳</t>
+          <t>天润工业</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6.27</v>
+        <v>10.66</v>
       </c>
       <c r="F32" t="n">
-        <v>6.24</v>
+        <v>10.61</v>
       </c>
       <c r="G32" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="H32" t="n">
-        <v>6.05</v>
+        <v>10.29</v>
       </c>
       <c r="I32" t="n">
-        <v>4.15</v>
+        <v>6.07</v>
       </c>
       <c r="J32" t="n">
-        <v>4.01</v>
+        <v>4.49</v>
       </c>
       <c r="K32" t="n">
-        <v>3.89</v>
+        <v>1.88</v>
       </c>
       <c r="L32" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.59</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>300196</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,32 +2192,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>长海股份</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63.51</v>
+        <v>18.34</v>
       </c>
       <c r="F33" t="n">
-        <v>63.19</v>
+        <v>18.25</v>
       </c>
       <c r="G33" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="H33" t="n">
-        <v>61.29</v>
+        <v>17.7</v>
       </c>
       <c r="I33" t="n">
-        <v>6.74</v>
+        <v>4.56</v>
       </c>
       <c r="J33" t="n">
-        <v>4.14</v>
+        <v>6.53</v>
       </c>
       <c r="K33" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="L33" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>8.789999999999999</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>688661</t>
+          <t>688679</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>和林微纳</t>
+          <t>通源环境</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>88.59999999999999</v>
+        <v>58.34</v>
       </c>
       <c r="F34" t="n">
-        <v>88.16</v>
+        <v>58.05</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="H34" t="n">
-        <v>85.52</v>
+        <v>56.31</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>5.12</v>
       </c>
       <c r="J34" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>2.49</v>
+        <v>2.84</v>
       </c>
       <c r="L34" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2279,13 +2279,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>9.9</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>002283</t>
+          <t>300990</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2300,32 +2300,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>天润工业</t>
+          <t>同飞股份</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10.67</v>
+        <v>86.83</v>
       </c>
       <c r="F35" t="n">
-        <v>10.62</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H35" t="n">
-        <v>10.3</v>
+        <v>83.81</v>
       </c>
       <c r="I35" t="n">
-        <v>6.17</v>
+        <v>5.53</v>
       </c>
       <c r="J35" t="n">
-        <v>4.35</v>
+        <v>5.16</v>
       </c>
       <c r="K35" t="n">
-        <v>1.99</v>
+        <v>2.51</v>
       </c>
       <c r="L35" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>11.06</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>301487</t>
+          <t>688202</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>盟固利</t>
+          <t>美迪西</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>21.17</v>
+        <v>68</v>
       </c>
       <c r="F36" t="n">
-        <v>21.06</v>
+        <v>67.66</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="H36" t="n">
-        <v>20.43</v>
+        <v>65.63</v>
       </c>
       <c r="I36" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="J36" t="n">
-        <v>5.18</v>
+        <v>3.59</v>
       </c>
       <c r="K36" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="L36" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>7.17</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>605289</t>
+          <t>600841</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2408,32 +2408,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>罗曼股份</t>
+          <t>动力新科</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>115.05</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>114.47</v>
+        <v>9.34</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="H37" t="n">
-        <v>111.04</v>
+        <v>9.06</v>
       </c>
       <c r="I37" t="n">
-        <v>3.59</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
-        <v>4.11</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>1.24</v>
+        <v>2.59</v>
       </c>
       <c r="L37" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>12.13</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>002534</t>
+          <t>301468</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2462,32 +2462,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>西子洁能</t>
+          <t>博盈特焊</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>17.87</v>
+        <v>51.59</v>
       </c>
       <c r="F38" t="n">
-        <v>17.78</v>
+        <v>51.33</v>
       </c>
       <c r="G38" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="H38" t="n">
-        <v>17.25</v>
+        <v>49.79</v>
       </c>
       <c r="I38" t="n">
-        <v>5.18</v>
+        <v>3.74</v>
       </c>
       <c r="J38" t="n">
-        <v>2.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="L38" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>7.31</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>300196</t>
+          <t>000796</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,32 +2516,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>长海股份</t>
+          <t>凯撒旅业</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>18.32</v>
+        <v>5.4</v>
       </c>
       <c r="F39" t="n">
-        <v>18.23</v>
+        <v>5.37</v>
       </c>
       <c r="G39" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="H39" t="n">
-        <v>17.68</v>
+        <v>5.21</v>
       </c>
       <c r="I39" t="n">
-        <v>4.45</v>
+        <v>3.05</v>
       </c>
       <c r="J39" t="n">
-        <v>6.41</v>
+        <v>4.07</v>
       </c>
       <c r="K39" t="n">
-        <v>3.03</v>
+        <v>2.64</v>
       </c>
       <c r="L39" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>6.88</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>688679</t>
+          <t>002201</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>通源环境</t>
+          <t>九鼎新材</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>58.23</v>
+        <v>11.58</v>
       </c>
       <c r="F40" t="n">
-        <v>57.94</v>
+        <v>11.52</v>
       </c>
       <c r="G40" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="H40" t="n">
-        <v>56.2</v>
+        <v>11.17</v>
       </c>
       <c r="I40" t="n">
-        <v>4.92</v>
+        <v>3.39</v>
       </c>
       <c r="J40" t="n">
-        <v>3.91</v>
+        <v>5.09</v>
       </c>
       <c r="K40" t="n">
-        <v>2.96</v>
+        <v>2.22</v>
       </c>
       <c r="L40" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>7.05</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>300990</t>
+          <t>688239</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2624,32 +2624,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>同飞股份</t>
+          <t>航宇科技</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>86.69</v>
+        <v>61.57</v>
       </c>
       <c r="F41" t="n">
-        <v>86.26000000000001</v>
+        <v>61.26</v>
       </c>
       <c r="G41" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="H41" t="n">
-        <v>83.67</v>
+        <v>59.42</v>
       </c>
       <c r="I41" t="n">
-        <v>5.36</v>
+        <v>3.92</v>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="K41" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="L41" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>7.88</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>300121</t>
+          <t>000949</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2678,32 +2678,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>阳谷华泰</t>
+          <t>新乡化纤</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13.04</v>
+        <v>7.81</v>
       </c>
       <c r="F42" t="n">
-        <v>12.97</v>
+        <v>7.77</v>
       </c>
       <c r="G42" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="H42" t="n">
-        <v>12.58</v>
+        <v>7.54</v>
       </c>
       <c r="I42" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="J42" t="n">
-        <v>4.42</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.28</v>
+        <v>1.41</v>
       </c>
       <c r="L42" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>5.96</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>002201</t>
+          <t>301667</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
+          <t>纳百川</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>11.63</v>
+        <v>85.5</v>
       </c>
       <c r="F43" t="n">
-        <v>11.57</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G43" t="n">
         <v>3.8</v>
       </c>
       <c r="H43" t="n">
-        <v>11.22</v>
+        <v>82.52</v>
       </c>
       <c r="I43" t="n">
-        <v>3.84</v>
+        <v>4.37</v>
       </c>
       <c r="J43" t="n">
-        <v>4.95</v>
+        <v>19.68</v>
       </c>
       <c r="K43" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="L43" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>8.289999999999999</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>688202</t>
+          <t>002718</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>美迪西</t>
+          <t>友邦吊顶</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>68.55</v>
+        <v>78.56</v>
       </c>
       <c r="F44" t="n">
-        <v>68.20999999999999</v>
+        <v>78.17</v>
       </c>
       <c r="G44" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H44" t="n">
-        <v>66.16</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>4.18</v>
+        <v>3.22</v>
       </c>
       <c r="J44" t="n">
-        <v>3.5</v>
+        <v>4.46</v>
       </c>
       <c r="K44" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="L44" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>7.61</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>301468</t>
+          <t>688543</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2840,32 +2840,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>博盈特焊</t>
+          <t>国科军工</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>51.53</v>
+        <v>71.2</v>
       </c>
       <c r="F45" t="n">
-        <v>51.27</v>
+        <v>70.84</v>
       </c>
       <c r="G45" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H45" t="n">
-        <v>49.73</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>3.62</v>
+        <v>4.03</v>
       </c>
       <c r="J45" t="n">
-        <v>9.5</v>
+        <v>4.26</v>
       </c>
       <c r="K45" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="L45" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>8.859999999999999</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>301667</t>
+          <t>301509</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2894,32 +2894,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>纳百川</t>
+          <t>金凯生科</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>85.84999999999999</v>
+        <v>43.47</v>
       </c>
       <c r="F46" t="n">
-        <v>85.42</v>
+        <v>43.25</v>
       </c>
       <c r="G46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>82.86</v>
+        <v>41.95</v>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="J46" t="n">
-        <v>19.11</v>
+        <v>15.76</v>
       </c>
       <c r="K46" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="L46" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>8.74</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>300731</t>
+          <t>603196</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2948,32 +2948,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>科创新源</t>
+          <t>璞源材料</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>69.09</v>
+        <v>32.54</v>
       </c>
       <c r="F47" t="n">
-        <v>68.73999999999999</v>
+        <v>32.38</v>
       </c>
       <c r="G47" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="H47" t="n">
-        <v>66.68000000000001</v>
+        <v>31.41</v>
       </c>
       <c r="I47" t="n">
-        <v>4.32</v>
+        <v>3.86</v>
       </c>
       <c r="J47" t="n">
-        <v>5.18</v>
+        <v>3.99</v>
       </c>
       <c r="K47" t="n">
-        <v>1.42</v>
+        <v>2.32</v>
       </c>
       <c r="L47" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>10.21</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>002718</t>
+          <t>688135</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3002,32 +3002,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>友邦吊顶</t>
+          <t>利扬芯片</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>79.45999999999999</v>
+        <v>29.98</v>
       </c>
       <c r="F48" t="n">
-        <v>79.06</v>
+        <v>29.83</v>
       </c>
       <c r="G48" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H48" t="n">
-        <v>76.69</v>
+        <v>28.94</v>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>3.27</v>
       </c>
       <c r="J48" t="n">
-        <v>4.36</v>
+        <v>4.52</v>
       </c>
       <c r="K48" t="n">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="L48" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>7.74</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>688239</t>
+          <t>300731</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3056,32 +3056,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>航宇科技</t>
+          <t>科创新源</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>61.7</v>
+        <v>69.31</v>
       </c>
       <c r="F49" t="n">
-        <v>61.39</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H49" t="n">
-        <v>59.55</v>
+        <v>66.89</v>
       </c>
       <c r="I49" t="n">
-        <v>4.14</v>
+        <v>4.65</v>
       </c>
       <c r="J49" t="n">
-        <v>2.67</v>
+        <v>5.29</v>
       </c>
       <c r="K49" t="n">
-        <v>2.43</v>
+        <v>1.34</v>
       </c>
       <c r="L49" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3089,13 +3089,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>7.52</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>600841</t>
+          <t>002427</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>动力新科</t>
+          <t>尤夫股份</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9.449999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="F50" t="n">
-        <v>9.4</v>
+        <v>6.67</v>
       </c>
       <c r="G50" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>9.119999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="I50" t="n">
-        <v>4.77</v>
+        <v>4.04</v>
       </c>
       <c r="J50" t="n">
-        <v>3.02</v>
+        <v>4.21</v>
       </c>
       <c r="K50" t="n">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="L50" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>7</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>000796</t>
+          <t>603716</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>凯撒旅业</t>
+          <t>塞力医疗</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.43</v>
+        <v>23.48</v>
       </c>
       <c r="F51" t="n">
-        <v>5.4</v>
+        <v>23.36</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="H51" t="n">
-        <v>5.24</v>
+        <v>22.66</v>
       </c>
       <c r="I51" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="J51" t="n">
-        <v>3.83</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>2.71</v>
+        <v>1.12</v>
       </c>
       <c r="L51" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>6.57</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>688543</t>
+          <t>300617</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>国科军工</t>
+          <t>安靠智电</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>71.22</v>
+        <v>59.12</v>
       </c>
       <c r="F52" t="n">
-        <v>70.86</v>
+        <v>58.82</v>
       </c>
       <c r="G52" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="H52" t="n">
-        <v>68.73</v>
+        <v>57.06</v>
       </c>
       <c r="I52" t="n">
-        <v>4.06</v>
+        <v>3.18</v>
       </c>
       <c r="J52" t="n">
-        <v>4.09</v>
+        <v>4.54</v>
       </c>
       <c r="K52" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="L52" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3251,13 +3251,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>7.96</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>301509</t>
+          <t>300191</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3272,32 +3272,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>金凯生科</t>
+          <t>潜能恒信</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>44.08</v>
+        <v>40.14</v>
       </c>
       <c r="F53" t="n">
-        <v>43.86</v>
+        <v>39.94</v>
       </c>
       <c r="G53" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="H53" t="n">
-        <v>42.54</v>
+        <v>38.74</v>
       </c>
       <c r="I53" t="n">
-        <v>6.65</v>
+        <v>3.51</v>
       </c>
       <c r="J53" t="n">
-        <v>15.17</v>
+        <v>5.11</v>
       </c>
       <c r="K53" t="n">
-        <v>1.81</v>
+        <v>1.03</v>
       </c>
       <c r="L53" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>8.789999999999999</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>301319</t>
+          <t>002550</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3326,32 +3326,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>唯特偶</t>
+          <t>千红制药</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>50.83</v>
+        <v>7.86</v>
       </c>
       <c r="F54" t="n">
-        <v>50.58</v>
+        <v>7.82</v>
       </c>
       <c r="G54" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="H54" t="n">
-        <v>49.06</v>
+        <v>7.59</v>
       </c>
       <c r="I54" t="n">
-        <v>4.48</v>
+        <v>3.69</v>
       </c>
       <c r="J54" t="n">
-        <v>5.32</v>
+        <v>4.29</v>
       </c>
       <c r="K54" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="L54" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3359,13 +3359,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>603196</t>
+          <t>000722</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3380,32 +3380,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>璞源材料</t>
+          <t>湖南发展</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>32.52</v>
+        <v>13.04</v>
       </c>
       <c r="F55" t="n">
-        <v>32.36</v>
+        <v>12.97</v>
       </c>
       <c r="G55" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="H55" t="n">
-        <v>31.39</v>
+        <v>12.58</v>
       </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
-        <v>3.81</v>
+        <v>5.92</v>
       </c>
       <c r="K55" t="n">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="L55" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>7</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>002437</t>
+          <t>300868</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>誉衡药业</t>
+          <t>杰美特</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3.75</v>
+        <v>60.68</v>
       </c>
       <c r="F56" t="n">
-        <v>3.73</v>
+        <v>60.38</v>
       </c>
       <c r="G56" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="H56" t="n">
-        <v>3.62</v>
+        <v>58.57</v>
       </c>
       <c r="I56" t="n">
-        <v>4.17</v>
+        <v>5.95</v>
       </c>
       <c r="J56" t="n">
-        <v>6.04</v>
+        <v>6.24</v>
       </c>
       <c r="K56" t="n">
-        <v>0.87</v>
+        <v>2.02</v>
       </c>
       <c r="L56" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>10.82</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>002427</t>
+          <t>603367</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>尤夫股份</t>
+          <t>辰欣药业</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6.77</v>
+        <v>16.53</v>
       </c>
       <c r="F57" t="n">
-        <v>6.74</v>
+        <v>16.45</v>
       </c>
       <c r="G57" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="H57" t="n">
-        <v>6.54</v>
+        <v>15.96</v>
       </c>
       <c r="I57" t="n">
-        <v>5.12</v>
+        <v>4.55</v>
       </c>
       <c r="J57" t="n">
-        <v>4.03</v>
+        <v>3.76</v>
       </c>
       <c r="K57" t="n">
-        <v>2.59</v>
+        <v>2.07</v>
       </c>
       <c r="L57" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3521,13 +3521,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>6.2</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>000593</t>
+          <t>300315</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>德龙汇能</t>
+          <t>掌趣科技</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>17.39</v>
+        <v>4.99</v>
       </c>
       <c r="F58" t="n">
-        <v>17.3</v>
+        <v>4.97</v>
       </c>
       <c r="G58" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="H58" t="n">
-        <v>16.78</v>
+        <v>4.82</v>
       </c>
       <c r="I58" t="n">
-        <v>3.02</v>
+        <v>3.53</v>
       </c>
       <c r="J58" t="n">
-        <v>6.61</v>
+        <v>2.46</v>
       </c>
       <c r="K58" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="L58" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>9.609999999999999</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>603716</t>
+          <t>002705</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>塞力医疗</t>
+          <t>新宝股份</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>23.8</v>
+        <v>15.38</v>
       </c>
       <c r="F59" t="n">
-        <v>23.68</v>
+        <v>15.3</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H59" t="n">
-        <v>22.97</v>
+        <v>14.84</v>
       </c>
       <c r="I59" t="n">
-        <v>4.75</v>
+        <v>3.01</v>
       </c>
       <c r="J59" t="n">
-        <v>8.06</v>
+        <v>2.31</v>
       </c>
       <c r="K59" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>9.76</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>300267</t>
+          <t>002970</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3650,32 +3650,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>尔康制药</t>
+          <t>锐明技术</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.04</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>4.02</v>
+        <v>67.37</v>
       </c>
       <c r="G60" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H60" t="n">
-        <v>3.9</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>3.59</v>
+        <v>3.04</v>
       </c>
       <c r="J60" t="n">
-        <v>5.29</v>
+        <v>3.43</v>
       </c>
       <c r="K60" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="L60" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>7.22</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>000722</t>
+          <t>603227</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>湖南发展</t>
+          <t>雪峰科技</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>13.07</v>
+        <v>10.55</v>
       </c>
       <c r="F61" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="G61" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H61" t="n">
-        <v>12.61</v>
+        <v>10.18</v>
       </c>
       <c r="I61" t="n">
-        <v>3.24</v>
+        <v>3.94</v>
       </c>
       <c r="J61" t="n">
-        <v>5.78</v>
+        <v>2.85</v>
       </c>
       <c r="K61" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="L61" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3737,13 +3737,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>8.33</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>300617</t>
+          <t>301080</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3758,32 +3758,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>安靠智电</t>
+          <t>百普赛斯</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>59.36</v>
+        <v>49.12</v>
       </c>
       <c r="F62" t="n">
-        <v>59.06</v>
+        <v>48.87</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="H62" t="n">
-        <v>57.29</v>
+        <v>47.4</v>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="J62" t="n">
-        <v>4.36</v>
+        <v>4.47</v>
       </c>
       <c r="K62" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="L62" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>8.51</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>300842</t>
+          <t>688559</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3812,32 +3812,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>帝科股份</t>
+          <t>海目星</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>85</v>
+        <v>55.16</v>
       </c>
       <c r="F63" t="n">
-        <v>84.58</v>
+        <v>54.88</v>
       </c>
       <c r="G63" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="H63" t="n">
-        <v>82.04000000000001</v>
+        <v>53.23</v>
       </c>
       <c r="I63" t="n">
-        <v>3.43</v>
+        <v>4.41</v>
       </c>
       <c r="J63" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="K63" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="L63" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>7.48</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>002550</t>
+          <t>301251</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>千红制药</t>
+          <t>威尔高</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>7.95</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>7.91</v>
+        <v>67.09</v>
       </c>
       <c r="G64" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="H64" t="n">
-        <v>7.67</v>
+        <v>65.08</v>
       </c>
       <c r="I64" t="n">
-        <v>4.88</v>
+        <v>4.07</v>
       </c>
       <c r="J64" t="n">
-        <v>4.1</v>
+        <v>8.74</v>
       </c>
       <c r="K64" t="n">
-        <v>1.89</v>
+        <v>1.37</v>
       </c>
       <c r="L64" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>7.19</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>603367</t>
+          <t>688480</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3920,32 +3920,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>辰欣药业</t>
+          <t>赛恩斯</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>16.72</v>
+        <v>89.66</v>
       </c>
       <c r="F65" t="n">
-        <v>16.64</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H65" t="n">
-        <v>16.14</v>
+        <v>86.53</v>
       </c>
       <c r="I65" t="n">
-        <v>5.76</v>
+        <v>5.86</v>
       </c>
       <c r="J65" t="n">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="K65" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="L65" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>6.35</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>002970</t>
+          <t>002035</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3974,32 +3974,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>锐明技术</t>
+          <t>华帝股份</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>68.11</v>
+        <v>6.39</v>
       </c>
       <c r="F66" t="n">
-        <v>67.77</v>
+        <v>6.36</v>
       </c>
       <c r="G66" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="H66" t="n">
-        <v>65.73999999999999</v>
+        <v>6.17</v>
       </c>
       <c r="I66" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
-        <v>3.22</v>
+        <v>5.72</v>
       </c>
       <c r="K66" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="L66" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4007,871 +4007,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>6.41</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>002705</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>新宝股份</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="F67" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="G67" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H67" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="I67" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K67" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="L67" t="n">
-        <v>45</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>6.27</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>603227</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>雪峰科技</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="F68" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="G68" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H68" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="I68" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="J68" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L68" t="n">
-        <v>44</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>688068</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>热景生物</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="F69" t="n">
-        <v>123.78</v>
-      </c>
-      <c r="G69" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H69" t="n">
-        <v>120.07</v>
-      </c>
-      <c r="I69" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="L69" t="n">
-        <v>44</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>7.32</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>301080</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>百普赛斯</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F70" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="G70" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="I70" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="J70" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="L70" t="n">
-        <v>43</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>688499</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>利元亨</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>48.94</v>
-      </c>
-      <c r="F71" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="G71" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H71" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I71" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="K71" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="L71" t="n">
-        <v>43</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>5.02</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>300685</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>艾德生物</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="F72" t="n">
-        <v>23.56</v>
-      </c>
-      <c r="G72" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H72" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="I72" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="J72" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K72" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L72" t="n">
-        <v>43</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>301251</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>威尔高</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="F73" t="n">
-        <v>66.56999999999999</v>
-      </c>
-      <c r="G73" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H73" t="n">
-        <v>64.56999999999999</v>
-      </c>
-      <c r="I73" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J73" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L73" t="n">
-        <v>42</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>688480</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>赛恩斯</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="F74" t="n">
-        <v>87.95999999999999</v>
-      </c>
-      <c r="G74" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H74" t="n">
-        <v>85.31999999999999</v>
-      </c>
-      <c r="I74" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="J74" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L74" t="n">
-        <v>40</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>6.41</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>002035</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>华帝股份</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F75" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="G75" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H75" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="I75" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="J75" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K75" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="L75" t="n">
-        <v>39</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>6.27</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>688108</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>赛诺医疗</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="F76" t="n">
-        <v>22.11</v>
-      </c>
-      <c r="G76" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H76" t="n">
-        <v>21.45</v>
-      </c>
-      <c r="I76" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K76" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="L76" t="n">
-        <v>38</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>5.68</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>688559</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>海目星</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>54.51</v>
-      </c>
-      <c r="F77" t="n">
-        <v>54.24</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H77" t="n">
-        <v>52.61</v>
-      </c>
-      <c r="I77" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="J77" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="L77" t="n">
-        <v>38</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>5.77</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>002755</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>奥赛康</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="F78" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="G78" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H78" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="I78" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="J78" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="L78" t="n">
-        <v>38</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>300580</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>贝斯特</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>24.82</v>
-      </c>
-      <c r="F79" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G79" t="n">
-        <v>3</v>
-      </c>
-      <c r="H79" t="n">
-        <v>23.96</v>
-      </c>
-      <c r="I79" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="J79" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="L79" t="n">
-        <v>36</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>300668</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>杰恩设计</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="F80" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H80" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="I80" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L80" t="n">
-        <v>32</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>002713</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>*ST东易</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="F81" t="n">
-        <v>14.07</v>
-      </c>
-      <c r="G81" t="n">
-        <v>3</v>
-      </c>
-      <c r="H81" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="I81" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L81" t="n">
-        <v>31</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>5.14</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>003018</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>金富科技</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="F82" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="G82" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H82" t="n">
-        <v>31.46</v>
-      </c>
-      <c r="I82" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="J82" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L82" t="n">
-        <v>31</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N82" t="n">
-        <v>5.31</v>
+        <v>5.17</v>
       </c>
     </row>
   </sheetData>

--- a/Liang_61_Report.xlsx
+++ b/Liang_61_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300489</t>
+          <t>002701</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,46 +518,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>光智科技</t>
+          <t>奥瑞金</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65.08</v>
+        <v>5.43</v>
       </c>
       <c r="F2" t="n">
-        <v>64.75</v>
+        <v>5.4</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="H2" t="n">
-        <v>62.81</v>
+        <v>5.24</v>
       </c>
       <c r="I2" t="n">
-        <v>5.92</v>
+        <v>6.68</v>
       </c>
       <c r="J2" t="n">
-        <v>16.17</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>98</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>✅ 低</t>
+          <t>⚠️ 高</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>27.31</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002975</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,29 +572,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>博杰股份</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39.13</v>
+        <v>89.69</v>
       </c>
       <c r="F3" t="n">
-        <v>38.93</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>37.76</v>
+        <v>86.56</v>
       </c>
       <c r="I3" t="n">
-        <v>3.99</v>
+        <v>3.21</v>
       </c>
       <c r="J3" t="n">
-        <v>13.32</v>
+        <v>19.91</v>
       </c>
       <c r="K3" t="n">
-        <v>2.48</v>
+        <v>3.77</v>
       </c>
       <c r="L3" t="n">
         <v>98</v>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>26.13</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300769</t>
+          <t>002213</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,29 +626,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>德方纳米</t>
+          <t>大为股份</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.87</v>
+        <v>34.14</v>
       </c>
       <c r="F4" t="n">
-        <v>44.65</v>
+        <v>33.97</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>43.31</v>
+        <v>32.95</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.01</v>
       </c>
       <c r="J4" t="n">
-        <v>9.77</v>
+        <v>30.08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.41</v>
+        <v>2.27</v>
       </c>
       <c r="L4" t="n">
         <v>98</v>
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>20.47</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>002213</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,32 +680,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>大为股份</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>38.85</v>
       </c>
       <c r="F5" t="n">
-        <v>33.83</v>
+        <v>38.66</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>32.82</v>
+        <v>37.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.58</v>
+        <v>3.24</v>
       </c>
       <c r="J5" t="n">
-        <v>24.61</v>
+        <v>15.81</v>
       </c>
       <c r="K5" t="n">
-        <v>3.12</v>
+        <v>1.75</v>
       </c>
       <c r="L5" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>31.61</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>600545</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -734,32 +734,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t>德方纳米</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.15</v>
+        <v>45.13</v>
       </c>
       <c r="F6" t="n">
-        <v>4.13</v>
+        <v>44.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.01</v>
+        <v>43.55</v>
       </c>
       <c r="I6" t="n">
-        <v>5.06</v>
+        <v>6.31</v>
       </c>
       <c r="J6" t="n">
-        <v>12.22</v>
+        <v>11.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="L6" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>17.19</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300300</t>
+          <t>002104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>海峡创新</t>
+          <t>恒宝股份</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.92</v>
+        <v>16.37</v>
       </c>
       <c r="F7" t="n">
-        <v>13.85</v>
+        <v>16.29</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>13.43</v>
+        <v>15.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.11</v>
+        <v>6.37</v>
       </c>
       <c r="J7" t="n">
-        <v>12.63</v>
+        <v>11.16</v>
       </c>
       <c r="K7" t="n">
-        <v>1.33</v>
+        <v>3.12</v>
       </c>
       <c r="L7" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20.99</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>000049</t>
+          <t>603123</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,32 +842,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>德赛电池</t>
+          <t>翠微股份</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26.97</v>
+        <v>13.57</v>
       </c>
       <c r="F8" t="n">
-        <v>26.84</v>
+        <v>13.5</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="H8" t="n">
-        <v>26.03</v>
+        <v>13.1</v>
       </c>
       <c r="I8" t="n">
-        <v>6.01</v>
+        <v>5.69</v>
       </c>
       <c r="J8" t="n">
-        <v>6.24</v>
+        <v>15.98</v>
       </c>
       <c r="K8" t="n">
-        <v>4.61</v>
+        <v>1.83</v>
       </c>
       <c r="L8" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11.97</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="9">
@@ -900,28 +900,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13.49</v>
+        <v>13.68</v>
       </c>
       <c r="F9" t="n">
-        <v>13.42</v>
+        <v>13.61</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>13.02</v>
+        <v>13.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>6.38</v>
       </c>
       <c r="J9" t="n">
-        <v>6.43</v>
+        <v>8.33</v>
       </c>
       <c r="K9" t="n">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="L9" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>15.11</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>002733</t>
+          <t>600545</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -950,32 +950,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29.23</v>
+        <v>4.12</v>
       </c>
       <c r="F10" t="n">
-        <v>29.08</v>
+        <v>4.1</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="H10" t="n">
-        <v>28.21</v>
+        <v>3.98</v>
       </c>
       <c r="I10" t="n">
-        <v>6.29</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>8.199999999999999</v>
+        <v>13.57</v>
       </c>
       <c r="K10" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="L10" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>002083</t>
+          <t>300348</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,32 +1004,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>孚日股份</t>
+          <t>长亮科技</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.86</v>
+        <v>14.59</v>
       </c>
       <c r="F11" t="n">
-        <v>12.8</v>
+        <v>14.52</v>
       </c>
       <c r="G11" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="H11" t="n">
-        <v>12.42</v>
+        <v>14.08</v>
       </c>
       <c r="I11" t="n">
-        <v>7.17</v>
+        <v>6.96</v>
       </c>
       <c r="J11" t="n">
-        <v>7.07</v>
+        <v>8.41</v>
       </c>
       <c r="K11" t="n">
-        <v>2.27</v>
+        <v>2.91</v>
       </c>
       <c r="L11" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>15.59</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>300302</t>
+          <t>300315</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1058,32 +1058,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>掌趣科技</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22.66</v>
+        <v>5.14</v>
       </c>
       <c r="F12" t="n">
-        <v>22.55</v>
+        <v>5.11</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="H12" t="n">
-        <v>21.87</v>
+        <v>4.96</v>
       </c>
       <c r="I12" t="n">
-        <v>3.56</v>
+        <v>6.64</v>
       </c>
       <c r="J12" t="n">
-        <v>10.38</v>
+        <v>6.47</v>
       </c>
       <c r="K12" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="L12" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>16.08</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>601311</t>
+          <t>002083</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>骆驼股份</t>
+          <t>孚日股份</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.93</v>
+        <v>12.85</v>
       </c>
       <c r="F13" t="n">
-        <v>9.880000000000001</v>
+        <v>12.79</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="n">
-        <v>9.58</v>
+        <v>12.41</v>
       </c>
       <c r="I13" t="n">
-        <v>4.75</v>
+        <v>7.08</v>
       </c>
       <c r="J13" t="n">
-        <v>4.11</v>
+        <v>8.9</v>
       </c>
       <c r="K13" t="n">
-        <v>4.59</v>
+        <v>1.7</v>
       </c>
       <c r="L13" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>8.869999999999999</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>300377</t>
+          <t>000049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>赢时胜</t>
+          <t>德赛电池</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18.44</v>
+        <v>26.95</v>
       </c>
       <c r="F14" t="n">
-        <v>18.35</v>
+        <v>26.82</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>17.8</v>
+        <v>26.02</v>
       </c>
       <c r="I14" t="n">
-        <v>3.54</v>
+        <v>5.94</v>
       </c>
       <c r="J14" t="n">
-        <v>5.29</v>
+        <v>6.78</v>
       </c>
       <c r="K14" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="L14" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>12.53</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>300671</t>
+          <t>600590</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1220,32 +1220,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>富满微</t>
+          <t>泰豪科技</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41.94</v>
+        <v>14.91</v>
       </c>
       <c r="F15" t="n">
-        <v>41.73</v>
+        <v>14.84</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>40.48</v>
+        <v>14.39</v>
       </c>
       <c r="I15" t="n">
-        <v>3.33</v>
+        <v>5.67</v>
       </c>
       <c r="J15" t="n">
-        <v>6.39</v>
+        <v>8.31</v>
       </c>
       <c r="K15" t="n">
-        <v>3.13</v>
+        <v>1.42</v>
       </c>
       <c r="L15" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>11.02</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>600590</t>
+          <t>601311</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,32 +1274,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>泰豪科技</t>
+          <t>骆驼股份</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14.87</v>
+        <v>9.99</v>
       </c>
       <c r="F16" t="n">
-        <v>14.8</v>
+        <v>9.94</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>14.36</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>4.99</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8</v>
+        <v>3.31</v>
       </c>
       <c r="L16" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>14.2</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>002528</t>
+          <t>002667</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,32 +1328,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ST英飞拓</t>
+          <t>威领股份</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.83</v>
+        <v>26.66</v>
       </c>
       <c r="F17" t="n">
-        <v>4.81</v>
+        <v>26.53</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.67</v>
+        <v>25.73</v>
       </c>
       <c r="I17" t="n">
-        <v>4.55</v>
+        <v>6.64</v>
       </c>
       <c r="J17" t="n">
-        <v>6.77</v>
+        <v>12.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.94</v>
+        <v>2.49</v>
       </c>
       <c r="L17" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6.3</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>600078</t>
+          <t>002617</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1382,32 +1382,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>澄星股份</t>
+          <t>露笑科技</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.52</v>
+        <v>7.64</v>
       </c>
       <c r="F18" t="n">
-        <v>12.46</v>
+        <v>7.6</v>
       </c>
       <c r="G18" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>12.09</v>
+        <v>7.37</v>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>4.51</v>
       </c>
       <c r="J18" t="n">
-        <v>6.12</v>
+        <v>5.77</v>
       </c>
       <c r="K18" t="n">
-        <v>3.72</v>
+        <v>2.13</v>
       </c>
       <c r="L18" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>9.35</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>002617</t>
+          <t>300377</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,32 +1436,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>赢时胜</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.68</v>
+        <v>18.42</v>
       </c>
       <c r="F19" t="n">
-        <v>7.64</v>
+        <v>18.33</v>
       </c>
       <c r="G19" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>7.41</v>
+        <v>17.78</v>
       </c>
       <c r="I19" t="n">
-        <v>5.06</v>
+        <v>3.43</v>
       </c>
       <c r="J19" t="n">
-        <v>4.41</v>
+        <v>6.51</v>
       </c>
       <c r="K19" t="n">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="L19" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>11.59</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>300706</t>
+          <t>300671</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,32 +1490,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>阿石创</t>
+          <t>富满微</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>38.58</v>
+        <v>42.24</v>
       </c>
       <c r="F20" t="n">
-        <v>38.39</v>
+        <v>42.03</v>
       </c>
       <c r="G20" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="H20" t="n">
-        <v>37.24</v>
+        <v>40.77</v>
       </c>
       <c r="I20" t="n">
-        <v>3.77</v>
+        <v>4.07</v>
       </c>
       <c r="J20" t="n">
-        <v>14.16</v>
+        <v>8.09</v>
       </c>
       <c r="K20" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="L20" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>11.68</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>002164</t>
+          <t>002017</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>东信和平</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13.31</v>
+        <v>19.8</v>
       </c>
       <c r="F21" t="n">
-        <v>13.24</v>
+        <v>19.7</v>
       </c>
       <c r="G21" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="H21" t="n">
-        <v>12.84</v>
+        <v>19.11</v>
       </c>
       <c r="I21" t="n">
-        <v>4.47</v>
+        <v>3.56</v>
       </c>
       <c r="J21" t="n">
-        <v>5.32</v>
+        <v>4.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4.25</v>
+        <v>3.08</v>
       </c>
       <c r="L21" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>603387</t>
+          <t>300480</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,32 +1598,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>基蛋生物</t>
+          <t>光力科技</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10.24</v>
+        <v>33.58</v>
       </c>
       <c r="F22" t="n">
-        <v>10.19</v>
+        <v>33.41</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H22" t="n">
-        <v>9.880000000000001</v>
+        <v>32.41</v>
       </c>
       <c r="I22" t="n">
-        <v>5.03</v>
+        <v>6.67</v>
       </c>
       <c r="J22" t="n">
-        <v>10.49</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="L22" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>10.17</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>600382</t>
+          <t>603052</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1652,32 +1652,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>广东明珠</t>
+          <t>可川科技</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.5</v>
+        <v>69.5</v>
       </c>
       <c r="F23" t="n">
-        <v>9.449999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="H23" t="n">
-        <v>9.17</v>
+        <v>67.08</v>
       </c>
       <c r="I23" t="n">
-        <v>5.67</v>
+        <v>4.89</v>
       </c>
       <c r="J23" t="n">
-        <v>4.98</v>
+        <v>6.61</v>
       </c>
       <c r="K23" t="n">
-        <v>3.77</v>
+        <v>1.65</v>
       </c>
       <c r="L23" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.03</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>301196</t>
+          <t>600078</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1706,32 +1706,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>唯科科技</t>
+          <t>澄星股份</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>111.1</v>
+        <v>12.48</v>
       </c>
       <c r="F24" t="n">
-        <v>110.54</v>
+        <v>12.42</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="H24" t="n">
-        <v>107.22</v>
+        <v>12.05</v>
       </c>
       <c r="I24" t="n">
-        <v>3.54</v>
+        <v>4.96</v>
       </c>
       <c r="J24" t="n">
-        <v>6.61</v>
+        <v>6.96</v>
       </c>
       <c r="K24" t="n">
-        <v>1.82</v>
+        <v>2.52</v>
       </c>
       <c r="L24" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>10.92</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>002196</t>
+          <t>301196</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,32 +1760,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>方正电机</t>
+          <t>唯科科技</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>14.4</v>
+        <v>111.48</v>
       </c>
       <c r="F25" t="n">
-        <v>14.33</v>
+        <v>110.92</v>
       </c>
       <c r="G25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="H25" t="n">
-        <v>13.9</v>
+        <v>107.59</v>
       </c>
       <c r="I25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
-        <v>5.92</v>
+        <v>8.91</v>
       </c>
       <c r="K25" t="n">
-        <v>2.94</v>
+        <v>1.46</v>
       </c>
       <c r="L25" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>7.68</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>002380</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>科远智慧</t>
+          <t>力诺药包</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>34.84</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>34.67</v>
+        <v>24.88</v>
       </c>
       <c r="G26" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H26" t="n">
-        <v>33.63</v>
+        <v>24.13</v>
       </c>
       <c r="I26" t="n">
-        <v>4.06</v>
+        <v>3.91</v>
       </c>
       <c r="J26" t="n">
-        <v>6.83</v>
+        <v>13.95</v>
       </c>
       <c r="K26" t="n">
-        <v>3.44</v>
+        <v>0.89</v>
       </c>
       <c r="L26" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>300191</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,32 +1868,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>潜能恒信</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>63.66</v>
+        <v>41.5</v>
       </c>
       <c r="F27" t="n">
-        <v>63.34</v>
+        <v>41.29</v>
       </c>
       <c r="G27" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="H27" t="n">
-        <v>61.44</v>
+        <v>40.05</v>
       </c>
       <c r="I27" t="n">
-        <v>6.99</v>
+        <v>7.01</v>
       </c>
       <c r="J27" t="n">
-        <v>4.38</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>3.02</v>
+        <v>1.14</v>
       </c>
       <c r="L27" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>7.23</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>000525</t>
+          <t>688693</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1922,32 +1922,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>红太阳</t>
+          <t>锴威特</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.22</v>
+        <v>81.67</v>
       </c>
       <c r="F28" t="n">
-        <v>6.19</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>3.32</v>
+        <v>4.04</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>22.37</v>
       </c>
       <c r="K28" t="n">
-        <v>3.74</v>
+        <v>1.32</v>
       </c>
       <c r="L28" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>5.37</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002896</t>
+          <t>002196</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>中大力德</t>
+          <t>方正电机</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>74.58</v>
+        <v>14.39</v>
       </c>
       <c r="F29" t="n">
-        <v>74.20999999999999</v>
+        <v>14.32</v>
       </c>
       <c r="G29" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H29" t="n">
-        <v>71.98</v>
+        <v>13.89</v>
       </c>
       <c r="I29" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="J29" t="n">
-        <v>3.01</v>
+        <v>7.28</v>
       </c>
       <c r="K29" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="L29" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>8.17</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>688661</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,32 +2030,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>和林微纳</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>88.09</v>
+        <v>63.23</v>
       </c>
       <c r="F30" t="n">
-        <v>87.65000000000001</v>
+        <v>62.91</v>
       </c>
       <c r="G30" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H30" t="n">
-        <v>85.02</v>
+        <v>61.02</v>
       </c>
       <c r="I30" t="n">
-        <v>6.39</v>
+        <v>6.27</v>
       </c>
       <c r="J30" t="n">
-        <v>3.27</v>
+        <v>5.25</v>
       </c>
       <c r="K30" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="L30" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>8.029999999999999</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>301487</t>
+          <t>603387</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>盟固利</t>
+          <t>基蛋生物</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>21.15</v>
+        <v>10.18</v>
       </c>
       <c r="F31" t="n">
-        <v>21.04</v>
+        <v>10.13</v>
       </c>
       <c r="G31" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H31" t="n">
-        <v>20.41</v>
+        <v>9.83</v>
       </c>
       <c r="I31" t="n">
-        <v>3.17</v>
+        <v>4.41</v>
       </c>
       <c r="J31" t="n">
-        <v>5.35</v>
+        <v>12.13</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>1.51</v>
       </c>
       <c r="L31" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>5.75</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>002283</t>
+          <t>605289</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2138,32 +2138,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>天润工业</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.66</v>
+        <v>114.91</v>
       </c>
       <c r="F32" t="n">
-        <v>10.61</v>
+        <v>114.34</v>
       </c>
       <c r="G32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H32" t="n">
-        <v>10.29</v>
+        <v>110.91</v>
       </c>
       <c r="I32" t="n">
-        <v>6.07</v>
+        <v>3.47</v>
       </c>
       <c r="J32" t="n">
-        <v>4.49</v>
+        <v>5.77</v>
       </c>
       <c r="K32" t="n">
-        <v>1.88</v>
+        <v>0.97</v>
       </c>
       <c r="L32" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>8.869999999999999</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>300196</t>
+          <t>688485</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,32 +2192,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>长海股份</t>
+          <t>九州一轨</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>18.34</v>
+        <v>41.04</v>
       </c>
       <c r="F33" t="n">
-        <v>18.25</v>
+        <v>40.83</v>
       </c>
       <c r="G33" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="H33" t="n">
-        <v>17.7</v>
+        <v>39.61</v>
       </c>
       <c r="I33" t="n">
-        <v>4.56</v>
+        <v>3.38</v>
       </c>
       <c r="J33" t="n">
-        <v>6.53</v>
+        <v>19.67</v>
       </c>
       <c r="K33" t="n">
-        <v>2.85</v>
+        <v>1.09</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>5.45</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>688679</t>
+          <t>002537</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>通源环境</t>
+          <t>海联金汇</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>58.34</v>
+        <v>8.09</v>
       </c>
       <c r="F34" t="n">
-        <v>58.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="H34" t="n">
-        <v>56.31</v>
+        <v>7.81</v>
       </c>
       <c r="I34" t="n">
-        <v>5.12</v>
+        <v>3.72</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>5.99</v>
       </c>
       <c r="K34" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="L34" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2279,13 +2279,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>5.61</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>300990</t>
+          <t>002283</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2300,32 +2300,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>同飞股份</t>
+          <t>天润工业</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>86.83</v>
+        <v>10.58</v>
       </c>
       <c r="F35" t="n">
-        <v>86.40000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="G35" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="H35" t="n">
-        <v>83.81</v>
+        <v>10.21</v>
       </c>
       <c r="I35" t="n">
-        <v>5.53</v>
+        <v>5.27</v>
       </c>
       <c r="J35" t="n">
-        <v>5.16</v>
+        <v>5.62</v>
       </c>
       <c r="K35" t="n">
-        <v>2.51</v>
+        <v>1.4</v>
       </c>
       <c r="L35" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>6.32</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>688202</t>
+          <t>688661</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>美迪西</t>
+          <t>和林微纳</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>68</v>
+        <v>87.12</v>
       </c>
       <c r="F36" t="n">
-        <v>67.66</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>65.63</v>
+        <v>84.08</v>
       </c>
       <c r="I36" t="n">
-        <v>3.34</v>
+        <v>5.22</v>
       </c>
       <c r="J36" t="n">
-        <v>3.59</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="L36" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>6.07</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>600841</t>
+          <t>600478</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2408,32 +2408,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>动力新科</t>
+          <t>科力远</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9.390000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="F37" t="n">
-        <v>9.34</v>
+        <v>7.43</v>
       </c>
       <c r="G37" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H37" t="n">
-        <v>9.06</v>
+        <v>7.21</v>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
       <c r="J37" t="n">
-        <v>3.15</v>
+        <v>3.79</v>
       </c>
       <c r="K37" t="n">
-        <v>2.59</v>
+        <v>1.74</v>
       </c>
       <c r="L37" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5.67</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>301468</t>
+          <t>603985</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2462,32 +2462,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>博盈特焊</t>
+          <t>恒润股份</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>51.59</v>
+        <v>21.08</v>
       </c>
       <c r="F38" t="n">
-        <v>51.33</v>
+        <v>20.97</v>
       </c>
       <c r="G38" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H38" t="n">
-        <v>49.79</v>
+        <v>20.34</v>
       </c>
       <c r="I38" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="J38" t="n">
-        <v>9.800000000000001</v>
+        <v>7.51</v>
       </c>
       <c r="K38" t="n">
-        <v>2.05</v>
+        <v>0.76</v>
       </c>
       <c r="L38" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>7.09</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>000796</t>
+          <t>301095</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,32 +2516,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>凯撒旅业</t>
+          <t>广立微</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5.4</v>
+        <v>72.88</v>
       </c>
       <c r="F39" t="n">
-        <v>5.37</v>
+        <v>72.52</v>
       </c>
       <c r="G39" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H39" t="n">
-        <v>5.21</v>
+        <v>70.34</v>
       </c>
       <c r="I39" t="n">
-        <v>3.05</v>
+        <v>4.19</v>
       </c>
       <c r="J39" t="n">
-        <v>4.07</v>
+        <v>3.63</v>
       </c>
       <c r="K39" t="n">
-        <v>2.64</v>
+        <v>1.41</v>
       </c>
       <c r="L39" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>002201</t>
+          <t>300731</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
+          <t>科创新源</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11.58</v>
+        <v>69.61</v>
       </c>
       <c r="F40" t="n">
-        <v>11.52</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H40" t="n">
-        <v>11.17</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>3.39</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
-        <v>5.09</v>
+        <v>6.72</v>
       </c>
       <c r="K40" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="L40" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>6.62</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>688239</t>
+          <t>301509</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2624,32 +2624,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>航宇科技</t>
+          <t>金凯生科</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>61.57</v>
+        <v>43.02</v>
       </c>
       <c r="F41" t="n">
-        <v>61.26</v>
+        <v>42.8</v>
       </c>
       <c r="G41" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>59.42</v>
+        <v>41.52</v>
       </c>
       <c r="I41" t="n">
-        <v>3.92</v>
+        <v>4.09</v>
       </c>
       <c r="J41" t="n">
-        <v>2.74</v>
+        <v>18.85</v>
       </c>
       <c r="K41" t="n">
-        <v>2.34</v>
+        <v>1.24</v>
       </c>
       <c r="L41" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>5.99</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>000949</t>
+          <t>605162</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2678,32 +2678,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>新乡化纤</t>
+          <t>新中港</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7.81</v>
+        <v>14.66</v>
       </c>
       <c r="F42" t="n">
-        <v>7.77</v>
+        <v>14.59</v>
       </c>
       <c r="G42" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H42" t="n">
-        <v>7.54</v>
+        <v>14.15</v>
       </c>
       <c r="I42" t="n">
-        <v>3.03</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.5</v>
+        <v>9.51</v>
       </c>
       <c r="K42" t="n">
-        <v>1.41</v>
+        <v>0.75</v>
       </c>
       <c r="L42" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2711,1303 +2711,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>301667</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>纳百川</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="F43" t="n">
-        <v>85.06999999999999</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H43" t="n">
-        <v>82.52</v>
-      </c>
-      <c r="I43" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="J43" t="n">
-        <v>19.68</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="L43" t="n">
-        <v>47</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>002718</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>友邦吊顶</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="F44" t="n">
-        <v>78.17</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H44" t="n">
-        <v>75.81999999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="J44" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="L44" t="n">
-        <v>46</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>6.16</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>688543</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>国科军工</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>70.84</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H45" t="n">
-        <v>68.70999999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J45" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="L45" t="n">
-        <v>46</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>6.44</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>301509</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>金凯生科</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>43.47</v>
-      </c>
-      <c r="F46" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="G46" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>41.95</v>
-      </c>
-      <c r="I46" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="J46" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="L46" t="n">
-        <v>45</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>603196</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>璞源材料</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>32.54</v>
-      </c>
-      <c r="F47" t="n">
-        <v>32.38</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="I47" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="L47" t="n">
-        <v>45</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>5.69</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>688135</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>利扬芯片</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="F48" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H48" t="n">
-        <v>28.94</v>
-      </c>
-      <c r="I48" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="J48" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="L48" t="n">
-        <v>45</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>5.77</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>300731</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>科创新源</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>69.31</v>
-      </c>
-      <c r="F49" t="n">
-        <v>68.95999999999999</v>
-      </c>
-      <c r="G49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H49" t="n">
-        <v>66.89</v>
-      </c>
-      <c r="I49" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="J49" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="L49" t="n">
-        <v>45</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>002427</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>尤夫股份</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F50" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="G50" t="n">
-        <v>4</v>
-      </c>
-      <c r="H50" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="I50" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="J50" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="L50" t="n">
-        <v>44</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>603716</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>塞力医疗</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>23.48</v>
-      </c>
-      <c r="F51" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H51" t="n">
-        <v>22.66</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J51" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L51" t="n">
-        <v>43</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>8.050000000000001</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>300617</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>安靠智电</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="F52" t="n">
-        <v>58.82</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H52" t="n">
-        <v>57.06</v>
-      </c>
-      <c r="I52" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="J52" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="L52" t="n">
-        <v>42</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>6.89</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>300191</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>潜能恒信</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>40.14</v>
-      </c>
-      <c r="F53" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H53" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="J53" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L53" t="n">
-        <v>42</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>8.16</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>002550</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>千红制药</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="F54" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="G54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="L54" t="n">
-        <v>41</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>000722</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>湖南发展</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="F55" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H55" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="I55" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="L55" t="n">
-        <v>41</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>6.64</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>300868</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>杰美特</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>60.68</v>
-      </c>
-      <c r="F56" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="G56" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H56" t="n">
-        <v>58.57</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="J56" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="L56" t="n">
-        <v>41</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>603367</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>辰欣药业</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="F57" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H57" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="L57" t="n">
-        <v>41</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>5.17</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>300315</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>掌趣科技</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="G58" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="L58" t="n">
-        <v>41</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>5.79</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>002705</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>新宝股份</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="F59" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="G59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2</v>
-      </c>
-      <c r="L59" t="n">
-        <v>41</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N59" t="n">
-        <v>5.27</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>002970</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>锐明技术</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>67.70999999999999</v>
-      </c>
-      <c r="F60" t="n">
-        <v>67.37</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H60" t="n">
-        <v>65.34999999999999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="L60" t="n">
-        <v>40</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N60" t="n">
-        <v>5.32</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>603227</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>雪峰科技</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="F61" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H61" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="L61" t="n">
-        <v>38</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>301080</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>百普赛斯</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="F62" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="G62" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H62" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I62" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="L62" t="n">
-        <v>37</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>5.08</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>688559</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>海目星</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>55.16</v>
-      </c>
-      <c r="F63" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H63" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="L63" t="n">
-        <v>36</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>5.03</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>301251</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>威尔高</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>67.43000000000001</v>
-      </c>
-      <c r="F64" t="n">
-        <v>67.09</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H64" t="n">
-        <v>65.08</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="J64" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="L64" t="n">
-        <v>36</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>688480</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>赛恩斯</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>89.66</v>
-      </c>
-      <c r="F65" t="n">
-        <v>89.20999999999999</v>
-      </c>
-      <c r="G65" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H65" t="n">
-        <v>86.53</v>
-      </c>
-      <c r="I65" t="n">
         <v>5.86</v>
-      </c>
-      <c r="J65" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L65" t="n">
-        <v>36</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>5.26</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>002035</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>华帝股份</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="F66" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="G66" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H66" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="I66" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J66" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="L66" t="n">
-        <v>34</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>5.17</v>
       </c>
     </row>
   </sheetData>

--- a/Liang_61_Report.xlsx
+++ b/Liang_61_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,25 +522,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="G2" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="H2" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
       <c r="I2" t="n">
-        <v>6.68</v>
+        <v>6.09</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>5.11</v>
       </c>
       <c r="K2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="L2" t="n">
         <v>98</v>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>7.6</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002975</t>
+          <t>002213</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,29 +572,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>博杰股份</t>
+          <t>大为股份</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>89.69</v>
+        <v>33.87</v>
       </c>
       <c r="F3" t="n">
-        <v>89.23999999999999</v>
+        <v>33.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>86.56</v>
+        <v>32.69</v>
       </c>
       <c r="I3" t="n">
-        <v>3.21</v>
+        <v>4.18</v>
       </c>
       <c r="J3" t="n">
-        <v>19.91</v>
+        <v>32.76</v>
       </c>
       <c r="K3" t="n">
-        <v>3.77</v>
+        <v>2.26</v>
       </c>
       <c r="L3" t="n">
         <v>98</v>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.54</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>002213</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,32 +626,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大为股份</t>
+          <t>德方纳米</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34.14</v>
+        <v>44.93</v>
       </c>
       <c r="F4" t="n">
-        <v>33.97</v>
+        <v>44.71</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>32.95</v>
+        <v>43.37</v>
       </c>
       <c r="I4" t="n">
-        <v>5.01</v>
+        <v>5.84</v>
       </c>
       <c r="J4" t="n">
-        <v>30.08</v>
+        <v>12.51</v>
       </c>
       <c r="K4" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="L4" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22.98</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002104</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,32 +680,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>恒宝股份</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38.85</v>
+        <v>16.3</v>
       </c>
       <c r="F5" t="n">
-        <v>38.66</v>
+        <v>16.22</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>37.5</v>
+        <v>15.73</v>
       </c>
       <c r="I5" t="n">
-        <v>3.24</v>
+        <v>5.91</v>
       </c>
       <c r="J5" t="n">
-        <v>15.81</v>
+        <v>12.27</v>
       </c>
       <c r="K5" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>18.39</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300769</t>
+          <t>603123</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -734,32 +734,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>德方纳米</t>
+          <t>翠微股份</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45.13</v>
+        <v>13.59</v>
       </c>
       <c r="F6" t="n">
-        <v>44.9</v>
+        <v>13.52</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
-        <v>43.55</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="n">
-        <v>6.31</v>
+        <v>5.84</v>
       </c>
       <c r="J6" t="n">
-        <v>11.8</v>
+        <v>17.29</v>
       </c>
       <c r="K6" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>14.69</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>002104</t>
+          <t>600552</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>恒宝股份</t>
+          <t>凯盛科技</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.37</v>
+        <v>13.49</v>
       </c>
       <c r="F7" t="n">
-        <v>16.29</v>
+        <v>13.42</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>15.8</v>
+        <v>13.02</v>
       </c>
       <c r="I7" t="n">
-        <v>6.37</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>11.16</v>
+        <v>9.18</v>
       </c>
       <c r="K7" t="n">
-        <v>3.12</v>
+        <v>2.28</v>
       </c>
       <c r="L7" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.92</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>603123</t>
+          <t>300348</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,32 +842,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>翠微股份</t>
+          <t>长亮科技</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13.57</v>
+        <v>14.51</v>
       </c>
       <c r="F8" t="n">
-        <v>13.5</v>
+        <v>14.44</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
-        <v>13.1</v>
+        <v>14.01</v>
       </c>
       <c r="I8" t="n">
-        <v>5.69</v>
+        <v>6.38</v>
       </c>
       <c r="J8" t="n">
-        <v>15.98</v>
+        <v>9.35</v>
       </c>
       <c r="K8" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="L8" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>15.04</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>600552</t>
+          <t>300315</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -896,32 +896,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>凯盛科技</t>
+          <t>掌趣科技</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13.68</v>
+        <v>5.12</v>
       </c>
       <c r="F9" t="n">
-        <v>13.61</v>
+        <v>5.09</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
-        <v>13.2</v>
+        <v>4.94</v>
       </c>
       <c r="I9" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="J9" t="n">
-        <v>8.33</v>
+        <v>7.09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="L9" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>11.61</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="10">
@@ -954,28 +954,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="G10" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="J10" t="n">
-        <v>13.57</v>
+        <v>14.36</v>
       </c>
       <c r="K10" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="L10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>11.3</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300348</t>
+          <t>002083</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,32 +1004,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>长亮科技</t>
+          <t>孚日股份</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.59</v>
+        <v>12.82</v>
       </c>
       <c r="F11" t="n">
-        <v>14.52</v>
+        <v>12.76</v>
       </c>
       <c r="G11" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="H11" t="n">
-        <v>14.08</v>
+        <v>12.38</v>
       </c>
       <c r="I11" t="n">
-        <v>6.96</v>
+        <v>6.83</v>
       </c>
       <c r="J11" t="n">
-        <v>8.41</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>2.91</v>
+        <v>1.7</v>
       </c>
       <c r="L11" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9.31</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>300315</t>
+          <t>002667</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1058,32 +1058,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>掌趣科技</t>
+          <t>威领股份</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.14</v>
+        <v>26.25</v>
       </c>
       <c r="F12" t="n">
-        <v>5.11</v>
+        <v>26.12</v>
       </c>
       <c r="G12" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.96</v>
+        <v>25.34</v>
       </c>
       <c r="I12" t="n">
-        <v>6.64</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>6.47</v>
+        <v>14.11</v>
       </c>
       <c r="K12" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="L12" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>9.24</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>002083</t>
+          <t>300671</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>孚日股份</t>
+          <t>富满微</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.85</v>
+        <v>42.5</v>
       </c>
       <c r="F13" t="n">
-        <v>12.79</v>
+        <v>42.29</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H13" t="n">
-        <v>12.41</v>
+        <v>41.02</v>
       </c>
       <c r="I13" t="n">
-        <v>7.08</v>
+        <v>4.71</v>
       </c>
       <c r="J13" t="n">
-        <v>8.9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7</v>
+        <v>2.51</v>
       </c>
       <c r="L13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>11.69</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>000049</t>
+          <t>601311</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>德赛电池</t>
+          <t>骆驼股份</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26.95</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>26.82</v>
+        <v>9.92</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H14" t="n">
-        <v>26.02</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>5.94</v>
+        <v>5.17</v>
       </c>
       <c r="J14" t="n">
-        <v>6.78</v>
+        <v>5.52</v>
       </c>
       <c r="K14" t="n">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="L14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.73</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="15">
@@ -1224,25 +1224,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14.91</v>
+        <v>14.84</v>
       </c>
       <c r="F15" t="n">
-        <v>14.84</v>
+        <v>14.77</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="n">
-        <v>14.39</v>
+        <v>14.33</v>
       </c>
       <c r="I15" t="n">
-        <v>5.67</v>
+        <v>5.17</v>
       </c>
       <c r="J15" t="n">
-        <v>8.31</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="L15" t="n">
         <v>59</v>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>11.34</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>601311</t>
+          <t>000049</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,32 +1274,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>骆驼股份</t>
+          <t>德赛电池</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.99</v>
+        <v>26.86</v>
       </c>
       <c r="F16" t="n">
-        <v>9.94</v>
+        <v>26.73</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H16" t="n">
-        <v>9.640000000000001</v>
+        <v>25.93</v>
       </c>
       <c r="I16" t="n">
-        <v>5.38</v>
+        <v>5.58</v>
       </c>
       <c r="J16" t="n">
-        <v>4.99</v>
+        <v>7.06</v>
       </c>
       <c r="K16" t="n">
-        <v>3.31</v>
+        <v>2.85</v>
       </c>
       <c r="L16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.41</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>002667</t>
+          <t>002617</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,32 +1328,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>威领股份</t>
+          <t>露笑科技</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>26.66</v>
+        <v>7.65</v>
       </c>
       <c r="F17" t="n">
-        <v>26.53</v>
+        <v>7.61</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>25.73</v>
+        <v>7.38</v>
       </c>
       <c r="I17" t="n">
-        <v>6.64</v>
+        <v>4.65</v>
       </c>
       <c r="J17" t="n">
-        <v>12.3</v>
+        <v>6.35</v>
       </c>
       <c r="K17" t="n">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="L17" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>8.33</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>002617</t>
+          <t>603052</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1382,32 +1382,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>可川科技</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.64</v>
+        <v>69.98</v>
       </c>
       <c r="F18" t="n">
-        <v>7.6</v>
+        <v>69.63</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H18" t="n">
-        <v>7.37</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>4.51</v>
+        <v>5.61</v>
       </c>
       <c r="J18" t="n">
-        <v>5.77</v>
+        <v>7.55</v>
       </c>
       <c r="K18" t="n">
-        <v>2.13</v>
+        <v>1.72</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>9.029999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>300377</t>
+          <t>001283</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,32 +1436,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>赢时胜</t>
+          <t>豪鹏科技</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18.42</v>
+        <v>69.53</v>
       </c>
       <c r="F19" t="n">
-        <v>18.33</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="H19" t="n">
-        <v>17.78</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>3.43</v>
+        <v>7.47</v>
       </c>
       <c r="J19" t="n">
-        <v>6.51</v>
+        <v>14.04</v>
       </c>
       <c r="K19" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="L19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>9.15</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>300671</t>
+          <t>002017</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,32 +1490,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>富满微</t>
+          <t>东信和平</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>42.24</v>
+        <v>19.74</v>
       </c>
       <c r="F20" t="n">
-        <v>42.03</v>
+        <v>19.64</v>
       </c>
       <c r="G20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H20" t="n">
-        <v>40.77</v>
+        <v>19.05</v>
       </c>
       <c r="I20" t="n">
-        <v>4.07</v>
+        <v>3.24</v>
       </c>
       <c r="J20" t="n">
-        <v>8.09</v>
+        <v>5.18</v>
       </c>
       <c r="K20" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="L20" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>8.27</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>002017</t>
+          <t>300480</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>东信和平</t>
+          <t>光力科技</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19.8</v>
+        <v>33.43</v>
       </c>
       <c r="F21" t="n">
-        <v>19.7</v>
+        <v>33.26</v>
       </c>
       <c r="G21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H21" t="n">
-        <v>19.11</v>
+        <v>32.26</v>
       </c>
       <c r="I21" t="n">
-        <v>3.56</v>
+        <v>6.19</v>
       </c>
       <c r="J21" t="n">
-        <v>4.75</v>
+        <v>10.37</v>
       </c>
       <c r="K21" t="n">
-        <v>3.08</v>
+        <v>1.63</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5.99</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>300480</t>
+          <t>301362</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,32 +1598,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>光力科技</t>
+          <t>民爆光电</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>33.58</v>
+        <v>143</v>
       </c>
       <c r="F22" t="n">
-        <v>33.41</v>
+        <v>142.28</v>
       </c>
       <c r="G22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>32.41</v>
+        <v>138.01</v>
       </c>
       <c r="I22" t="n">
-        <v>6.67</v>
+        <v>4.99</v>
       </c>
       <c r="J22" t="n">
-        <v>9.470000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="K22" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>9.380000000000001</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>603052</t>
+          <t>301196</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1652,32 +1652,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>可川科技</t>
+          <t>唯科科技</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>69.5</v>
+        <v>111.2</v>
       </c>
       <c r="F23" t="n">
-        <v>69.15000000000001</v>
+        <v>110.64</v>
       </c>
       <c r="G23" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>67.08</v>
+        <v>107.32</v>
       </c>
       <c r="I23" t="n">
-        <v>4.89</v>
+        <v>3.63</v>
       </c>
       <c r="J23" t="n">
-        <v>6.61</v>
+        <v>9.85</v>
       </c>
       <c r="K23" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="L23" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>9.16</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1710,28 +1710,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>12.48</v>
+        <v>12.44</v>
       </c>
       <c r="F24" t="n">
-        <v>12.42</v>
+        <v>12.38</v>
       </c>
       <c r="G24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H24" t="n">
-        <v>12.05</v>
+        <v>12.01</v>
       </c>
       <c r="I24" t="n">
-        <v>4.96</v>
+        <v>4.63</v>
       </c>
       <c r="J24" t="n">
-        <v>6.96</v>
+        <v>7.51</v>
       </c>
       <c r="K24" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.32</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>301196</t>
+          <t>300191</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,32 +1760,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>唯科科技</t>
+          <t>潜能恒信</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>111.48</v>
+        <v>41.4</v>
       </c>
       <c r="F25" t="n">
-        <v>110.92</v>
+        <v>41.19</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="H25" t="n">
-        <v>107.59</v>
+        <v>39.95</v>
       </c>
       <c r="I25" t="n">
-        <v>3.9</v>
+        <v>6.76</v>
       </c>
       <c r="J25" t="n">
-        <v>8.91</v>
+        <v>10.35</v>
       </c>
       <c r="K25" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="L25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>8.789999999999999</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="26">
@@ -1833,13 +1833,13 @@
         <v>3.91</v>
       </c>
       <c r="J26" t="n">
-        <v>13.95</v>
+        <v>14.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="L26" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>10.26</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>300191</t>
+          <t>605222</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,32 +1868,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>潜能恒信</t>
+          <t>起帆电缆</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>41.5</v>
+        <v>24.65</v>
       </c>
       <c r="F27" t="n">
-        <v>41.29</v>
+        <v>24.53</v>
       </c>
       <c r="G27" t="n">
         <v>4.4</v>
       </c>
       <c r="H27" t="n">
-        <v>40.05</v>
+        <v>23.79</v>
       </c>
       <c r="I27" t="n">
-        <v>7.01</v>
+        <v>5.34</v>
       </c>
       <c r="J27" t="n">
-        <v>9.550000000000001</v>
+        <v>5.93</v>
       </c>
       <c r="K27" t="n">
-        <v>1.14</v>
+        <v>2.15</v>
       </c>
       <c r="L27" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>9.32</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>688693</t>
+          <t>002196</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1922,32 +1922,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>锴威特</t>
+          <t>方正电机</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>81.67</v>
+        <v>14.35</v>
       </c>
       <c r="F28" t="n">
-        <v>81.26000000000001</v>
+        <v>14.28</v>
       </c>
       <c r="G28" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H28" t="n">
-        <v>78.81999999999999</v>
+        <v>13.85</v>
       </c>
       <c r="I28" t="n">
-        <v>4.04</v>
+        <v>3.39</v>
       </c>
       <c r="J28" t="n">
-        <v>22.37</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="L28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7.56</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002196</t>
+          <t>688693</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>方正电机</t>
+          <t>锴威特</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14.39</v>
+        <v>81.11</v>
       </c>
       <c r="F29" t="n">
-        <v>14.32</v>
+        <v>80.7</v>
       </c>
       <c r="G29" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="H29" t="n">
-        <v>13.89</v>
+        <v>78.28</v>
       </c>
       <c r="I29" t="n">
-        <v>3.67</v>
+        <v>3.32</v>
       </c>
       <c r="J29" t="n">
-        <v>7.28</v>
+        <v>23.93</v>
       </c>
       <c r="K29" t="n">
-        <v>2.15</v>
+        <v>1.27</v>
       </c>
       <c r="L29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>5.6</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>603387</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,29 +2030,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>基蛋生物</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>63.23</v>
+        <v>10.19</v>
       </c>
       <c r="F30" t="n">
-        <v>62.91</v>
+        <v>10.14</v>
       </c>
       <c r="G30" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="H30" t="n">
-        <v>61.02</v>
+        <v>9.84</v>
       </c>
       <c r="I30" t="n">
-        <v>6.27</v>
+        <v>4.51</v>
       </c>
       <c r="J30" t="n">
-        <v>5.25</v>
+        <v>13.16</v>
       </c>
       <c r="K30" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="L30" t="n">
         <v>42</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>5.14</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>603387</t>
+          <t>603985</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2084,29 +2084,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>基蛋生物</t>
+          <t>恒润股份</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10.18</v>
+        <v>21.16</v>
       </c>
       <c r="F31" t="n">
-        <v>10.13</v>
+        <v>21.05</v>
       </c>
       <c r="G31" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="n">
-        <v>9.83</v>
+        <v>20.42</v>
       </c>
       <c r="I31" t="n">
-        <v>4.41</v>
+        <v>4.19</v>
       </c>
       <c r="J31" t="n">
-        <v>12.13</v>
+        <v>9.31</v>
       </c>
       <c r="K31" t="n">
-        <v>1.51</v>
+        <v>0.85</v>
       </c>
       <c r="L31" t="n">
         <v>42</v>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>6.97</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>605289</t>
+          <t>002537</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2138,32 +2138,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>罗曼股份</t>
+          <t>海联金汇</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>114.91</v>
+        <v>8.1</v>
       </c>
       <c r="F32" t="n">
-        <v>114.34</v>
+        <v>8.06</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="H32" t="n">
-        <v>110.91</v>
+        <v>7.82</v>
       </c>
       <c r="I32" t="n">
-        <v>3.47</v>
+        <v>3.85</v>
       </c>
       <c r="J32" t="n">
-        <v>5.77</v>
+        <v>6.79</v>
       </c>
       <c r="K32" t="n">
-        <v>0.97</v>
+        <v>1.73</v>
       </c>
       <c r="L32" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7.86</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>688485</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,29 +2192,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>九州一轨</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>41.04</v>
+        <v>63.1</v>
       </c>
       <c r="F33" t="n">
-        <v>40.83</v>
+        <v>62.78</v>
       </c>
       <c r="G33" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="H33" t="n">
-        <v>39.61</v>
+        <v>60.9</v>
       </c>
       <c r="I33" t="n">
-        <v>3.38</v>
+        <v>6.05</v>
       </c>
       <c r="J33" t="n">
-        <v>19.67</v>
+        <v>5.64</v>
       </c>
       <c r="K33" t="n">
-        <v>1.09</v>
+        <v>2.09</v>
       </c>
       <c r="L33" t="n">
         <v>41</v>
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>7.57</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>002537</t>
+          <t>605289</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>海联金汇</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8.09</v>
+        <v>114.5</v>
       </c>
       <c r="F34" t="n">
-        <v>8.050000000000001</v>
+        <v>113.93</v>
       </c>
       <c r="G34" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="H34" t="n">
-        <v>7.81</v>
+        <v>110.51</v>
       </c>
       <c r="I34" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
-        <v>5.99</v>
+        <v>6.21</v>
       </c>
       <c r="K34" t="n">
-        <v>1.67</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2279,13 +2279,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>6.18</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>002283</t>
+          <t>688661</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2300,29 +2300,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>天润工业</t>
+          <t>和林微纳</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10.58</v>
+        <v>86.81</v>
       </c>
       <c r="F35" t="n">
-        <v>10.53</v>
+        <v>86.38</v>
       </c>
       <c r="G35" t="n">
         <v>3.8</v>
       </c>
       <c r="H35" t="n">
-        <v>10.21</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>5.27</v>
+        <v>4.84</v>
       </c>
       <c r="J35" t="n">
-        <v>5.62</v>
+        <v>4.35</v>
       </c>
       <c r="K35" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="L35" t="n">
         <v>40</v>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>6.58</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>688661</t>
+          <t>002283</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>和林微纳</t>
+          <t>天润工业</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>87.12</v>
+        <v>10.57</v>
       </c>
       <c r="F36" t="n">
-        <v>86.68000000000001</v>
+        <v>10.52</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H36" t="n">
-        <v>84.08</v>
+        <v>10.2</v>
       </c>
       <c r="I36" t="n">
-        <v>5.22</v>
+        <v>5.17</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>6.08</v>
       </c>
       <c r="K36" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>5.82</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="37">
@@ -2412,28 +2412,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7.47</v>
+        <v>7.43</v>
       </c>
       <c r="F37" t="n">
-        <v>7.43</v>
+        <v>7.39</v>
       </c>
       <c r="G37" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H37" t="n">
-        <v>7.21</v>
+        <v>7.17</v>
       </c>
       <c r="I37" t="n">
-        <v>4.04</v>
+        <v>3.48</v>
       </c>
       <c r="J37" t="n">
-        <v>3.79</v>
+        <v>4.29</v>
       </c>
       <c r="K37" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="L37" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5.12</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>603985</t>
+          <t>688543</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2462,29 +2462,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>恒润股份</t>
+          <t>国科军工</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>21.08</v>
+        <v>70.69</v>
       </c>
       <c r="F38" t="n">
-        <v>20.97</v>
+        <v>70.34</v>
       </c>
       <c r="G38" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>20.34</v>
+        <v>68.23</v>
       </c>
       <c r="I38" t="n">
-        <v>3.79</v>
+        <v>3.29</v>
       </c>
       <c r="J38" t="n">
-        <v>7.51</v>
+        <v>6.37</v>
       </c>
       <c r="K38" t="n">
-        <v>0.76</v>
+        <v>1.66</v>
       </c>
       <c r="L38" t="n">
         <v>37</v>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>7.51</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>301095</t>
+          <t>300731</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,29 +2516,29 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>广立微</t>
+          <t>科创新源</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>72.88</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>72.52</v>
+        <v>68.91</v>
       </c>
       <c r="G39" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H39" t="n">
-        <v>70.34</v>
+        <v>66.84</v>
       </c>
       <c r="I39" t="n">
-        <v>4.19</v>
+        <v>4.57</v>
       </c>
       <c r="J39" t="n">
-        <v>3.63</v>
+        <v>7.35</v>
       </c>
       <c r="K39" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="L39" t="n">
         <v>34</v>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>300731</t>
+          <t>301419</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>科创新源</t>
+          <t>阿莱德</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>69.61</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
-        <v>69.26000000000001</v>
+        <v>44.78</v>
       </c>
       <c r="G40" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="H40" t="n">
-        <v>67.18000000000001</v>
+        <v>43.44</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.83</v>
       </c>
       <c r="J40" t="n">
-        <v>6.72</v>
+        <v>15.3</v>
       </c>
       <c r="K40" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="L40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>6.12</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="41">
@@ -2628,25 +2628,25 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>43.02</v>
+        <v>43.46</v>
       </c>
       <c r="F41" t="n">
-        <v>42.8</v>
+        <v>43.24</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="H41" t="n">
-        <v>41.52</v>
+        <v>41.94</v>
       </c>
       <c r="I41" t="n">
-        <v>4.09</v>
+        <v>5.15</v>
       </c>
       <c r="J41" t="n">
-        <v>18.85</v>
+        <v>20.89</v>
       </c>
       <c r="K41" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="L41" t="n">
         <v>32</v>
@@ -2657,61 +2657,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>605162</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>🔥 猎妖启动</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>量价共振/多头排列</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>新中港</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="F42" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H42" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="I42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J42" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L42" t="n">
-        <v>30</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>✅ 低</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>5.86</v>
+        <v>5.11</v>
       </c>
     </row>
   </sheetData>
